--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S121"/>
+  <dimension ref="A1:S116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -553,30 +553,30 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 80 m² · Casa Forte</t>
+          <t>Apartamento · 1 quarto · 33 m² · Rosarinho</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua André Rebouças</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Casa Forte</t>
+          <t>Rosarinho</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2150.0</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2150.0</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>65.15</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -611,17 +611,17 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-com-1-dormitorio-para-alugar-80-m-por-r-2-500-mes-casa-forte-recife-pe-1536739742</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-rosarinho-bairros-recife-com-garagem-33m2-aluguel-RS2150-id-2838265316/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 84 m² · Espinheiro</t>
+          <t>Apartamento · 30 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2600.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2600.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -696,12 +696,12 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>30.95</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-tem-84-metros-quadrados-com-3-quartos-em-espinheiro-recife-pe-1536676766</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/lindo-flat-mobiliado-1536744470</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Josinildo Imóveis</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -751,22 +751,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · Aflitos</t>
+          <t>Apartamento · 3 quartos · 70 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Nereu Gomes Maciel</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -801,17 +801,17 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>https://josinildoimoveis.com.br/imovel/apartamento-para-alugar-no-bairro-aflitos-em-recife-pe/PARJI47</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-70m2-aluguel-RS2500-id-2903057019/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Viva Real Olinda</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -846,22 +846,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 71 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 42 m² · Casa Amarela</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Rua Gildo Branco</t>
+          <t>Rua Engenheiro Oscar Ferreira</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2850.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2850.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -886,17 +886,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40.14</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-71m2-aluguel-RS2850-id-2911876830/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-forte-bairros-recife-com-garagem-42m2-aluguel-RS2600-id-2912453536/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · Torre</t>
+          <t>Apartamento · 3 quartos · 100 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -981,29 +981,29 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
-      </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-com-30-metros-quadrados-com-1-quarto-em-torre-recife-pe-1536668915</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-possui-100-metros-quadrados-com-3-quartos-em-boa-vista-recife-pe-1536781661</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · Rosarinho</t>
+          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1046,37 +1046,37 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Rosarinho</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>2124.0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>550.0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-com-1-quarto-no-rosarinho-recife-pe-1536647035</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/excelente-apartamento-semimobiliado-flat-pronto-para-morar-com-aproximadamente-32-metros-1536741419</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 54 m² · Hipódromo</t>
+          <t>Apartamento · 4 quartos · 140 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1141,42 +1141,42 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Hipódromo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3400.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>500.0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3400.0</t>
+          <t>3350.0</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>23.93</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-apartamento-2-quartos-otima-localizacao-na-estrada-de-belem-recife-1536739660</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/excelente-apartamento-amplo-proximo-ao-mar-1536716034</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Tamarineira</t>
+          <t>Apartamento · 3 quartos · 68 m² · Campo Grande</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1236,42 +1236,42 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Tamarineira</t>
+          <t>Campo Grande</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>3400.0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>950.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3400.0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apt-60m2-mobiliado-de-2-quartos-2-wcs-1-vaga-de-garagem-1536693487</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/o-3-quartos-mais-ventilado-do-mundo-1481906905</t>
         </is>
       </c>
     </row>
@@ -1313,30 +1313,30 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 55 m² · Graças</t>
+          <t>Apartamento · 2 quartos · 70 m² · Casa Forte</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Edson Álvares</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Casa Forte</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3700.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3700.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67.27</t>
+          <t>51.43</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1371,17 +1371,17 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-2quartos-1suite-55m-armarios-com-lazer-02-vagas-1536662262</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-forte-bairros-recife-com-garagem-70m2-aluguel-RS3600-id-2912455117/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1408,185 +1408,181 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Recife, OLX Imóveis</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 56 m² · 1 vaga · Espinheiro</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Rua São Salvador, 200</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Espinheiro</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4400.0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>850.0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>4825.0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>86.16</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>56.0</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-espinheiro-56m2-RS4000/id-44249374/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Olinda</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 51 m² · Aflitos</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Aflitos</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>3990.0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>3990.0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 58 m² · 1 vaga · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Rua Norberto Pessoa, 238</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1300.0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1300.0</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>78.24</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>51.0</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-com-2-quartos-nos-aflitos-recife-pe-1536643666</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>OLX Imóveis</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 51 m² · Aflitos</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Aflitos</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4000.0</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>4000.0</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>78.43</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>51.0</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-tem-51-metros-quadrados-com-2-quartos-em-aflitos-recife-pe-1536668721</t>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>22.41</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>58.0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1300/id-46461545/</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1598,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 58 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 41 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rua Norberto Pessoa, 238</t>
+          <t>Rua Professor Marculino Botelho, 404</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1617,37 +1613,37 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1300.0</t>
+          <t>1200.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1300.0</t>
+          <t>1400.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>34.15</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1662,22 +1658,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1300/id-46461545/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-pe-olinda-bairro-novo-41m2-RS1200/id-45673360/</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1681,7 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1693,37 +1689,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 41 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 50 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rua Professor Marculino Botelho, 404</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1200.0</t>
+          <t>1100.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>97.38</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1400.0</t>
+          <t>1447.38</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1733,17 +1729,17 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>34.15</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1753,7 +1749,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1768,7 +1764,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-pe-olinda-bairro-novo-41m2-RS1200/id-45673360/</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/224/apartamento-2-quartos-jose-mariano-boa-vista-recife/</t>
         </is>
       </c>
     </row>
@@ -1776,30 +1772,30 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 52 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Caetano Ribeiro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1100.0</t>
+          <t>1300.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1809,12 +1805,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>97.38</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1447.38</t>
+          <t>1550.0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1824,7 +1820,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.81</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1834,7 +1830,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1844,22 +1840,22 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/224/apartamento-2-quartos-jose-mariano-boa-vista-recife/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-52m2-aluguel-RS1300-id-2911238418/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2227,7 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2239,7 +2235,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Apartamento · 36 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 50 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2249,42 +2245,42 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1900.0</t>
+          <t>1450.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>405.0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>80.96</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1900.0</t>
+          <t>1935.96</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>52.78</t>
+          <t>38.72</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2299,22 +2295,22 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-no-rua-carlos-nigro-casa-caiada-olinda-pe-casa-caiada-olin-1536641197</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/6691/apartamento-2-quartos-santo-amaro-recife/</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2318,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2330,37 +2326,37 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · Santo Amaro</t>
+          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Coronel Alberto Lundgren, 604</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1450.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>405.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>80.96</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1935.96</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2370,17 +2366,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>38.72</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2390,22 +2386,22 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/6691/apartamento-2-quartos-santo-amaro-recife/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS1800/id-46397377/</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2409,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2421,32 +2417,32 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rua Coronel Alberto Lundgren, 604</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2461,17 +2457,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2481,22 +2477,22 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>30</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS1800/id-46397377/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2500,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2512,17 +2508,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 38 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Coronel Alberto Lundgren, 604</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2532,27 +2528,27 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>52.63</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2562,7 +2558,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2572,7 +2568,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2587,7 +2583,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/flat-quatro-rodas-1526587978</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS2000/id-46397376/</t>
         </is>
       </c>
     </row>
@@ -2595,35 +2591,35 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 2 quartos · 65 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Professor José Cândido Pessoa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2633,27 +2629,27 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2663,22 +2659,22 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-65m2-aluguel-RS2200-id-2897302602/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2694,59 +2690,59 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rua Coronel Alberto Lundgren, 604</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O25" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -2754,22 +2750,22 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS2000/id-46397376/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -2777,20 +2773,20 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Apartamento · 36 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2800,7 +2796,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2815,7 +2811,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2825,17 +2821,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>61.11</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2845,22 +2841,22 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-no-rua-carlos-nigro-casa-caiada-olinda-pe-casa-caiada-olin-1536640769</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-31m2-RS2500/id-45418272/</t>
         </is>
       </c>
     </row>
@@ -2868,30 +2864,30 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 65 m² · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 35 m² · Parnamirim</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rua Professor José Cândido Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2906,7 +2902,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2916,17 +2912,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>33.85</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2936,22 +2932,22 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-65m2-aluguel-RS2200-id-2897302602/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-excelente-flat-com-1-quarto-no-bairro-do-parnamirim-recife-1529402955</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2963,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 71 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 80 m² · Casa Forte</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2977,12 +2973,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Casa Forte</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2350.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2997,7 +2993,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2350.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3007,12 +3003,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3027,22 +3023,22 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1506210201</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-com-1-dormitorio-para-alugar-80-m-por-r-2-500-mes-casa-forte-recife-pe-1536739742</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3046,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3058,57 +3054,57 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 72 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Presidente Getúlio Vargas, 1748</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2360.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>683.0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2360.0</t>
+          <t>2576.0</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>32.78</t>
+          <t>71.56</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3118,22 +3114,22 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1471005149</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-36m2-RS1800/id-45673358/</t>
         </is>
       </c>
     </row>
@@ -3149,52 +3145,52 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua Professor José Cândido Pessoa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>684.0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2577.0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3209,22 +3205,22 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-720m2-RS1800/id-43805924/</t>
         </is>
       </c>
     </row>
@@ -3232,30 +3228,30 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 84 m² · Espinheiro</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3270,7 +3266,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3280,17 +3276,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>30.95</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3300,22 +3296,22 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-31m2-RS2500/id-45418272/</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-tem-84-metros-quadrados-com-3-quartos-em-espinheiro-recife-pe-1536676766</t>
         </is>
       </c>
     </row>
@@ -3323,30 +3319,30 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 55 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Professor José Cândido Pessoa</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3361,7 +3357,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3371,19 +3367,19 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>47.27</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="O32" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -3391,22 +3387,22 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-apto-de-1-qt-varanda-e-piscina-no-edf-monteiro-home-service-casa-caiada-olinda-1536608306</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-55m2-aluguel-RS2600-id-2912341217/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3414,30 +3410,30 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 35 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3452,7 +3448,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3462,7 +3458,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>78.12</t>
+          <t>74.29</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3472,32 +3468,32 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/flat-empresarial-jam-1523997215</t>
+          <t>https://www.vivareal.com.br/imovel/flat-1-quartos-bairro-novo-bairros-olinda-com-garagem-35m2-aluguel-RS2600-id-2912188115/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3505,25 +3501,25 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · Aflitos</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rua da Glória</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3533,7 +3529,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3543,27 +3539,27 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2691.0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3573,22 +3569,22 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-50m2-aluguel-RS2500-id-2904799000/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-aflitos-recife--pe_33374631</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3592,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Josinildo Imóveis</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3604,57 +3600,57 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · Aflitos</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Avenida Presidente Getúlio Vargas, 1748</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>683.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2576.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>71.56</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3664,22 +3660,22 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-36m2-RS1800/id-45673358/</t>
+          <t>https://josinildoimoveis.com.br/imovel/apartamento-para-alugar-no-bairro-aflitos-em-recife-pe/PARJI47</t>
         </is>
       </c>
     </row>
@@ -3687,7 +3683,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3695,47 +3691,47 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · Tamarineira</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rua Professor José Cândido Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Tamarineira</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>684.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2577.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3745,7 +3741,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3755,22 +3751,22 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-720m2-RS1800/id-43805924/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-1-quarto-alugar-tamarineira-recife--pe_33377972</t>
         </is>
       </c>
     </row>
@@ -3778,35 +3774,35 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 55 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rua Professor José Cândido Pessoa</t>
+          <t>Rua Otaviano Pessoa Monteiro, 93</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2600.0</t>
+          <t>1526.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1178.0</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3816,17 +3812,17 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2600.0</t>
+          <t>2704.0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>47.27</t>
+          <t>29.08</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3846,22 +3842,22 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-55m2-aluguel-RS2600-id-2912341217/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1526/id-45586419/</t>
         </is>
       </c>
     </row>
@@ -3877,12 +3873,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 90 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Rua Doutor Manoel de Almeida Belo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3892,7 +3888,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2600.0</t>
+          <t>2750.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3907,7 +3903,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2600.0</t>
+          <t>2750.0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3917,42 +3913,42 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>74.29</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/flat-1-quartos-bairro-novo-bairros-olinda-com-garagem-35m2-aluguel-RS2600-id-2912188115/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-bairros-olinda-com-garagem-90m2-aluguel-RS2750-id-2706913615/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3956,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3968,7 +3964,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · Aflitos</t>
+          <t>Apartamento · 2 quartos · 63 m² · Aflitos</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3983,12 +3979,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3998,22 +3994,22 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2691.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4028,22 +4024,22 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-aflitos-recife--pe_33374631</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/850251137-34</t>
         </is>
       </c>
     </row>
@@ -4051,30 +4047,30 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · Tamarineira</t>
+          <t>Apartamento · 1 quarto · 40 m² · Ilha do Leite</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Jornalista Trajano Chacon</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tamarineira</t>
+          <t>Ilha do Leite</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4089,7 +4085,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4099,7 +4095,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4109,7 +4105,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4119,22 +4115,22 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-1-quarto-alugar-tamarineira-recife--pe_33377972</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-ilha-do-leite-bairros-recife-com-garagem-40m2-aluguel-RS2800-id-2912104117/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4142,20 +4138,20 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 36 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa Monteiro, 93</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4165,12 +4161,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1526.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1178.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4180,22 +4176,22 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2704.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4205,27 +4201,27 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1526/id-45586419/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-36m2-aluguel-RS2800-id-2705654338/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4233,30 +4229,30 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 31 m² · 1 vaga · Paissandu</t>
+          <t>Apartamento · 3 quartos · 71 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Gildo Branco</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paissandu</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>2850.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4271,7 +4267,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>2850.0</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4281,17 +4277,17 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>40.14</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4301,22 +4297,22 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-no-versatti-residence-service-paissandu-recife-pe-1536641831</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-71m2-aluguel-RS2850-id-2911876830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4320,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -4332,22 +4328,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 90 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 31 m² · 1 vaga · Parnamirim</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Condado, Nº 50</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>2850.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4362,7 +4358,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>2851.0</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4372,42 +4368,42 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>31.11</t>
+          <t>91.97</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>31.0</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-bairro-novo-1492211765</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-31m2-RS2850/id-45010491/</t>
         </is>
       </c>
     </row>
@@ -4415,35 +4411,35 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>CTI Imobiliária, Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 63 m² · Aflitos</t>
+          <t>Apartamento · 2 quartos · 45 m² · 1 vaga · Torre</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua José De Holanda, 854</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>380.0</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4453,17 +4449,17 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>2880.0</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4473,7 +4469,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4483,22 +4479,22 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/850251137-34</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-torre-recife-pe/1353</t>
         </is>
       </c>
     </row>
@@ -4506,90 +4502,90 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>380.0</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>176.42</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>2956.42</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-36m2-aluguel-RS2800-id-2705654338/?source=ranking%2Crp</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/6596/apartamento-2-quartos-torre-recife/</t>
         </is>
       </c>
     </row>
@@ -4597,7 +4593,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>CTI Imobiliária</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4605,57 +4601,57 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 31 m² · 1 vaga · Parnamirim</t>
+          <t>Apartamento · 2 quartos · 80 m² · Graças</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rua Condado, Nº 50</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2850.0</t>
+          <t>1850.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>953.0</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2851.0</t>
+          <t>2997.0</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>91.97</t>
+          <t>37.46</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4665,22 +4661,22 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>57</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-31m2-RS2850/id-45010491/</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-gracas-recife-pe/6882</t>
         </is>
       </c>
     </row>
@@ -4688,7 +4684,7 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CTI Imobiliária, Chaves na Mão Recife</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4696,27 +4692,27 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 45 m² · 1 vaga · Torre</t>
+          <t>Apartamento · 2 quartos · 42 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rua José De Holanda, 854</t>
+          <t>Rua Ulisses Tenório de Albuquerque</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2998.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>380.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4726,17 +4722,17 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2880.0</t>
+          <t>2998.0</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>71.38</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4746,7 +4742,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4756,22 +4752,22 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-torre-recife-pe/1353</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-42m2-aluguel-RS2998-id-2911376544/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4775,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -4787,59 +4783,59 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
+          <t>Apartamento · 3 quartos · 92 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Carlos De Lima Cavalcante</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>380.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>176.42</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2956.42</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>32.61</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="O48" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -4847,7 +4843,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -4862,7 +4858,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/6596/apartamento-2-quartos-torre-recife/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS3000/id-42437394/</t>
         </is>
       </c>
     </row>
@@ -4870,7 +4866,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CTI Imobiliária</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -4878,57 +4874,57 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Graças</t>
+          <t>Apartamento · 1 quarto · 40 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos De Lima Cavalcante, 2595</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1850.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>953.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2997.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>37.46</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4938,22 +4934,22 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-gracas-recife-pe/6882</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-40m2-RS3000/id-45710865/</t>
         </is>
       </c>
     </row>
@@ -4961,11 +4957,11 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, OLX Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4984,7 +4980,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1674.0</t>
+          <t>1822.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4994,12 +4990,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>295.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2999.5</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5009,7 +5005,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>32.26</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5060,12 +5056,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 92 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 42 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Avenida Carlos De Lima Cavalcante</t>
+          <t>Avenida Doutor José Augusto Moreira, 900</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5100,17 +5096,17 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5120,7 +5116,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -5135,7 +5131,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS3000/id-42437394/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-RS3000/id-44380568/</t>
         </is>
       </c>
     </row>
@@ -5143,7 +5139,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -5151,17 +5147,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 40 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 37 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos De Lima Cavalcante, 2595</t>
+          <t>Rua Do Futuro, 20</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5191,7 +5187,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>81.08</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5211,22 +5207,22 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-40m2-RS3000/id-45710865/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-37m2-RS3000/id-44879310/</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5230,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -5242,17 +5238,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 42 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 30 m² · Torre</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Avenida Doutor José Augusto Moreira, 900</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5282,7 +5278,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5292,7 +5288,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5302,22 +5298,22 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-RS3000/id-44380568/</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-com-30-metros-quadrados-com-1-quarto-em-torre-recife-pe-1536668915</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5321,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -5333,12 +5329,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 37 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 1 quarto · 33 m² · Graças</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rua Do Futuro, 20</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5353,7 +5349,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5368,12 +5364,12 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>81.08</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5383,7 +5379,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5393,22 +5389,22 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-37m2-RS3000/id-44879310/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-1-quarto-alugar-33m2-gracas-recife--pe_33286759</t>
         </is>
       </c>
     </row>
@@ -5416,20 +5412,20 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · Graças</t>
+          <t>Apartamento · 3 quartos · 95 m² · Graças</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Amélia</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5444,7 +5440,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5459,22 +5455,22 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5484,22 +5480,22 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-1-quarto-alugar-33m2-gracas-recife--pe_33286759</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-gracas-bairros-recife-com-garagem-95m2-aluguel-RS3000-id-2912199906/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5507,7 +5503,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -5515,17 +5511,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 38 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 35 m² · Rosarinho</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Rua Engenheiro Sampaio</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Rosarinho</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5555,7 +5551,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>78.95</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5570,27 +5566,27 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-38m2-aluguel-RS3000-id-2911358634/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/flat-1-quartos-rosarinho-bairros-recife-com-garagem-35m2-aluguel-RS3000-id-2912109324/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5697,12 +5693,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 62 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 38 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa Monteiro</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5737,42 +5733,42 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>48.39</t>
+          <t>78.95</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-62m2-aluguel-RS3000-id-2911451041/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-38m2-aluguel-RS3000-id-2911358634/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6140,7 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -6152,7 +6148,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 44 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 38 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6162,7 +6158,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -6192,12 +6188,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -6212,22 +6208,22 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-flat-mobiliado-em-olinda-de-2-quartos-perto-da-fmo-e-do-patteo-1524537393</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-1-quarto-alugar-38m2-boa-vista-recife--pe_33378812</t>
         </is>
       </c>
     </row>
@@ -6235,20 +6231,20 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 88 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -6283,17 +6279,17 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6303,22 +6299,22 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1534740130</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3200-id-2686319323/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -6326,20 +6322,20 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Apartamento · 41 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 88 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Otaviano Pessoa Monteiro</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6374,17 +6370,17 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>78.05</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -6394,22 +6390,22 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/flat-residencial-jam-1481475897</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-88m2-aluguel-RS3200-id-2911479216/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -6417,7 +6413,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -6425,22 +6421,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 38 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 66 m² · 1 vaga · Campo Grande</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Barão De Vera Cruz</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Campo Grande</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6455,7 +6451,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6465,19 +6461,19 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="O66" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -6485,22 +6481,22 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-1-quarto-alugar-38m2-boa-vista-recife--pe_33378812</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-campo-grande-79m2-RS3300/id-44353442/</t>
         </is>
       </c>
     </row>
@@ -6508,30 +6504,30 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 48 m² · 1 vaga · Torre</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Rua José De Holanda</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6546,7 +6542,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6556,7 +6552,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>68.75</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6576,22 +6572,22 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3200-id-2686319323/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-RS3300/id-35751827/</t>
         </is>
       </c>
     </row>
@@ -6607,17 +6603,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 66 m² · 1 vaga · Campo Grande</t>
+          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Casa Forte</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rua Barão De Vera Cruz</t>
+          <t>Rua Lemos Torres, 147</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Campo Grande</t>
+          <t>Casa Forte</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -6637,7 +6633,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3301.0</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6647,42 +6643,42 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>60.02</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-campo-grande-79m2-RS3300/id-44353442/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-forte-55m2-RS3300/id-41878758/</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6686,7 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -6698,22 +6694,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 48 m² · 1 vaga · Torre</t>
+          <t>Apartamento · 2 quartos · 54 m² · Hipódromo</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rua José De Holanda</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Hipódromo</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3400.0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6728,7 +6724,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3400.0</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6738,7 +6734,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>68.75</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -6748,7 +6744,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6758,22 +6754,22 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-RS3300/id-35751827/</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-apartamento-2-quartos-otima-localizacao-na-estrada-de-belem-recife-1536739660</t>
         </is>
       </c>
     </row>
@@ -6781,7 +6777,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -6789,22 +6785,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Casa Forte</t>
+          <t>Apartamento · 2 quartos · 57 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rua Lemos Torres, 147</t>
+          <t>Rua Francisco Ambrósio De Barros Leite, 1225</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Casa Forte</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6819,7 +6815,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>3301.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -6829,7 +6825,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>60.02</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -6849,22 +6845,22 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-forte-55m2-RS3300/id-41878758/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-RS3500/id-42986293/</t>
         </is>
       </c>
     </row>
@@ -6872,30 +6868,30 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Olinda, OLX Imóveis</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 95 m² · 1 vaga · Aflitos</t>
+          <t>Apartamento · 2 quartos · 59 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Pereira Simões, 1529 - 2</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>3400.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6910,7 +6906,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>3400.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -6920,17 +6916,17 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>35.79</t>
+          <t>59.32</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -6940,22 +6936,22 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/edf-araras-1532381063</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-59m2-RS3500/id-45711136/</t>
         </is>
       </c>
     </row>
@@ -6963,7 +6959,7 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -6971,17 +6967,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 57 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 39 m² · 1 vaga · Santana</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rua Francisco Ambrósio De Barros Leite, 1225</t>
+          <t>Rua Samuel Farias, 70</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Santana</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -7011,12 +7007,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>89.74</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -7031,22 +7027,22 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-RS3500/id-42986293/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-santana-RS3500/id-46556867/</t>
         </is>
       </c>
     </row>
@@ -7054,7 +7050,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -7062,17 +7058,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 59 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Boa Vista</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rua Pereira Simões, 1529 - 2</t>
+          <t>Rua Dom Bosco, 1297</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -7102,17 +7098,17 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>59.32</t>
+          <t>116.67</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7122,22 +7118,22 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-59m2-RS3500/id-45711136/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-boa-vista-RS3500/id-45835639/</t>
         </is>
       </c>
     </row>
@@ -7145,7 +7141,7 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -7153,17 +7149,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 39 m² · 1 vaga · Santana</t>
+          <t>Apartamento · 1 quarto · 33 m² · Graças</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rua Samuel Farias, 70</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Santana</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -7193,7 +7189,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>89.74</t>
+          <t>106.06</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -7203,7 +7199,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7213,22 +7209,22 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-santana-RS3500/id-46556867/</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-possui-33-metros-quadrados-com-1-quarto-em-gracas-recife-pe-1531183418</t>
         </is>
       </c>
     </row>
@@ -7236,7 +7232,7 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -7244,57 +7240,57 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 60 m² · Tamarineira</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rua Dom Bosco, 1297</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Tamarineira</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
+          <t>2400.0</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>950.0</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
           <t>3500.0</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>3500.0</t>
-        </is>
-      </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>116.67</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7304,22 +7300,22 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-boa-vista-RS3500/id-45835639/</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apt-60m2-mobiliado-de-2-quartos-2-wcs-1-vaga-de-garagem-1536693487</t>
         </is>
       </c>
     </row>
@@ -7691,7 +7687,7 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -7699,17 +7695,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Apartamento · 4 quartos · 130 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 51 m² · Torre</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Avenida Ministro Marcos Freire</t>
+          <t>Rua dos Operários</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -7739,17 +7735,17 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -7759,22 +7755,22 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-casa-caiada-bairros-olinda-com-garagem-130m2-aluguel-RS3500-id-2911955918/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-torre-bairros-recife-com-garagem-51m2-aluguel-RS3500-id-2912459623/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -7782,7 +7778,7 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -7790,17 +7786,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 61 m² · Tamarineira</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Rua São Vicente</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Tamarineira</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -7830,19 +7826,19 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="O81" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -7850,22 +7846,22 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-60m2-aluguel-RS3500-id-2904577437/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-tamarineira-bairros-recife-com-garagem-61m2-aluguel-RS3500-id-2912447139/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -7881,12 +7877,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 63 m² · Casa Caiada</t>
+          <t>Apartamento · 4 quartos · 130 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Rua Professor Francisco Xavier Paes Barreto</t>
+          <t>Avenida Ministro Marcos Freire</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -7921,42 +7917,42 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>26.92</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>63.0</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-63m2-aluguel-RS3500-id-2863367956/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-casa-caiada-bairros-olinda-com-garagem-130m2-aluguel-RS3500-id-2911955918/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -7972,17 +7968,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 59 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 63 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Rua Pereira Simões</t>
+          <t>Rua Professor Francisco Xavier Paes Barreto</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -8012,42 +8008,42 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>59.32</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-59m2-aluguel-RS3500-id-2905566215/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-63m2-aluguel-RS3500-id-2863367956/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8233,7 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -8245,17 +8241,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 86 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 1 quarto · 34 m² · 1 vaga · Parnamirim</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Parnamirim, 375</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -8275,7 +8271,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3601.0</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -8285,17 +8281,17 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>105.91</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -8305,22 +8301,22 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-no-edf-rainha-santa-isabel-gracas-recife-pe-1536641795</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-34m2-RS3600/id-38113683/</t>
         </is>
       </c>
     </row>
@@ -8328,67 +8324,67 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Recife, Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · 1 vaga · Parnamirim</t>
+          <t>Apartamento · 2 quartos · 57 m² · 1 vaga · Santo Amaro</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Dois de Julho</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3700.0</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3700.0</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>102.86</t>
+          <t>64.91</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="O87" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -8396,22 +8392,22 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-no-beach-class-jaqueira-parnamirim-recife-pe-1532730665</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-santo-amaro-RS3700/id-46659867/</t>
         </is>
       </c>
     </row>
@@ -8419,7 +8415,7 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -8427,47 +8423,47 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 52 m² · 1 vaga · Torre</t>
+          <t>Apartamento · 2 quartos · 56 m² · 1 vaga · Torreão</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Cândido Lacerda, 221</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Torreão</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3700.0</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>66.07</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -8477,7 +8473,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -8487,22 +8483,22 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-no-engenho-capibaribe-torre-recife-pe-1536641254</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torreao-62m2-RS3500/id-46711944/</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8506,7 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -8518,27 +8514,27 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 34 m² · 1 vaga · Parnamirim</t>
+          <t>Apartamento · 3 quartos · Encruzilhada</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Avenida Parnamirim, 375</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3700.0</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8548,27 +8544,27 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>3601.0</t>
+          <t>3700.0</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>105.91</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -8578,7 +8574,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
@@ -8593,7 +8589,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-34m2-RS3600/id-38113683/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-encruzilhada-recife--pe_33362592</t>
         </is>
       </c>
     </row>
@@ -8601,7 +8597,7 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -8609,37 +8605,37 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 56 m² · 1 vaga · Torreão</t>
+          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Paissandu</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Rua Cândido Lacerda, 221</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Torreão</t>
+          <t>Paissandu</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>627.0</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>3700.0</t>
+          <t>3756.0</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -8649,17 +8645,17 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>66.07</t>
+          <t>117.38</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -8669,22 +8665,22 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torreao-62m2-RS3500/id-46711944/</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/edf-versatti-residence-service-mobiliado-1431994234</t>
         </is>
       </c>
     </row>
@@ -8692,35 +8688,35 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Recife, OLX Imóveis</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · Encruzilhada</t>
+          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Torre</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua José De Holanda, 854</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>3700.0</t>
+          <t>3800.0</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8730,27 +8726,27 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>3700.0</t>
+          <t>3800.0</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>87.36</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -8760,22 +8756,22 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-encruzilhada-recife--pe_33362592</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-43m2-RS3800/id-45247450/</t>
         </is>
       </c>
     </row>
@@ -8783,7 +8779,7 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -8791,57 +8787,57 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 57 m² · 1 vaga · Santo Amaro</t>
+          <t>Apartamento · 1 quarto · 65 m² · Encruzilhada</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Rua Dois De Julho, --</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>3700.0</t>
+          <t>3800.0</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>3720.0</t>
+          <t>3800.0</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>65.26</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -8851,22 +8847,22 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-santo-amaro-RS3700/id-46659867/</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-com-65-metros-quadrados-com-1-quarto-em-encruzilhada-recife-pe-1531178255</t>
         </is>
       </c>
     </row>
@@ -8882,7 +8878,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Paissandu</t>
+          <t>Apartamento · 1 quarto · 32 m² · Rosarinho</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8892,37 +8888,37 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Paissandu</t>
+          <t>Rosarinho</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3800.0</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>627.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>3756.0</t>
+          <t>3800.0</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>117.38</t>
+          <t>118.75</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -8957,7 +8953,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/edf-versatti-residence-service-mobiliado-1431994234</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-possui-32-metros-quadrados-com-1-quarto-em-rosarinho-recife-pe-1472930251</t>
         </is>
       </c>
     </row>
@@ -8965,30 +8961,30 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife, OLX Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Torre</t>
+          <t>Apartamento · 1 quarto · 34 m² · Jaqueira</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Rua José De Holanda, 854</t>
+          <t>Av Parnamirim</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Jaqueira</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>3800.0</t>
+          <t>3850.0</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -9003,7 +8999,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>3800.0</t>
+          <t>3850.0</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -9013,17 +9009,17 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>87.36</t>
+          <t>113.24</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -9033,22 +9029,22 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-43m2-RS3800/id-45247450/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-pe-recife-jaqueira-34m2-RS3850/id-45251422/</t>
         </is>
       </c>
     </row>
@@ -9064,7 +9060,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 32 m² · Rosarinho</t>
+          <t>Apartamento · 1 quarto · 35 m² · Parnamirim</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -9074,12 +9070,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosarinho</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>3800.0</t>
+          <t>3950.0</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -9094,7 +9090,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>3800.0</t>
+          <t>3950.0</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -9104,7 +9100,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>118.75</t>
+          <t>112.86</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -9124,7 +9120,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
@@ -9139,7 +9135,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-possui-32-metros-quadrados-com-1-quarto-em-rosarinho-recife-pe-1472930251</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-com-35-metros-quadrados-com-1-quarto-em-parnamirim-recife-pe-1517750493</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9151,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 65 m² · 2 vagas · Casa Amarela</t>
+          <t>Apartamento · 2 quartos · 51 m² · Aflitos</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9165,42 +9161,42 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>3800.0</t>
+          <t>3990.0</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>3820.0</t>
+          <t>3990.0</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>58.77</t>
+          <t>78.24</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -9215,22 +9211,22 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-com-excelente-localizacao-na-rua-conselheiro-nabuco-210-1536589680</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-tem-51-metros-quadrados-com-2-quartos-em-aflitos-recife-pe-1534852699</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9234,7 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -9246,22 +9242,22 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 34 m² · Jaqueira</t>
+          <t>Apartamento · 2 quartos · 51 m² · Aflitos</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Av Parnamirim</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Jaqueira</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>3850.0</t>
+          <t>4000.0</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9276,7 +9272,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>3850.0</t>
+          <t>4000.0</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -9286,17 +9282,17 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>113.24</t>
+          <t>78.43</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -9306,22 +9302,22 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-pe-recife-jaqueira-34m2-RS3850/id-45251422/</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-tem-51-metros-quadrados-com-2-quartos-em-aflitos-recife-pe-1536668721</t>
         </is>
       </c>
     </row>
@@ -9329,30 +9325,30 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Apartamento · 37 m² · Espinheiro</t>
+          <t>Apartamento · 2 quartos · 42 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos de Lima Cavalcanti</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>3900.0</t>
+          <t>4000.0</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -9367,7 +9363,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>3900.0</t>
+          <t>4000.0</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -9377,17 +9373,17 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>105.41</t>
+          <t>95.24</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -9397,7 +9393,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -9412,7 +9408,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-em-espinheiro-recife-1536591468</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-derby-bairros-recife-com-garagem-42m2-aluguel-RS4000-id-2912348332/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -9420,7 +9416,7 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -9428,47 +9424,47 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Paissandu</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Estácio Coimbra, 171</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Paissandu</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>3900.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>620.0</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>3900.0</t>
+          <t>4020.0</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>70.91</t>
+          <t>91.36</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -9478,7 +9474,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -9488,22 +9484,22 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-em-boa-vista-recife-1536591457</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-paissandu-44m2-RS3200/id-42692438/</t>
         </is>
       </c>
     </row>
@@ -9511,7 +9507,7 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Rogério Corretor</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -9519,7 +9515,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 51 m² · Aflitos</t>
+          <t>Apartamento · 3 quartos · 145 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9529,12 +9525,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>3990.0</t>
+          <t>4100.0</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -9549,7 +9545,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>3990.0</t>
+          <t>4100.0</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -9559,12 +9555,12 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>78.24</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -9579,22 +9575,22 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-tem-51-metros-quadrados-com-2-quartos-em-aflitos-recife-pe-1534852699</t>
+          <t>https://www.rogeriocorretor.com/imovel/apartamento-3-quartos-casa-caiada-olinda-2-vagas-145m2-code-333</t>
         </is>
       </c>
     </row>
@@ -9602,7 +9598,7 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -9610,7 +9606,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 88 m² · 1 vaga · Espinheiro</t>
+          <t>Apartamento · 2 quartos · 43 m² · Casa Amarela</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -9620,17 +9616,17 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>4000.0</t>
+          <t>4200.0</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9640,7 +9636,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>4001.0</t>
+          <t>4200.0</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -9650,12 +9646,12 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>45.47</t>
+          <t>97.67</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -9670,22 +9666,22 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-em-espinheiro-recife-1536591228</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-43m2-casa-amarela-recife--pe_33376830</t>
         </is>
       </c>
     </row>
@@ -9693,7 +9689,7 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Rogério Corretor</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -9701,37 +9697,37 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Paissandu</t>
+          <t>Apartamento · 2 quartos · 80 m² · Aflitos</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Rua Estácio Coimbra, 171</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Paissandu</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>620.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>4020.0</t>
+          <t>4350.0</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -9741,7 +9737,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>91.36</t>
+          <t>54.38</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -9751,7 +9747,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -9761,22 +9757,22 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-paissandu-44m2-RS3200/id-42692438/</t>
+          <t>https://www.rogeriocorretor.com/imovel/apartamento-2-quartos-aflitos-recife-1-vaga-80m2-code-695</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9780,7 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Rogério Corretor</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -9792,7 +9788,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 145 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 51 m² · Torre</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -9802,42 +9798,42 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>4100.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>850.0</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>4100.0</t>
+          <t>4361.0</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>85.51</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -9852,22 +9848,22 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>https://www.rogeriocorretor.com/imovel/apartamento-3-quartos-casa-caiada-olinda-2-vagas-145m2-code-333</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-venda-tem-51-metros-quadrados-com-2-quartos-em-torre-recife-pe-1452568355</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9871,7 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -9883,27 +9879,27 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 43 m² · Casa Amarela</t>
+          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos De Lima Cavalcante</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>4200.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1195.0</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -9913,7 +9909,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>4200.0</t>
+          <t>4395.0</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -9923,7 +9919,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>97.67</t>
+          <t>79.91</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -9933,7 +9929,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -9943,22 +9939,22 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-43m2-casa-amarela-recife--pe_33376830</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-55m2-RS3200/id-46174975/</t>
         </is>
       </c>
     </row>
@@ -9966,35 +9962,35 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Rogério Corretor</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Aflitos</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Amarela</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Arnoldo Magalhães</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>4400.0</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -10004,29 +10000,29 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>4350.0</t>
+          <t>4400.0</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>54.38</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="O105" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -10039,17 +10035,17 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>https://www.rogeriocorretor.com/imovel/apartamento-2-quartos-aflitos-recife-1-vaga-80m2-code-695</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-amarela-bairros-recife-com-garagem-80m2-aluguel-RS4400-id-2912439916/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -10057,7 +10053,7 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -10065,57 +10061,57 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 51 m² · Torre</t>
+          <t>Apartamento · 3 quartos · 98 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Ministro Marcos Freire, 3291</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>4499.0</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>850.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>4361.0</t>
+          <t>4499.0</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>85.51</t>
+          <t>45.91</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -10125,22 +10121,22 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-venda-tem-51-metros-quadrados-com-2-quartos-em-torre-recife-pe-1452568355</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4499/id-46461488/</t>
         </is>
       </c>
     </row>
@@ -10156,12 +10152,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 85 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos De Lima Cavalcante</t>
+          <t>Avenida Ministro Marcos Freire</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -10171,12 +10167,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>1195.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -10186,27 +10182,27 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>4395.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>79.91</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -10216,7 +10212,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
@@ -10231,7 +10227,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-55m2-RS3200/id-46174975/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-110m2-RS4500/id-42417501/</t>
         </is>
       </c>
     </row>
@@ -10239,15 +10235,15 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · 2 vagas · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 97 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10287,7 +10283,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>52.94</t>
+          <t>46.39</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -10307,7 +10303,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
@@ -10322,7 +10318,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-110m2-RS4500/id-42417501/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4500/id-46421413/</t>
         </is>
       </c>
     </row>
@@ -10330,7 +10326,7 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Rogério Corretor</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -10338,17 +10334,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 97 m² · 2 vagas · Casa Caiada</t>
+          <t>Apartamento · 4 quartos · 90 m² · Torre</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Avenida Ministro Marcos Freire, 3291</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -10378,17 +10374,17 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>46.39</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -10398,7 +10394,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
@@ -10413,7 +10409,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4500/id-46421413/</t>
+          <t>https://www.rogeriocorretor.com/imovel/casa-4-quartos-torre-recife-90m2-code-736</t>
         </is>
       </c>
     </row>
@@ -10421,15 +10417,15 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 97 m² · 2 vagas · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 145 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10469,19 +10465,19 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>46.39</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="O110" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -10489,22 +10485,22 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4499/id-46461488/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-145m2-aluguel-RS4500-id-2912449937/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -10512,7 +10508,7 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -10520,22 +10516,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 2 vagas · Parnamirim</t>
+          <t>Apartamento · 3 quartos · 118 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Ministro Marcos Freire, 2505</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>5000.0</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -10550,7 +10546,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>5000.0</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -10560,7 +10556,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>42.37</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -10570,7 +10566,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -10580,22 +10576,22 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-no-abraham-lincoln-parnamirim-recife-pe-1536641390</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS5000/id-42812242/</t>
         </is>
       </c>
     </row>
@@ -10611,7 +10607,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 92 m² · 2 vagas · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 38 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10621,12 +10617,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>5000.0</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -10641,7 +10637,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>5000.0</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -10651,12 +10647,12 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>48.91</t>
+          <t>131.58</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -10671,22 +10667,22 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-1529307796</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-tem-38-metros-quadrados-com-1-quarto-em-boa-vista-recife-pe-1525997038</t>
         </is>
       </c>
     </row>
@@ -10694,7 +10690,7 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -10702,57 +10698,57 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 2 vagas · Parnamirim</t>
+          <t>Apartamento · 2 quartos · 148 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Ministro Marcos Freire, 3455</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1388.0</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>500.0</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>5388.0</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>36.41</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -10762,22 +10758,22 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-no-abraham-lincoln-parnamirim-recife-pe-1536590317</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-148m2-RS3500/id-45673363/</t>
         </is>
       </c>
     </row>
@@ -10785,7 +10781,7 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Rogério Corretor</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -10793,7 +10789,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Apartamento · 4 quartos · 90 m² · Torre</t>
+          <t>Apartamento · 2 quartos · 58 m² · Graças</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -10803,12 +10799,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>5500.0</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -10823,7 +10819,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>5500.0</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -10833,12 +10829,12 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>94.83</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -10853,22 +10849,22 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>https://www.rogeriocorretor.com/imovel/casa-4-quartos-torre-recife-90m2-code-736</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-tem-58-metros-quadrados-com-2-quartos-em-gracas-recife-pe-1516171399</t>
         </is>
       </c>
     </row>
@@ -10876,30 +10872,30 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>OLX Imóveis</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 145 m² · Casa Caiada</t>
+          <t>Apartamento · 4 quartos · 182 m² · Aflitos</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Avenida Ministro Marcos Freire</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>5501.0</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -10914,7 +10910,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>5501.0</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -10924,17 +10920,17 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -10944,22 +10940,22 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-145m2-aluguel-RS4500-id-2912449937/?source=ranking%2Crp</t>
+          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-e-venda-tem-182-metros-quadrados-com-4-quartos-em-aflitos-recife-p-1522651723</t>
         </is>
       </c>
     </row>
@@ -10975,27 +10971,27 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 56 m² · 1 vaga · Espinheiro</t>
+          <t>Apartamento · 3 quartos · 87 m² · 2 vagas · Torre</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Rua São Salvador, 200</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>4000.0</t>
+          <t>6000.0</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>850.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -11005,29 +11001,29 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>4850.0</t>
+          <t>6000.0</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>86.61</t>
+          <t>68.97</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="O116" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -11035,7 +11031,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
@@ -11050,462 +11046,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-espinheiro-56m2-RS4000/id-44249374/</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr"/>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda</t>
-        </is>
-      </c>
-      <c r="C117" t="n">
-        <v>1</v>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 118 m² · 2 vagas · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Avenida Ministro Marcos Freire, 2505</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>42.37</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P117" t="inlineStr">
-        <is>
-          <t>118.0</t>
-        </is>
-      </c>
-      <c r="Q117" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R117" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS5000/id-42812242/</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr"/>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda</t>
-        </is>
-      </c>
-      <c r="C118" t="n">
-        <v>1</v>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 148 m² · 1 vaga · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Avenida Ministro Marcos Freire, 3455</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>3500.0</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>1388.0</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>500.0</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>5388.0</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>36.41</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O118" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P118" t="inlineStr">
-        <is>
-          <t>148.0</t>
-        </is>
-      </c>
-      <c r="Q118" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R118" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-148m2-RS3500/id-45673363/</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr"/>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>OLX Imóveis</t>
-        </is>
-      </c>
-      <c r="C119" t="n">
-        <v>1</v>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 55 m² · Espinheiro</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Espinheiro</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>5400.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>5400.0</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>98.18</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O119" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P119" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
-      <c r="Q119" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R119" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-com-2-quartos-no-espinheiro-recife-pe-1536638203</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr"/>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Recife</t>
-        </is>
-      </c>
-      <c r="C120" t="n">
-        <v>1</v>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 87 m² · 2 vagas · Torre</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Torre</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>6000.0</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>6000.0</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>68.97</t>
-        </is>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O120" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P120" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R120" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="S120" t="inlineStr">
-        <is>
           <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-torre-RS6000/id-45626439/</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr"/>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>OLX Imóveis</t>
-        </is>
-      </c>
-      <c r="C121" t="n">
-        <v>1</v>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 57 m² · 1 vaga · Aflitos</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Aflitos</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>850.0</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>150.0</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>6000.0</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>105.26</t>
-        </is>
-      </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O121" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P121" t="inlineStr">
-        <is>
-          <t>57.0</t>
-        </is>
-      </c>
-      <c r="Q121" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R121" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-aflitos-recife-pe-1527554361</t>
         </is>
       </c>
     </row>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -29,18 +29,12 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S102"/>
+  <dimension ref="A1:S94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -546,287 +539,275 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Olinda</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 58 m² · 1 vaga · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Rua Norberto Pessoa, 238</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1300.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1300.0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>22.41</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>58.0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1300/id-46461545/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Olinda</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Apartamento · 1 quarto · 41 m² · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Rua Professor Marculino Botelho, 404</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>OLX Imóveis</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>34.15</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-pe-olinda-bairro-novo-41m2-RS1200/id-45673360/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Âncora Imobiliária</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Graças</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>2524.0</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>2524.0</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>76.48</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/excelente-apartamento-flat-mobiliado-pronto-para-morar-com-aproximadamente-33-metros-quad-1536996786</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 50 m² · Boa Vista</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Boa Vista</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1100.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>250.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>97.38</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1447.38</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>OLX Imóveis</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 1 quarto · 33 m² · Espinheiro</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Espinheiro</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>2800.0</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>2803.0</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>84.94</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-tem-33-metros-quadrados-com-1-quarto-em-espinheiro-recife-pe-1537043906</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>OLX Imóveis</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3900.0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3901.0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>65.02</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>28.95</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-em-casa-caiada-olinda-2-dorms-1-suite-1537040792</t>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>https://ancoraimobiliaria.com.br/imovel/224/apartamento-2-quartos-jose-mariano-boa-vista-recife/</t>
         </is>
       </c>
     </row>
@@ -834,7 +815,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -842,22 +823,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 58 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 57 m² · Arruda</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rua Norberto Pessoa, 238</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1300.0</t>
+          <t>1600.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -872,7 +853,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1300.0</t>
+          <t>1600.0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -882,17 +863,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -902,22 +883,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1300/id-46461545/</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/850301025-80</t>
         </is>
       </c>
     </row>
@@ -933,12 +914,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 41 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rua Professor Marculino Botelho, 404</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -948,42 +929,42 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1200.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1400.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>34.15</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -993,7 +974,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1003,12 +984,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-pe-olinda-bairro-novo-41m2-RS1200/id-45673360/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1700/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -1016,7 +997,7 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1024,7 +1005,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · Boa Vista</t>
+          <t>Apartamento · 1 quarto · 33 m² · Encruzilhada</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1034,42 +1015,42 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1100.0</t>
+          <t>1750.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>97.38</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1447.38</t>
+          <t>1750.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>53.03</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1084,22 +1065,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/224/apartamento-2-quartos-jose-mariano-boa-vista-recife/</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/123-rua-carlos-borromeu-de-frente-para-o-mercado-da-encruzilhada/850471068-78</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1088,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1115,22 +1096,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 57 m² · Arruda</t>
+          <t>Apartamento · 1 quarto · 1625 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Doutor Manoel de Barros Lima</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1600.0</t>
+          <t>1850.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1145,7 +1126,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1600.0</t>
+          <t>1850.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1155,42 +1136,42 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>1625.0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>57.0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/850301025-80</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-1-quarto-bairro-novo-olinda-pe-1625m2-id-2912186542/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1179,7 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1206,57 +1187,57 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 50 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1450.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>405.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>80.96</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1935.96</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>38.72</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1266,22 +1247,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1700/id-45733416/</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/6691/apartamento-2-quartos-santo-amaro-recife/</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1270,7 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1297,47 +1278,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · Encruzilhada</t>
+          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Coronel Alberto Lundgren, 604</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1750.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1750.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>53.03</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1347,7 +1328,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1357,22 +1338,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/123-rua-carlos-borromeu-de-frente-para-o-mercado-da-encruzilhada/850471068-78</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS1800/id-46397377/</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1361,7 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1388,37 +1369,37 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · Santo Amaro</t>
+          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Coronel Alberto Lundgren, 604</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1450.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>405.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>80.96</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1935.96</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1428,17 +1409,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>38.72</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1448,22 +1429,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/6691/apartamento-2-quartos-santo-amaro-recife/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS2000/id-46397376/</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1452,7 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1479,12 +1460,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 65 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua Coronel Alberto Lundgren, 604</t>
+          <t>Rua Professor José Cândido Pessoa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1494,42 +1475,42 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1539,22 +1520,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS1800/id-46397377/</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-bairro-novo-olinda-pe-65m2-id-2897302602/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1543,7 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1570,47 +1551,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 55 m² · 1 vaga · Boa Vista</t>
+          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Professor José Cândido Pessoa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>684.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2477.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>68.81</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1620,7 +1601,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1630,12 +1611,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1645,7 +1626,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-flat-com-vista-do-mar-de-olinda-1536986072</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-720m2-RS1700/id-43805924/</t>
         </is>
       </c>
     </row>
@@ -1661,59 +1642,59 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rua Coronel Alberto Lundgren, 604</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -1721,22 +1702,22 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>30</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS2000/id-46397376/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -1744,55 +1725,55 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rua Professor José Cândido Pessoa</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>684.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2477.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>68.81</t>
+          <t>81.97</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1812,22 +1793,22 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-720m2-RS1700/id-43805924/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-31m2-RS2500/id-45418272/</t>
         </is>
       </c>
     </row>
@@ -1843,52 +1824,52 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Avenida Presidente Getúlio Vargas, 1748</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>683.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2576.0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>71.56</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1903,22 +1884,22 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-36m2-RS1800/id-45673358/</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1907,7 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1934,22 +1915,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 31 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 55 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos De Lima Cavalcante</t>
+          <t>Rua Professor José Cândido Pessoa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1964,7 +1945,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1974,19 +1955,19 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>80.65</t>
+          <t>47.27</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O17" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -1994,22 +1975,22 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-31m2-RS2500/id-45418272/</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-bairro-novo-olinda-pe-55m2-id-2912341217/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2017,7 +1998,7 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2025,12 +2006,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 35 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Avenida Presidente Getúlio Vargas, 1748</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2040,32 +2021,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>683.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2576.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>71.56</t>
+          <t>74.29</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2080,27 +2061,27 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-36m2-RS1800/id-45673358/</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-flat-1-quarto-mobiliado-bairro-novo-olinda-pe-35m2-id-2912188115/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2089,7 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Zap Imóveis</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2116,37 +2097,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · Aflitos</t>
+          <t>Apartamento · 1 quarto · 48 m² · Graças</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Esmeraldino Bandeira</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>1778.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>755.0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2691.0</t>
+          <t>2613.0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2156,17 +2137,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>54.44</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2176,12 +2157,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2191,7 +2172,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-aflitos-recife--pe_33374631</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-1-quarto-gracas-recife-pe-48m2-id-2821571718/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2180,7 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Josinildo Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2222,12 +2203,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2237,12 +2218,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>2691.0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2272,17 +2253,17 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>https://josinildoimoveis.com.br/imovel/apartamento-para-alugar-no-bairro-aflitos-em-recife-pe/PARJI47</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-aflitos-recife--pe_33374631</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2271,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Josinildo Imóveis</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2298,7 +2279,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 126 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · Aflitos</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2308,7 +2289,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2338,7 +2319,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2358,22 +2339,22 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/triplex-3qts-suite-prox-faculdade-de-medicina-olinda-1531200065</t>
+          <t>https://josinildoimoveis.com.br/imovel/apartamento-para-alugar-no-bairro-aflitos-em-recife-pe/PARJI47</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2435,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2472,11 +2453,11 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Zap Imóveis</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2545,7 +2526,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2555,7 +2536,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-flat-1-quarto-mobiliado-tamarineira-recife-pe-47m2-id-2912638648/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/flat-1-quartos-tamarineira-bairros-recife-com-garagem-47m2-aluguel-RS2750-id-2912638648/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2563,7 +2544,7 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2571,7 +2552,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 31 m² · 1 vaga · Paissandu</t>
+          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2581,7 +2562,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paissandu</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2591,7 +2572,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2606,17 +2587,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>23.33</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2631,22 +2612,22 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-no-versatti-residence-service-paissandu-recife-pe-1536936592</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2635,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2662,7 +2643,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Casa Forte</t>
+          <t>Apartamento · 2 quartos · 63 m² · Aflitos</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2672,7 +2653,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Casa Forte</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2702,7 +2683,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2722,22 +2703,22 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-casa-forte-recife-pe-1536936310</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/850251137-34</t>
         </is>
       </c>
     </row>
@@ -2745,25 +2726,25 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 120 m² · Santo Amaro</t>
+          <t>Apartamento · 1 quarto · 40 m² · Ilha do Leite</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Jornalista Trajano Chacon</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Ilha do Leite</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2773,7 +2754,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2788,22 +2769,22 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>23.33</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2813,22 +2794,22 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-120m2-santo-amaro-recife--pe_33323393</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-ilha-do-leite-bairros-recife-com-garagem-40m2-aluguel-RS2800-id-2912104117/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2817,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2844,17 +2825,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 63 m² · Aflitos</t>
+          <t>Apartamento · 3 quartos · 71 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Gildo Branco</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2884,19 +2865,19 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="O27" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -2904,22 +2885,22 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/850251137-34</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-com-piscina-casa-caiada-olinda-pe-71m2-id-2911301943/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2927,7 +2908,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Zap Imóveis</t>
+          <t>Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2935,17 +2916,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 40 m² · Ilha do Leite</t>
+          <t>Apartamento · 1 quarto · 36 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rua Jornalista Trajano Chacon</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ilha do Leite</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2975,7 +2956,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2990,27 +2971,27 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-1-quarto-mobiliado-ilha-do-leite-recife-pe-40m2-id-2912104117/?source=ranking%2Crp</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-1-quarto-mobiliado-casa-caiada-olinda-pe-36m2-id-2705654338/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3018,7 +2999,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3026,17 +3007,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 31 m² · 1 vaga · Parnamirim</t>
+          <t>Apartamento · 3 quartos · 71 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rua Condado, Nº 50</t>
+          <t>Rua Gildo Branco</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3056,7 +3037,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2851.0</t>
+          <t>2850.0</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3066,42 +3047,42 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>91.97</t>
+          <t>40.14</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-31m2-RS2850/id-45010491/</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-com-piscina-casa-caiada-olinda-pe-71m2-id-2911876830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3109,35 +3090,35 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CTI Imobiliária, Chaves na Mão Recife</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 45 m² · 1 vaga · Torre</t>
+          <t>Apartamento · 1 quarto · 31 m² · 1 vaga · Parnamirim</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rua José De Holanda, 854</t>
+          <t>Rua Condado, Nº 50</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2850.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>380.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3147,27 +3128,27 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2880.0</t>
+          <t>2851.0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>91.97</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3177,22 +3158,22 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-torre-recife-pe/1353</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-31m2-RS2850/id-45010491/</t>
         </is>
       </c>
     </row>
@@ -3200,35 +3181,35 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>CTI Imobiliária, Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Espinheiro</t>
+          <t>Apartamento · 2 quartos · 45 m² · 1 vaga · Torre</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua José De Holanda, 854</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2900.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>380.0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3238,27 +3219,27 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2900.0</t>
+          <t>2880.0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3268,22 +3249,22 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-espinheiro-recife-pe-1536936362</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-torre-recife-pe/1353</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3345,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3455,7 +3436,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>59</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3473,20 +3454,20 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, OLX Imóveis</t>
+          <t>Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 42 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa Monteiro, 93</t>
+          <t>Rua Ulisses Tenório de Albuquerque</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3496,32 +3477,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1674.0</t>
+          <t>2998.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1178.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>295.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2999.5</t>
+          <t>2998.0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>71.38</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3541,22 +3522,22 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1822/id-45585830/</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-casa-caiada-olinda-pe-42m2-id-2911376544/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3637,7 +3618,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3728,7 +3709,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3746,20 +3727,20 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, OLX Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 42 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Avenida Doutor José Augusto Moreira, 900</t>
+          <t>Rua Otaviano Pessoa Monteiro, 93</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3769,44 +3750,44 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
+          <t>1822.0</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>1178.0</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
           <t>3000.0</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>32.26</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O37" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -3814,12 +3795,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3829,7 +3810,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-RS3000/id-44380568/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1822/id-45585830/</t>
         </is>
       </c>
     </row>
@@ -3837,7 +3818,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3845,17 +3826,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 37 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 1 quarto · 42 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rua Do Futuro, 20</t>
+          <t>Avenida Doutor José Augusto Moreira, 900</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3885,7 +3866,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>81.08</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3905,22 +3886,22 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-37m2-RS3000/id-44879310/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-RS3000/id-44380568/</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3909,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3936,17 +3917,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Parnamirim</t>
+          <t>Apartamento · 1 quarto · 37 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Do Futuro, 20</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3976,7 +3957,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>81.08</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3986,7 +3967,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3996,22 +3977,22 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-parnamirim-recife-pe-1536936955</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-37m2-RS3000/id-44879310/</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4000,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -4027,7 +4008,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · 1 vaga · Parnamirim</t>
+          <t>Apartamento · 1 quarto · 33 m² · Graças</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4037,22 +4018,22 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>400.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4067,7 +4048,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4087,22 +4068,22 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-no-costa-do-sol-parnamirim-recife-pe-1536936608</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-1-quarto-alugar-33m2-gracas-recife--pe_33286759</t>
         </is>
       </c>
     </row>
@@ -4110,25 +4091,25 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Casa Forte</t>
+          <t>Apartamento · 1 quarto · 35 m² · Rosarinho</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Engenheiro Sampaio</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Casa Forte</t>
+          <t>Rosarinho</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4158,7 +4139,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4168,32 +4149,32 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-casa-forte-recife-pe-1536936505</t>
+          <t>https://www.vivareal.com.br/imovel/flat-1-quartos-rosarinho-bairros-recife-com-garagem-35m2-aluguel-RS3000-id-2912109324/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4182,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -4209,17 +4190,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Jaqueira</t>
+          <t>Apartamento · 2 quartos · 62 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Otaviano Pessoa Monteiro</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Jaqueira</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4249,17 +4230,17 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>48.39</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4269,22 +4250,22 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-no-castello-de-ferrara-jaqueira-recife-pe-1536936460</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-com-cozinha-casa-caiada-olinda-pe-62m2-id-2911451041/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4292,25 +4273,25 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>OLX Imóveis, Zap Imóveis</t>
+          <t>Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · 1 vaga · Rosarinho</t>
+          <t>Apartamento · 3 quartos · 60 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rua Engenheiro Sampaio</t>
+          <t>Rua Professor Francisco Xavier Paes Barreto</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosarinho</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4340,17 +4321,17 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4360,12 +4341,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4375,7 +4356,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-rosarinho-recife-pe-1536936336</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-mobiliado-casa-caiada-olinda-pe-60m2-id-2912144534/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4364,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Josinildo Imóveis</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -4391,7 +4372,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · Graças</t>
+          <t>Apartamento · 2 quartos · 42 m² · Torre</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4401,17 +4382,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4421,22 +4402,22 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4451,22 +4432,22 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-1-quarto-alugar-33m2-gracas-recife--pe_33286759</t>
+          <t>https://josinildoimoveis.com.br/imovel/edf-green-life-torre/PARJI03</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4455,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Josinildo Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -4482,22 +4463,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 42 m² · Torre</t>
+          <t>Apartamento · 1 quarto · 34 m² · 1 vaga · Paissandu</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Estácio Coimbra, 171</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Paissandu</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>3100.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4512,7 +4493,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>3100.0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4522,17 +4503,17 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>91.18</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4542,22 +4523,22 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>https://josinildoimoveis.com.br/imovel/edf-green-life-torre/PARJI03</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-paissandu-RS3100/id-42651969/</t>
         </is>
       </c>
     </row>
@@ -4565,7 +4546,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Zap Imóveis</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4573,17 +4554,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 34 m² · 1 vaga · Paissandu</t>
+          <t>Apartamento · 3 quartos · 80 m² · Derby</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rua Estácio Coimbra, 171</t>
+          <t>Rua Guilherme Pinto</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Paissandu</t>
+          <t>Derby</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4613,17 +4594,17 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>91.18</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4633,22 +4614,22 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-paissandu-RS3100/id-42651969/</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-derby-recife-pe-80m2-id-2901500302/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4656,7 +4637,7 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Zap Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4664,22 +4645,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Derby</t>
+          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rua Guilherme Pinto</t>
+          <t>Rua Amélia, 623</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>3100.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4694,7 +4675,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>3100.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4704,17 +4685,17 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4724,22 +4705,22 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-derby-recife-pe-80m2-id-2901500302/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-RS3200/id-45197779/</t>
         </is>
       </c>
     </row>
@@ -4747,25 +4728,25 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife, OLX Imóveis</t>
+          <t>Newville, Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 2 quartos · 52 m² · Torre</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rua Amélia, 623</t>
+          <t>Rua José de Holanda</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4795,19 +4776,19 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O48" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -4815,22 +4796,22 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-RS3200/id-45197779/</t>
+          <t>https://newville.com.br/imovel/apartamento_2_quartos--torre--recife--pe--locacao--cod-6391</t>
         </is>
       </c>
     </row>
@@ -4838,25 +4819,25 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Newville, Zap Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 52 m² · Torre</t>
+          <t>Apartamento · 1 quarto · 38 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rua José de Holanda</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4886,17 +4867,17 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4906,22 +4887,22 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>https://newville.com.br/imovel/apartamento_2_quartos--torre--recife--pe--locacao--cod-6391</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-1-quarto-alugar-38m2-boa-vista-recife--pe_33378812</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4910,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -4937,17 +4918,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 38 m² · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4977,17 +4958,17 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4997,22 +4978,22 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-1-quarto-alugar-38m2-boa-vista-recife--pe_33378812</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-mobiliado-casa-caiada-olinda-pe-60m2-id-2686319323/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5001,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -5028,22 +5009,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 66 m² · 1 vaga · Campo Grande</t>
+          <t>Apartamento · 2 quartos · 57 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rua Barão De Vera Cruz</t>
+          <t>Rua Pereira Simões</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Campo Grande</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5058,7 +5039,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5068,42 +5049,42 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>56.14</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-campo-grande-79m2-RS3300/id-44353442/</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-mobiliado-bairro-novo-olinda-pe-57m2-id-2901326206/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5092,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -5119,22 +5100,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 48 m² · 1 vaga · Torre</t>
+          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rua José De Holanda</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5149,7 +5130,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5159,7 +5140,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>68.75</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5169,7 +5150,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5179,22 +5160,22 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-RS3300/id-35751827/</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-mobiliado-casa-caiada-olinda-pe-60m2-id-2906163316/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5183,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -5210,22 +5191,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Casa Forte</t>
+          <t>Apartamento · 3 quartos · 88 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rua Lemos Torres, 147</t>
+          <t>Rua Otaviano Pessoa Monteiro</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Casa Forte</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5240,7 +5221,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>3301.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5250,12 +5231,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>60.02</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -5270,22 +5251,22 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-forte-55m2-RS3300/id-41878758/</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-com-interfone-casa-caiada-olinda-pe-88m2-id-2911479216/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5293,7 +5274,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -5301,22 +5282,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 95 m² · 1 vaga · Aflitos</t>
+          <t>Apartamento · 3 quartos · 66 m² · 1 vaga · Campo Grande</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Barão De Vera Cruz</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Campo Grande</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>3400.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5331,7 +5312,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>3400.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5341,7 +5322,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>35.79</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5351,7 +5332,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5361,12 +5342,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5376,7 +5357,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/edf-araras-1532381063</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-campo-grande-79m2-RS3300/id-44353442/</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5365,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -5392,22 +5373,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 57 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 48 m² · 1 vaga · Torre</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rua Francisco Ambrósio De Barros Leite, 1225</t>
+          <t>Rua José De Holanda</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5422,7 +5403,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5432,7 +5413,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>68.75</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5442,7 +5423,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5452,22 +5433,22 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-RS3500/id-42986293/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-RS3300/id-35751827/</t>
         </is>
       </c>
     </row>
@@ -5475,7 +5456,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -5483,22 +5464,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 59 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Casa Forte</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rua Pereira Simões, 1529 - 2</t>
+          <t>Rua Lemos Torres, 147</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Forte</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5513,7 +5494,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3301.0</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5523,7 +5504,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>59.32</t>
+          <t>60.02</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5533,7 +5514,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5543,7 +5524,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -5553,12 +5534,12 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-59m2-RS3500/id-45711136/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-forte-55m2-RS3300/id-41878758/</t>
         </is>
       </c>
     </row>
@@ -5566,7 +5547,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -5574,17 +5555,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 39 m² · 1 vaga · Santana</t>
+          <t>Apartamento · 2 quartos · 57 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rua Samuel Farias, 70</t>
+          <t>Rua Francisco Ambrósio De Barros Leite, 1225</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Santana</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5614,19 +5595,19 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>89.74</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O57" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -5634,22 +5615,22 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-santana-RS3500/id-46556867/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-RS3500/id-42986293/</t>
         </is>
       </c>
     </row>
@@ -5657,7 +5638,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -5665,17 +5646,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 59 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rua Dom Bosco, 1297</t>
+          <t>Rua Pereira Simões, 1529 - 2</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5705,17 +5686,17 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>116.67</t>
+          <t>59.32</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5725,22 +5706,22 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-boa-vista-RS3500/id-45835639/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-59m2-RS3500/id-45711136/</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5729,7 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -5756,17 +5737,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Jaqueira</t>
+          <t>Apartamento · 1 quarto · 39 m² · 1 vaga · Santana</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Samuel Farias, 70</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Jaqueira</t>
+          <t>Santana</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5796,7 +5777,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>116.67</t>
+          <t>89.74</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5806,7 +5787,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5816,22 +5797,22 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-no-golden-jaqueira-home-service-jaqueira-recife-pe-1536936366</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-santana-RS3500/id-46556867/</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5820,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -5847,17 +5828,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · Torre</t>
+          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Boa Vista</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Dom Bosco, 1297</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5887,17 +5868,17 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>116.67</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5907,12 +5888,12 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5922,7 +5903,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-77m2-torre-recife--pe_33379670</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-boa-vista-RS3500/id-45835639/</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5919,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 82 m² · Casa Forte</t>
+          <t>Apartamento · 3 quartos · 77 m² · Torre</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5948,7 +5929,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Casa Forte</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5958,7 +5939,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5973,17 +5954,17 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>42.68</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -5998,22 +5979,22 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-82m2-casa-forte-recife--pe_33364920</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-77m2-torre-recife--pe_33379670</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6010,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · Tamarineira</t>
+          <t>Apartamento · 2 quartos · 82 m² · Casa Forte</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6039,7 +6020,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tamarineira</t>
+          <t>Casa Forte</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -6069,7 +6050,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>42.68</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6089,12 +6070,12 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -6104,7 +6085,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-70m2-tamarineira-recife--pe_33364198</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-82m2-casa-forte-recife--pe_33364920</t>
         </is>
       </c>
     </row>
@@ -6112,7 +6093,7 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Rogério Corretor</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -6120,7 +6101,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 34 m² · Graças</t>
+          <t>Apartamento · 2 quartos · 70 m² · Tamarineira</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6130,7 +6111,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Tamarineira</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -6140,7 +6121,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6155,17 +6136,17 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>102.94</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -6180,12 +6161,12 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -6195,7 +6176,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>https://www.rogeriocorretor.com/imovel/apartamento-1-quarto-gracas-recife-1-vaga-34m2-code-726</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-70m2-tamarineira-recife--pe_33364198</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6184,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CTI Imobiliária</t>
+          <t>Rogério Corretor</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -6211,7 +6192,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 44 m² · Boa Vista</t>
+          <t>Apartamento · 1 quarto · 34 m² · Graças</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6221,42 +6202,42 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>553.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>3527.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>80.16</t>
+          <t>102.94</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -6271,22 +6252,22 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6519</t>
+          <t>https://www.rogeriocorretor.com/imovel/apartamento-1-quarto-gracas-recife-1-vaga-34m2-code-726</t>
         </is>
       </c>
     </row>
@@ -6294,30 +6275,30 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 51 m² · Torre</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos De Lima Cavalcante, 60</t>
+          <t>Rua dos Operários</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>3527.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6332,7 +6313,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>3527.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6342,7 +6323,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>80.16</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6352,7 +6333,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -6362,22 +6343,22 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-44m2-RS3527/id-46693013/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-torre-bairros-recife-com-garagem-51m2-aluguel-RS3500-id-2912459623/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -6385,30 +6366,30 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 86 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 2 quartos · 51 m² · Torre</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua dos Operários</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6423,7 +6404,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6433,32 +6414,32 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6468,7 +6449,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-no-edf-rainha-santa-isabel-gracas-recife-pe-1536937008</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-torre-bairros-recife-com-garagem-51m2-aluguel-RS3500-id-2912474451/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6457,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -6484,22 +6465,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 52 m² · 1 vaga · Torre</t>
+          <t>Apartamento · 4 quartos · 130 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Ministro Marcos Freire</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6514,7 +6495,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6524,17 +6505,17 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>26.92</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6544,22 +6525,22 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-no-engenho-capibaribe-torre-recife-pe-1536936521</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-4-quartos-casa-caiada-olinda-pe-130m2-id-2911955918/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -6567,30 +6548,30 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 3 quartos · 90 m² · Derby</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Guilherme Pinto</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Derby</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3503.0</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6605,7 +6586,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3503.0</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6615,34 +6596,34 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>109.09</t>
+          <t>38.92</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="R68" t="inlineStr">
         <is>
           <t>2026-09-19</t>
@@ -6650,7 +6631,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-vender-e-alugar-no-maria-zilda-gracas-recife-pe-1536936332</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-derby-bairros-recife-com-garagem-90m2-aluguel-RS3503-id-2912537316/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -6658,7 +6639,7 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>CTI Imobiliária</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -6666,57 +6647,57 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 34 m² · 1 vaga · Parnamirim</t>
+          <t>Apartamento · 2 quartos · 44 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Avenida Parnamirim, 375</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>553.0</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>174.0</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>3601.0</t>
+          <t>3527.0</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>105.91</t>
+          <t>80.16</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6726,22 +6707,22 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-34m2-RS3600/id-38113683/</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6519</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6730,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -6757,47 +6738,47 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 56 m² · 1 vaga · Torreão</t>
+          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rua Cândido Lacerda, 221</t>
+          <t>Avenida Governador Carlos De Lima Cavalcante, 60</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Torreão</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3527.0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>3700.0</t>
+          <t>3527.0</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>66.07</t>
+          <t>80.16</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -6807,7 +6788,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6817,22 +6798,22 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torreao-62m2-RS3500/id-46711944/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-44m2-RS3527/id-46693013/</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6821,7 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -6848,22 +6829,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 51 m² · 1 vaga · Casa Forte</t>
+          <t>Apartamento · 1 quarto · 34 m² · 1 vaga · Parnamirim</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Parnamirim, 375</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Casa Forte</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>3700.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6878,7 +6859,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>3700.0</t>
+          <t>3601.0</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -6888,17 +6869,17 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>72.55</t>
+          <t>105.91</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -6908,22 +6889,22 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-casa-forte-recife-pe-1536936540</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-34m2-RS3600/id-38113683/</t>
         </is>
       </c>
     </row>
@@ -6931,7 +6912,7 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -6939,39 +6920,39 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · Encruzilhada</t>
+          <t>Apartamento · 2 quartos · 56 m² · 1 vaga · Torreão</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Cândido Lacerda, 221</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Torreão</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
+          <t>3500.0</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
           <t>3700.0</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>3700.0</t>
-        </is>
-      </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>SIM</t>
@@ -6979,17 +6960,17 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>66.07</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -6999,22 +6980,22 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-encruzilhada-recife--pe_33362592</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torreao-62m2-RS3500/id-46711944/</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7003,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -7030,17 +7011,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 57 m² · 1 vaga · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · Encruzilhada</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rua Dois De Julho, --</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -7050,17 +7031,17 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>3720.0</t>
+          <t>3700.0</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -7070,17 +7051,17 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>65.26</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7090,22 +7071,22 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-santo-amaro-RS3700/id-46659867/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-encruzilhada-recife--pe_33362592</t>
         </is>
       </c>
     </row>
@@ -7113,7 +7094,7 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -7121,37 +7102,37 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 90 m² · Graças</t>
+          <t>Apartamento · 2 quartos · 57 m² · 1 vaga · Santo Amaro</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Dois De Julho, --</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>3700.0</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>1300.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>185.21</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>3785.21</t>
+          <t>3720.0</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7161,17 +7142,17 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>42.06</t>
+          <t>65.26</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7181,22 +7162,22 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/2698/apartamento-3-quartos-san-patrick-graças-recife/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-santo-amaro-RS3700/id-46659867/</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7185,7 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -7212,57 +7193,57 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 43 m² · 1 vaga · Torre</t>
+          <t>Apartamento · 3 quartos · 90 m² · Graças</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rua José De Holanda, 854</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>3800.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1300.0</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>185.21</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>3800.0</t>
+          <t>3785.21</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>88.37</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7272,22 +7253,22 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-43m2-RS3800/id-45247450/</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/2698/apartamento-3-quartos-san-patrick-graças-recife/</t>
         </is>
       </c>
     </row>
@@ -7295,7 +7276,7 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -7303,12 +7284,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
+          <t>Apartamento · 2 quartos · 43 m² · 1 vaga · Torre</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua José De Holanda, 854</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -7343,7 +7324,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>84.44</t>
+          <t>88.37</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7353,7 +7334,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7363,22 +7344,22 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/imovel-para-aluguel-com-45-metros-quadrados-com-2-quartos-em-torre-recife-pe-1536980516</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-43m2-RS3800/id-45247450/</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7367,7 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Zap Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -7394,22 +7375,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 82 m² · Tamarineira</t>
+          <t>Apartamento · 1 quarto · 34 m² · Jaqueira</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Estrada do Arraial</t>
+          <t>Av Parnamirim</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tamarineira</t>
+          <t>Jaqueira</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>3800.0</t>
+          <t>3850.0</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -7424,7 +7405,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>3800.0</t>
+          <t>3850.0</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -7434,12 +7415,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>46.34</t>
+          <t>113.24</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -7454,22 +7435,22 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-com-piscina-tamarineira-recife-pe-82m2-id-2912591518/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-pe-recife-jaqueira-34m2-RS3850/id-45251422/</t>
         </is>
       </c>
     </row>
@@ -7477,30 +7458,30 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 34 m² · Jaqueira</t>
+          <t>Apartamento · 2 quartos · 42 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Av Parnamirim</t>
+          <t>Avenida Governador Carlos de Lima Cavalcanti</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Jaqueira</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>3850.0</t>
+          <t>4000.0</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -7515,7 +7496,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>3850.0</t>
+          <t>4000.0</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -7525,19 +7506,19 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>113.24</t>
+          <t>95.24</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O78" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -7545,22 +7526,22 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-pe-recife-jaqueira-34m2-RS3850/id-45251422/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-derby-bairros-recife-com-garagem-42m2-aluguel-RS4000-id-2912348332/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7549,7 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -7576,59 +7557,59 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Parnamirim</t>
+          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Paissandu</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Estácio Coimbra, 171</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Paissandu</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>3900.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>620.0</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>3900.0</t>
+          <t>4020.0</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>118.18</t>
+          <t>91.36</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="O79" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -7636,22 +7617,22 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-parnamirim-recife-pe-1536936547</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-paissandu-44m2-RS3200/id-42692438/</t>
         </is>
       </c>
     </row>
@@ -7659,30 +7640,30 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Olinda, Rogério Corretor</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 53 m² · 1 vaga · Espinheiro</t>
+          <t>Apartamento · 3 quartos · 145 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Min. Marcos Freire, 3495</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>3973.0</t>
+          <t>4100.0</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -7697,7 +7678,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>3973.0</t>
+          <t>4100.0</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -7707,17 +7688,17 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>74.96</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -7727,22 +7708,22 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-no-edf-porto-design-espinheiro-recife-pe-1536936106</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4100/id-46901493/</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7731,7 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -7758,7 +7739,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · 1 vaga · Aflitos</t>
+          <t>Apartamento · 2 quartos · 43 m² · Casa Amarela</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7768,17 +7749,17 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>3990.0</t>
+          <t>4200.0</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7788,17 +7769,17 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>3990.0</t>
+          <t>4200.0</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>97.67</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7818,22 +7799,22 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-aflitos-recife-pe-1536936368</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-43m2-casa-amarela-recife--pe_33376830</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7822,7 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Rogério Corretor</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -7849,7 +7830,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 72 m² · 1 vaga · Casa Amarela</t>
+          <t>Apartamento · 2 quartos · 80 m² · Aflitos</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7859,17 +7840,17 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>4000.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7879,17 +7860,17 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>4000.0</t>
+          <t>4350.0</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>54.38</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -7909,22 +7890,22 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-para-locacao-casa-amarela-recife-pe-1536936562</t>
+          <t>https://www.rogeriocorretor.com/imovel/apartamento-2-quartos-aflitos-recife-1-vaga-80m2-code-695</t>
         </is>
       </c>
     </row>
@@ -7932,7 +7913,7 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Zap Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -7940,27 +7921,27 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 42 m² · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcanti</t>
+          <t>Avenida Governador Carlos De Lima Cavalcante</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>4000.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1195.0</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7970,17 +7951,17 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>4000.0</t>
+          <t>4395.0</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>95.24</t>
+          <t>79.91</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -8000,22 +7981,22 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-com-piscina-derby-recife-pe-42m2-id-2912348332/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-55m2-RS3200/id-46174975/</t>
         </is>
       </c>
     </row>
@@ -8023,67 +8004,67 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Paissandu</t>
+          <t>Apartamento · 3 quartos · 80 m² · Casa Amarela</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Rua Estácio Coimbra, 171</t>
+          <t>Rua Arnoldo Magalhães</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Paissandu</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>4400.0</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>620.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>4020.0</t>
+          <t>4400.0</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>91.36</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O84" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -8091,22 +8072,22 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-paissandu-44m2-RS3200/id-42692438/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-amarela-bairros-recife-com-garagem-80m2-aluguel-RS4400-id-2912439916/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -8114,20 +8095,20 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Rogério Corretor</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 145 m² · 2 vagas · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 98 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Avenida Min. Marcos Freire, 3495</t>
+          <t>Avenida Ministro Marcos Freire, 3291</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -8137,7 +8118,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>4100.0</t>
+          <t>4499.0</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -8152,7 +8133,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>4100.0</t>
+          <t>4499.0</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -8162,7 +8143,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>45.91</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -8182,22 +8163,22 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4100/id-46901493/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4499/id-46461488/</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8186,7 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -8213,27 +8194,27 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 43 m² · Casa Amarela</t>
+          <t>Apartamento · 3 quartos · 85 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Ministro Marcos Freire</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>4200.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8243,27 +8224,27 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>4200.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>97.67</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -8273,22 +8254,22 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-43m2-casa-amarela-recife--pe_33376830</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-110m2-RS4500/id-42417501/</t>
         </is>
       </c>
     </row>
@@ -8296,7 +8277,7 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -8304,22 +8285,22 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 85 m² · Espinheiro</t>
+          <t>Apartamento · 3 quartos · 97 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Ministro Marcos Freire, 3291</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>4300.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -8334,7 +8315,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>4300.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -8344,17 +8325,17 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>50.59</t>
+          <t>46.39</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -8364,22 +8345,22 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/alugo-otimo-apartamento-com-2-quartos-no-bairro-do-espinheiro-recife-1529010380</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4500/id-46421413/</t>
         </is>
       </c>
     </row>
@@ -8395,7 +8376,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Aflitos</t>
+          <t>Apartamento · 4 quartos · 90 m² · Torre</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8405,17 +8386,17 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8425,22 +8406,22 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>4350.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>54.38</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -8455,12 +8436,12 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -8470,7 +8451,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>https://www.rogeriocorretor.com/imovel/apartamento-2-quartos-aflitos-recife-1-vaga-80m2-code-695</t>
+          <t>https://www.rogeriocorretor.com/imovel/casa-4-quartos-torre-recife-90m2-code-736</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8459,7 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -8486,27 +8467,27 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 56 m² · 1 vaga · Espinheiro</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos De Lima Cavalcante</t>
+          <t>Rua São Salvador, 200</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>4000.0</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1195.0</t>
+          <t>850.0</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8516,7 +8497,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>4395.0</t>
+          <t>4850.0</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -8526,7 +8507,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>79.91</t>
+          <t>86.61</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -8536,7 +8517,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -8546,22 +8527,22 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-55m2-RS3200/id-46174975/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-espinheiro-56m2-RS4000/id-44249374/</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8550,7 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Zap Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -8577,22 +8558,22 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 80 m² · Casa Amarela</t>
+          <t>Apartamento · 3 quartos · 118 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Rua Arnoldo Magalhães</t>
+          <t>Avenida Ministro Marcos Freire, 2505</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>4400.0</t>
+          <t>5000.0</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -8607,7 +8588,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>4400.0</t>
+          <t>5000.0</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -8617,7 +8598,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>42.37</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -8637,22 +8618,22 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-com-piscina-casa-amarela-recife-pe-80m2-id-2912439916/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS5000/id-42812242/</t>
         </is>
       </c>
     </row>
@@ -8660,30 +8641,30 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 98 m² · 2 vagas · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 77 m² · Casa Amarela</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Avenida Ministro Marcos Freire, 3291</t>
+          <t>Rua Guimarães Peixoto</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>4499.0</t>
+          <t>5000.0</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -8698,7 +8679,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>4499.0</t>
+          <t>5000.0</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -8708,7 +8689,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>45.91</t>
+          <t>64.94</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -8728,22 +8709,22 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4499/id-46461488/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-amarela-bairros-recife-com-garagem-77m2-aluguel-RS5000-id-2912641830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -8759,12 +8740,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · 2 vagas · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 148 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Avenida Ministro Marcos Freire</t>
+          <t>Avenida Ministro Marcos Freire, 3455</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -8774,42 +8755,42 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1388.0</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>500.0</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>5388.0</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>52.94</t>
+          <t>36.41</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -8819,12 +8800,12 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8834,7 +8815,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-110m2-RS4500/id-42417501/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-148m2-RS3500/id-45673363/</t>
         </is>
       </c>
     </row>
@@ -8842,30 +8823,30 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, OLX Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 97 m² · 2 vagas · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 89 m² · Torre</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Avenida Ministro Marcos Freire, 3291</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>5500.0</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -8880,7 +8861,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>5500.0</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -8890,7 +8871,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>46.39</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -8900,7 +8881,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -8910,22 +8891,22 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4500/id-46421413/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-89m2-torre-recife--pe_33386591</t>
         </is>
       </c>
     </row>
@@ -8933,7 +8914,7 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>OLX Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -8941,7 +8922,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Apartamento · 4 quartos · 115 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 87 m² · 2 vagas · Torre</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8951,12 +8932,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>6000.0</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -8971,7 +8952,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>6000.0</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -8981,17 +8962,17 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>68.97</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -9001,748 +8982,20 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>115.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/apartamento-4-quartos-2-suites-115m-vista-mar-casa-caiada-1513769273</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr"/>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Rogério Corretor</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>1</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Apartamento · 4 quartos · 90 m² · Torre</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Torre</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>https://www.rogeriocorretor.com/imovel/casa-4-quartos-torre-recife-90m2-code-736</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr"/>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Zap Imóveis</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>1</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 135 m² · Aflitos</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Rua Conselheiro Portela</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Aflitos</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>33.33</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>135.0</t>
-        </is>
-      </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R96" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-com-ambientes-integrados-aflitos-recife-pe-135m2-id-2912435214/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr"/>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Recife, OLX Imóveis</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>2</v>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 56 m² · 1 vaga · Espinheiro</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Rua São Salvador, 200</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Espinheiro</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>4400.0</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>850.0</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>4825.0</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>86.94</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>55.5</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R97" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-espinheiro-56m2-RS4000/id-44249374/</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr"/>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>OLX Imóveis</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>1</v>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Apartamento · 1 quarto · 100 m² · 1 vaga · Graças</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Graças</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>4800.0</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>98.0</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>4898.0</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>48.98</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R98" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>https://pe.olx.com.br/grande-recife/imoveis/maria-bernardete-imovel-comercial-terreo-edf-maria-bernadete-de-frente-a-pallato-100m-1534312974</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr"/>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda, OLX Imóveis</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>2</v>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 116 m² · 2 vagas · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Avenida Ministro Marcos Freire, 2505</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>42.92</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>116.5</t>
-        </is>
-      </c>
-      <c r="Q99" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R99" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS5000/id-42812242/</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr"/>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>1</v>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 148 m² · 1 vaga · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Avenida Ministro Marcos Freire, 3455</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>3500.0</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>1388.0</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>500.0</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>5388.0</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>36.41</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>148.0</t>
-        </is>
-      </c>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R100" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-148m2-RS3500/id-45673363/</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr"/>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Portal CRECI Brasil</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>1</v>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 89 m² · Torre</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Torre</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>5500.0</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>5500.0</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>61.8</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>89.0</t>
-        </is>
-      </c>
-      <c r="Q101" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R101" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-89m2-torre-recife--pe_33386591</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr"/>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Recife</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>1</v>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 87 m² · 2 vagas · Torre</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Torre</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>6000.0</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>6000.0</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>68.97</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
-      <c r="Q102" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R102" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="S102" t="inlineStr">
         <is>
           <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-torre-RS6000/id-45626439/</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S98"/>
+  <dimension ref="A1:S75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -553,25 +553,25 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · Rosarinho</t>
+          <t>Apartamento · 1 quarto · 43 m² · Santana</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Rua Engenheiro Sampaio</t>
+          <t>Rua Nestor Silva</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Rosarinho</t>
+          <t>Santana</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -581,153 +581,157 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3020.0</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>70.23</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>43.0</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-santana-bairros-recife-com-garagem-43m2-aluguel-RS3000-id-2913452276/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>REMAX Recife e Olinda</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 51 m² · Aflitos</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Aflitos</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>3990.0</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>3990.0</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>85.71</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>35.0</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>78.24</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>51.0</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/flat-1-quartos-rosarinho-bairros-recife-com-garagem-35m2-aluguel-RS3000-id-2913427019/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 58 m² · 1 vaga · Bairro Novo</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Rua Norberto Pessoa, 238</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Bairro Novo</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1300.0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>1300.0</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>22.41</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>58.0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1300/id-46461545/</t>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/307-manuel-de-carvalho-edificio-praca-das-cerejeiras/850721013-37</t>
         </is>
       </c>
     </row>
@@ -743,12 +747,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 41 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 58 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rua Professor Marculino Botelho, 404</t>
+          <t>Rua Norberto Pessoa, 238</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -758,44 +762,44 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1200.0</t>
+          <t>1300.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1400.0</t>
+          <t>1300.0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>34.15</t>
+          <t>22.41</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O4" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -803,7 +807,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -813,12 +817,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-pe-olinda-bairro-novo-41m2-RS1200/id-45673360/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1300/id-46461545/</t>
         </is>
       </c>
     </row>
@@ -826,7 +830,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -834,37 +838,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · Boa Vista</t>
+          <t>Apartamento · 1 quarto · 41 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Professor Marculino Botelho, 404</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1100.0</t>
+          <t>1200.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>97.38</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1447.38</t>
+          <t>1400.0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -874,17 +878,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>34.15</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -894,12 +898,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -909,7 +913,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/224/apartamento-2-quartos-jose-mariano-boa-vista-recife/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-pe-olinda-bairro-novo-41m2-RS1200/id-45673360/</t>
         </is>
       </c>
     </row>
@@ -917,65 +921,65 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 50 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rua Carlos Nigro</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1499.0</t>
+          <t>1100.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>97.38</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1499.0</t>
+          <t>1447.38</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>49.97</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -985,22 +989,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-30m2-aluguel-RS1499-id-2912697216/?source=ranking%2Crp</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/224/apartamento-2-quartos-jose-mariano-boa-vista-recife/</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1012,7 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1016,7 +1020,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 57 m² · Arruda</t>
+          <t>Apartamento · 1 quarto · 40 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1026,42 +1030,42 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1600.0</t>
+          <t>1100.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>505.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1600.0</t>
+          <t>1677.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1076,22 +1080,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/850301025-80</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/2553/apartamento-1-quarto-arpege-boa-vista-recife/</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1103,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1107,57 +1111,57 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 40 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1100.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>505.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1677.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1167,22 +1171,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/2553/apartamento-1-quarto-arpege-boa-vista-recife/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1700/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1194,7 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1198,57 +1202,57 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 50 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1450.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>405.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>80.96</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1935.96</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>38.72</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1258,22 +1262,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1700/id-45733416/</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/6691/apartamento-2-quartos-santo-amaro-recife/</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1285,7 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1289,47 +1293,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · Encruzilhada</t>
+          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Coronel Alberto Lundgren, 604</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1750.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1750.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>53.03</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1339,7 +1343,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1349,22 +1353,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/123-rua-carlos-borromeu-de-frente-para-o-mercado-da-encruzilhada/850471068-78</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS1800/id-46397377/</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1376,7 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1380,12 +1384,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 1625 m² · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rua Doutor Manoel de Barros Lima</t>
+          <t>Rua Coronel Alberto Lundgren, 604</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1395,32 +1399,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1850.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1850.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1440,22 +1444,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1625.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-1-quarto-bairro-novo-olinda-pe-1625m2-id-2912186542/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS2000/id-46397376/</t>
         </is>
       </c>
     </row>
@@ -1463,55 +1467,55 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua Carlos Nigro</t>
+          <t>Rua Professor José Cândido Pessoa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1900.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>684.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1900.0</t>
+          <t>2477.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>52.78</t>
+          <t>68.81</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1536,17 +1540,17 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-36m2-aluguel-RS1900-id-2912776917/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-720m2-RS1700/id-43805924/</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1558,7 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1562,57 +1566,57 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1450.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>405.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>80.96</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1935.96</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>38.72</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1622,22 +1626,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>34</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/6691/apartamento-2-quartos-santo-amaro-recife/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -1645,45 +1649,45 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 49 m² · Espinheiro</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rua Coronel Alberto Lundgren</t>
+          <t>Rua Da Hora, 235</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>500.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1693,19 +1697,19 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -1713,22 +1717,22 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS1800/id-46397377/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-pe-recife-espinheiro-49m2-RS2000/id-44279997/</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1740,7 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1744,37 +1748,37 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Avenida Doutor José Augusto Moreira</t>
+          <t>Avenida Presidente Getúlio Vargas, 1748</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>683.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2002.0</t>
+          <t>2576.0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1784,12 +1788,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>33.37</t>
+          <t>71.56</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1804,22 +1808,22 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-com-elevador-casa-caiada-olinda-pe-60m2-id-2910983844/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-36m2-RS1800/id-45673358/</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1831,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1835,47 +1839,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 35 m² · Ilha do Leite</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rua Coronel Alberto Lundgren, 604</t>
+          <t>Rua Jornalista Trajano Chacon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Ilha do Leite</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>74.29</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1895,22 +1899,22 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS2000/id-46397376/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-ilha-do-leite-bairros-recife-com-garagem-35m2-aluguel-RS2600-id-2913377274/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1918,35 +1922,35 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · Aflitos</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rua Carlos Nigro</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1956,27 +1960,27 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2691.0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>61.11</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1986,22 +1990,22 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-36m2-aluguel-RS2200-id-2912776533/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-aflitos-recife--pe_33374631</t>
         </is>
       </c>
     </row>
@@ -2009,30 +2013,30 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Josinildo Imóveis</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 65 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 74 m² · Aflitos</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rua Professor José Cândido Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2047,7 +2051,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2057,17 +2061,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>33.85</t>
+          <t>36.49</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2077,7 +2081,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2087,12 +2091,12 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-65m2-aluguel-RS2200-id-2897302602/?source=ranking%2Crp</t>
+          <t>https://josinildoimoveis.com.br/imovel/apartamento-para-alugar-no-bairro-aflitos-em-recife-pe/PARJI47</t>
         </is>
       </c>
     </row>
@@ -2108,82 +2112,82 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rua Professor José Cândido Pessoa</t>
+          <t>Rua Otaviano Pessoa Monteiro, 93</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1526.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>684.0</t>
+          <t>1178.0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2704.0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>29.08</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
           <t>93.0</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2477.0</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>68.81</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>36.0</t>
-        </is>
-      </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-720m2-RS1700/id-43805924/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1526/id-45586419/</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2195,7 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>CTI Imobiliária</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2199,57 +2203,57 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 80 m² · Graças</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>1600.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>953.0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2747.0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>34.34</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2259,22 +2263,22 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>63</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-gracas-recife-pe/6882</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2286,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2290,27 +2294,27 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 49 m² · Espinheiro</t>
+          <t>Apartamento · 1 quarto · 31 m² · Parnamirim</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rua Da Hora, 235</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2850.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>500.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2320,27 +2324,27 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2850.0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>91.94</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2350,22 +2354,22 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-pe-recife-espinheiro-49m2-RS2000/id-44279997/</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/n%C2%BA-50-rua-condado-perto-do-cafe-sao-braz/850091040-261</t>
         </is>
       </c>
     </row>
@@ -2373,25 +2377,25 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>CTI Imobiliária</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 38 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2401,7 +2405,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>380.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2411,52 +2415,52 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2880.0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>65.79</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-38m2-aluguel-RS2500-id-2698090477/?source=ranking%2Crp</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-torre-recife-pe/1353</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2468,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Zap Imóveis Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2472,57 +2476,57 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>380.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>176.42</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2956.42</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2532,22 +2536,22 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-1-quarto-mobiliado-casa-caiada-olinda-pe-30m2-id-2912752809/?source=ranking%2Crp</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/6596/apartamento-2-quartos-torre-recife/</t>
         </is>
       </c>
     </row>
@@ -2563,47 +2567,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 40 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Avenida Presidente Getúlio Vargas, 1748</t>
+          <t>Avenida Governador Carlos De Lima Cavalcante, 2595</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>683.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2576.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>71.56</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2623,12 +2627,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2638,7 +2642,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-36m2-RS1800/id-45673358/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-40m2-RS3000/id-45710865/</t>
         </is>
       </c>
     </row>
@@ -2646,30 +2650,30 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · Ilha do Leite</t>
+          <t>Apartamento · 1 quarto · 42 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rua Jornalista Trajano Chacon</t>
+          <t>Avenida Doutor José Augusto Moreira, 900</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ilha do Leite</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2600.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2684,7 +2688,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2600.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2694,7 +2698,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>74.29</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2714,22 +2718,22 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-ilha-do-leite-bairros-recife-com-garagem-35m2-aluguel-RS2600-id-2913377274/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-RS3000/id-44380568/</t>
         </is>
       </c>
     </row>
@@ -2737,35 +2741,35 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Rua Otaviano Pessoa Monteiro, 93</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2600.0</t>
+          <t>1822.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1178.0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2775,52 +2779,52 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2600.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>74.29</t>
+          <t>32.26</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/flat-1-quartos-bairro-novo-bairros-olinda-com-garagem-35m2-aluguel-RS2600-id-2912188115/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1822/id-45585830/</t>
         </is>
       </c>
     </row>
@@ -2828,30 +2832,30 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 55 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 92 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rua Professor José Cândido Pessoa</t>
+          <t>Avenida Carlos De Lima Cavalcante</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2600.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2866,7 +2870,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2600.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2876,19 +2880,19 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>47.27</t>
+          <t>32.61</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O27" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -2896,22 +2900,22 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-55m2-aluguel-RS2600-id-2912341217/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS3000/id-42437394/</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2923,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2927,37 +2931,37 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · Aflitos</t>
+          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Cardeal Arcoverde, 276</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2332.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>550.0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2691.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2967,17 +2971,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>93.75</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2987,22 +2991,22 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-aflitos-recife--pe_33374631</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS2332/id-46081872/</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3014,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Josinildo Imóveis</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3018,22 +3022,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 74 m² · Aflitos</t>
+          <t>Apartamento · 1 quarto · 35 m² · Rosarinho</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Engenheiro Sampaio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Rosarinho</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3048,7 +3052,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3058,42 +3062,42 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>https://josinildoimoveis.com.br/imovel/apartamento-para-alugar-no-bairro-aflitos-em-recife-pe/PARJI47</t>
+          <t>https://www.vivareal.com.br/imovel/flat-1-quartos-rosarinho-bairros-recife-com-garagem-35m2-aluguel-RS3000-id-2913427019/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3105,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Josinildo Imóveis</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -3109,27 +3113,27 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 42 m² · Torre</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa Monteiro, 93</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1526.0</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1178.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3139,17 +3143,17 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2704.0</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3159,7 +3163,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3169,22 +3173,22 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1526/id-45586419/</t>
+          <t>https://josinildoimoveis.com.br/imovel/edf-green-life-torre/PARJI03</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3196,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CTI Imobiliária</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -3200,12 +3204,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Graças</t>
+          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Amélia, 623</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3215,42 +3219,42 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1600.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>953.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2747.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>34.34</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3260,22 +3264,22 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-gracas-recife-pe/6882</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-RS3200/id-45197779/</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3287,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Newville</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -3291,7 +3295,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 63 m² · Aflitos</t>
+          <t>Apartamento · 2 quartos · 52 m² · Torre</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3301,12 +3305,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3321,7 +3325,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3331,7 +3335,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3351,22 +3355,22 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/850251137-34</t>
+          <t>https://newville.com.br/imovel/apartamento_2_quartos--torre--recife--pe--locacao--cod-6391</t>
         </is>
       </c>
     </row>
@@ -3374,30 +3378,30 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 71 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 38 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rua Gildo Branco</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3412,7 +3416,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3422,17 +3426,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3442,22 +3446,22 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-71m2-aluguel-RS2800-id-2911301943/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-1-quarto-alugar-38m2-boa-vista-recife--pe_33378812</t>
         </is>
       </c>
     </row>
@@ -3465,30 +3469,30 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 40 m² · Santana</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Santana</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3503,7 +3507,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3513,42 +3517,42 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-60m2-aluguel-RS2800-id-2912116616/?source=ranking%2Crp</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/70-rua-samuel-de-farias/850091105-39</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3560,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Viva Real Olinda</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3564,22 +3568,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 35 m² · Encruzilhada</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3594,7 +3598,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3604,7 +3608,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>91.43</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3614,32 +3618,32 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-36m2-aluguel-RS2800-id-2705654338/?source=ranking%2Crp</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/68-rua-engenheiro-sampaio/850701030-102</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3651,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Zap Imóveis Olinda</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3655,22 +3659,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Apartamento · 40 m² · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 37 m² · Espinheiro</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Rua Barão de Itamaracá</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3685,7 +3689,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3695,12 +3699,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>86.49</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3715,22 +3719,22 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-quitinete-com-blindex-casa-caiada-olinda-pe-40m2-id-2910716413/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-espinheiro-bairros-recife-com-garagem-37m2-aluguel-RS3200-id-2913453536/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3742,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Viva Real Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3746,52 +3750,52 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 71 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 70 m² · 1 vaga · Casa Amarela</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rua Gildo Branco</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2850.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>237.0</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2850.0</t>
+          <t>3202.0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>40.14</t>
+          <t>45.74</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3806,22 +3810,22 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-71m2-aluguel-RS2850-id-2911876830/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-amarela-70m2-RS2000/id-43758789/</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3833,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CTI Imobiliária</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3837,27 +3841,27 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
+          <t>Apartamento · 3 quartos · 66 m² · 1 vaga · Campo Grande</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Barão De Vera Cruz</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Campo Grande</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>380.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3867,27 +3871,27 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2880.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3897,12 +3901,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3912,7 +3916,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-torre-recife-pe/1353</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-campo-grande-79m2-RS3300/id-44353442/</t>
         </is>
       </c>
     </row>
@@ -3920,90 +3924,90 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · Aflitos</t>
+          <t>Apartamento · 2 quartos · 65 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rua Samuel Campelo</t>
+          <t>Rua Eduardo De Moraes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2900.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>422.0</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2900.0</t>
+          <t>3317.0</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>82.86</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-aflitos-bairros-recife-com-garagem-35m2-aluguel-RS2900-id-2913410942/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-1038m2-RS2700/id-27611651/</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4023,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
+          <t>Apartamento · 2 quartos · 75 m² · Graças</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4029,27 +4033,27 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>380.0</t>
+          <t>588.0</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>176.42</t>
+          <t>109.04</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2956.42</t>
+          <t>3397.04</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4059,7 +4063,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>45.29</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4079,22 +4083,22 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/6596/apartamento-2-quartos-torre-recife/</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/3178/apartamento-2-quartos-celina-gonçalves-de-oliveira-graças-recife/</t>
         </is>
       </c>
     </row>
@@ -4102,7 +4106,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Viva Real Olinda</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -4110,22 +4114,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 42 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 37 m² · Rosarinho</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rua Ulisses Tenório de Albuquerque</t>
+          <t>Rua Doutor José Maria</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Rosarinho</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2998.0</t>
+          <t>3400.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4140,7 +4144,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2998.0</t>
+          <t>3400.0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4150,12 +4154,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>71.38</t>
+          <t>91.89</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4165,27 +4169,27 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-42m2-aluguel-RS2998-id-2911376544/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-rosarinho-bairros-recife-com-garagem-37m2-aluguel-RS3400-id-2913418918/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4193,7 +4197,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -4201,22 +4205,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 40 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 36 m² · Ilha do Leite</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos De Lima Cavalcante, 2595</t>
+          <t>Rua Jornalista Trajano Chacon</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Ilha do Leite</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3450.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4231,7 +4235,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3450.0</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4241,7 +4245,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>95.83</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4256,27 +4260,27 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-40m2-RS3000/id-45710865/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-ilha-do-leite-bairros-recife-com-garagem-36m2-aluguel-RS3450-id-2913191116/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4292,22 +4296,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 42 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 59 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Avenida Doutor José Augusto Moreira, 900</t>
+          <t>Rua Pereira Simões, 1529 - 2</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4322,7 +4326,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4332,17 +4336,17 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>59.32</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4352,22 +4356,22 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-RS3000/id-44380568/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-59m2-RS3500/id-45711136/</t>
         </is>
       </c>
     </row>
@@ -4383,27 +4387,27 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 57 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa Monteiro, 93</t>
+          <t>Rua Francisco Ambrósio De Barros Leite, 1225</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1822.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1178.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4413,17 +4417,17 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>32.26</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4443,12 +4447,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4458,7 +4462,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1822/id-45585830/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-RS3500/id-42986293/</t>
         </is>
       </c>
     </row>
@@ -4466,7 +4470,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -4474,22 +4478,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 92 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 50 m² · 1 vaga · Torre</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Avenida Carlos De Lima Cavalcante</t>
+          <t>Rua Real Da Torre</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4504,7 +4508,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4514,42 +4518,42 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS3000/id-42437394/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-50m2-RS3500/id-46933917/</t>
         </is>
       </c>
     </row>
@@ -4557,20 +4561,20 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Chaves na Mão Recife, Rogério Corretor</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rua Cardeal Arcoverde, 276</t>
+          <t>Rua Cardeal Arcoverde, 1</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4580,32 +4584,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2332.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>550.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>93.75</t>
+          <t>106.06</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4625,22 +4629,22 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS2332/id-46081872/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS3500/id-45844382/</t>
         </is>
       </c>
     </row>
@@ -4648,35 +4652,35 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 59 m² · Santo Amaro</t>
+          <t>Apartamento · 2 quartos · 70 m² · Tamarineira</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rua Dom Pedro Henrique</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Tamarineira</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4686,52 +4690,52 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>50.85</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-santo-amaro-bairros-recife-com-garagem-59m2-aluguel-RS3000-id-2913400521/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-70m2-tamarineira-recife--pe_33364198</t>
         </is>
       </c>
     </row>
@@ -4739,30 +4743,30 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 68 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 77 m² · Torre</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4777,7 +4781,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4787,17 +4791,17 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>44.12</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4807,22 +4811,22 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-68m2-aluguel-RS3000-id-2913457037/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-77m2-torre-recife--pe_33379670</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4834,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Viva Real Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -4838,27 +4842,27 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 62 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 82 m² · Casa Forte</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa Monteiro</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Casa Forte</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4868,17 +4872,17 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>48.39</t>
+          <t>42.68</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4888,7 +4892,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4898,22 +4902,22 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-62m2-aluguel-RS3000-id-2911451041/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-82m2-casa-forte-recife--pe_33364920</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4925,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Josinildo Imóveis</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -4929,7 +4933,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 42 m² · Torre</t>
+          <t>Apartamento · 3 quartos · 83 m² · Aflitos</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4939,12 +4943,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4959,7 +4963,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4969,12 +4973,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>42.09</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4989,22 +4993,22 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>83.15</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>https://josinildoimoveis.com.br/imovel/edf-green-life-torre/PARJI03</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/850191006-42</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5016,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -5020,82 +5024,82 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 2 quartos · 56 m² · Torreão</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rua Amélia, 623</t>
+          <t>Rua Cândido Lacerda</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Torreão</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3502.0</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>62.54</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>56.0</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-RS3200/id-45197779/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-torreao-bairros-recife-com-garagem-56m2-aluguel-RS3500-id-2913434332/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5103,55 +5107,55 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Newville</t>
+          <t>CTI Imobiliária, Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 52 m² · Torre</t>
+          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Boa Vista</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos De Lima Cavalcanti, 60</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>553.0</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>174.0</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3527.0</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>80.16</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5161,7 +5165,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5171,22 +5175,22 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>https://newville.com.br/imovel/apartamento_2_quartos--torre--recife--pe--locacao--cod-6391</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6519</t>
         </is>
       </c>
     </row>
@@ -5194,7 +5198,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>CTI Imobiliária</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -5202,7 +5206,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 38 m² · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 41 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5217,67 +5221,67 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>550.0</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3542.0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>86.39</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-1-quarto-alugar-38m2-boa-vista-recife--pe_33378812</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6210</t>
         </is>
       </c>
     </row>
@@ -5285,30 +5289,30 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 37 m² · Espinheiro</t>
+          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Parnamirim</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rua Barão de Itamaracá</t>
+          <t>Avenida Parnamirim, 375</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5323,7 +5327,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5333,7 +5337,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>86.49</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5353,22 +5357,22 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-espinheiro-bairros-recife-com-garagem-37m2-aluguel-RS3200-id-2913453536/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-32m2-RS3600/id-41530823/</t>
         </is>
       </c>
     </row>
@@ -5376,35 +5380,35 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 34 m² · 1 vaga · Parnamirim</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Avenida Parnamirim, 375</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>600.0</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5414,52 +5418,52 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>105.88</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3200-id-2906163316/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-55m2-RS3000/id-46882194/</t>
         </is>
       </c>
     </row>
@@ -5467,7 +5471,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Viva Real Olinda</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -5475,22 +5479,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
+          <t>Apartamento · 4 quartos · 120 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Rua Dom Carlos Coelho</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5505,7 +5509,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5515,19 +5519,19 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="O56" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -5535,22 +5539,22 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3200-id-2686319323/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-boa-vista-bairros-recife-com-garagem-120m2-aluguel-RS3600-id-2913416134/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5558,7 +5562,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Zap Imóveis</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -5566,22 +5570,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 32 m² · Paissandu</t>
+          <t>Apartamento · 2 quartos · 51 m² · Aflitos</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rua Estácio Coimbra</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Paissandu</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3699.0</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5596,7 +5600,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3699.0</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5606,17 +5610,17 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>72.53</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5626,22 +5630,22 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-1-quarto-mobiliado-paissandu-recife-pe-32m2-id-2911836585/?source=ranking%2Crp</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/307-rua-manuel-de-carvalho/850701030-101</t>
         </is>
       </c>
     </row>
@@ -5649,7 +5653,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -5657,27 +5661,27 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 57 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · Encruzilhada</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rua Pereira Simões</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3700.0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5687,52 +5691,52 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3700.0</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>56.14</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-mobiliado-bairro-novo-olinda-pe-57m2-id-2901326206/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-encruzilhada-recife--pe_33362592</t>
         </is>
       </c>
     </row>
@@ -5740,7 +5744,7 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -5748,7 +5752,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · 1 vaga · Casa Amarela</t>
+          <t>Apartamento · 3 quartos · Rosarinho</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5758,72 +5762,72 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Rosarinho</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>3800.0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>237.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>3202.0</t>
+          <t>3800.0</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>45.74</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-amarela-70m2-RS2000/id-43758789/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-rosarinho-recife--pe_33388298</t>
         </is>
       </c>
     </row>
@@ -5831,7 +5835,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -5839,22 +5843,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 66 m² · 1 vaga · Campo Grande</t>
+          <t>Apartamento · 2 quartos · 70 m² · Encruzilhada</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rua Barão De Vera Cruz</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Campo Grande</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3800.0</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5869,7 +5873,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3800.0</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5879,17 +5883,17 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>54.29</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5899,22 +5903,22 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-campo-grande-79m2-RS3300/id-44353442/</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/edf-arcadia/850091082-77</t>
         </is>
       </c>
     </row>
@@ -5922,30 +5926,30 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 58 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rua Pereira Simões</t>
+          <t>Rua José de Holanda</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3800.0</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5960,7 +5964,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3800.0</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -5970,7 +5974,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>84.44</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5985,27 +5989,27 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-58m2-aluguel-RS3300-id-2913435980/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-torre-bairros-recife-com-garagem-45m2-aluguel-RS3800-id-2913001614/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6017,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -6021,17 +6025,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 65 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 74 m² · 1 vaga · Aflitos</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rua Eduardo De Moraes</t>
+          <t>Rua Da Angustura, 195</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -6041,17 +6045,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>422.0</t>
+          <t>1200.0</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>3317.0</t>
+          <t>4091.0</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6061,34 +6065,34 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>51.03</t>
+          <t>55.28</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R62" t="inlineStr">
         <is>
           <t>2026-09-22</t>
@@ -6096,7 +6100,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-1038m2-RS2700/id-27611651/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-aflitos-74m2-RS2700/id-46898128/</t>
         </is>
       </c>
     </row>
@@ -6104,65 +6108,65 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Chaves na Mão Olinda, Rogério Corretor</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 75 m² · Graças</t>
+          <t>Apartamento · 3 quartos · 145 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Min. Marcos Freire, 3495</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>4100.0</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>588.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>109.04</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>3397.04</t>
+          <t>4100.0</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>45.29</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6172,22 +6176,22 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/3178/apartamento-2-quartos-celina-gonçalves-de-oliveira-graças-recife/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4100/id-46901493/</t>
         </is>
       </c>
     </row>
@@ -6195,30 +6199,30 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 37 m² · Rosarinho</t>
+          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Aflitos</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rua Doutor José Maria</t>
+          <t>Avenida Conselheiro Rosa E Silva, 801</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosarinho</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>3400.0</t>
+          <t>4141.0</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6233,7 +6237,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>3400.0</t>
+          <t>4142.0</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6243,42 +6247,42 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>91.89</t>
+          <t>75.31</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-rosarinho-bairros-recife-com-garagem-37m2-aluguel-RS3400-id-2913418918/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-aflitos-55m2-RS4141/id-45283901/</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6290,7 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -6294,27 +6298,27 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · Ilha do Leite</t>
+          <t>Apartamento · 2 quartos · 43 m² · Casa Amarela</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rua Jornalista Trajano Chacon</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ilha do Leite</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>3450.0</t>
+          <t>4200.0</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6324,52 +6328,52 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>3450.0</t>
+          <t>4200.0</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>95.83</t>
+          <t>97.67</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-ilha-do-leite-bairros-recife-com-garagem-36m2-aluguel-RS3450-id-2913191116/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-43m2-casa-amarela-recife--pe_33376830</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6381,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -6385,22 +6389,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 59 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 58 m² · Espinheiro</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rua Pereira Simões, 1529 - 2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4200.0</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6415,7 +6419,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4200.0</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6425,7 +6429,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>59.32</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6435,32 +6439,32 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>58.0</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-59m2-RS3500/id-45711136/</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/862-rua-da-hora/850251129-67</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6472,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Rogério Corretor</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -6476,27 +6480,27 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 57 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 80 m² · Aflitos</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rua Francisco Ambrósio De Barros Leite, 1225</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6506,17 +6510,17 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4350.0</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>54.38</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6526,7 +6530,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6536,12 +6540,12 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6551,7 +6555,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-RS3500/id-42986293/</t>
+          <t>https://www.rogeriocorretor.com/imovel/apartamento-2-quartos-aflitos-recife-1-vaga-80m2-code-695</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6563,7 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -6567,27 +6571,27 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · 1 vaga · Torre</t>
+          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rua Real Da Torre</t>
+          <t>Avenida Governador Carlos De Lima Cavalcante</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1195.0</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6597,17 +6601,17 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4395.0</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>79.91</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -6627,22 +6631,22 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-50m2-RS3500/id-46933917/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-55m2-RS3200/id-46174975/</t>
         </is>
       </c>
     </row>
@@ -6650,30 +6654,30 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife, Rogério Corretor</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 3 quartos · 85 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rua Cardeal Arcoverde, 1</t>
+          <t>Avenida Ministro Marcos Freire</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6688,7 +6692,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6698,17 +6702,17 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>106.06</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6718,12 +6722,12 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6733,7 +6737,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS3500/id-45844382/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-110m2-RS4500/id-42417501/</t>
         </is>
       </c>
     </row>
@@ -6741,7 +6745,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -6749,27 +6753,27 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · Tamarineira</t>
+          <t>Apartamento · 3 quartos · 97 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Ministro Marcos Freire, 3291</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tamarineira</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6779,27 +6783,27 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>46.39</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6809,12 +6813,12 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6824,7 +6828,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-70m2-tamarineira-recife--pe_33364198</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4500/id-46421413/</t>
         </is>
       </c>
     </row>
@@ -6832,7 +6836,7 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -6840,22 +6844,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · Torre</t>
+          <t>Apartamento · 2 quartos · 56 m² · 1 vaga · Espinheiro</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua São Salvador, 200</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6870,7 +6874,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -6880,17 +6884,17 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>80.36</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -6900,22 +6904,22 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-77m2-torre-recife--pe_33379670</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-espinheiro-70m2-RS4500/id-46923849/</t>
         </is>
       </c>
     </row>
@@ -6923,7 +6927,7 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Rogério Corretor</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -6931,7 +6935,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 82 m² · Casa Forte</t>
+          <t>Apartamento · 4 quartos · 90 m² · Torre</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6941,17 +6945,17 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Casa Forte</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6961,22 +6965,22 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>42.68</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -6991,12 +6995,12 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -7006,7 +7010,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-82m2-casa-forte-recife--pe_33364920</t>
+          <t>https://www.rogeriocorretor.com/imovel/casa-4-quartos-torre-recife-90m2-code-736</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7018,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Zap Imóveis Olinda</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -7022,22 +7026,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 59 m² · Bairro Novo</t>
+          <t>Apartamento · 4 quartos · 87 m² · Rosarinho</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rua Pereira Simões</t>
+          <t>Rua Hipólito Braga</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Rosarinho</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4590.0</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7052,7 +7056,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4590.0</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -7062,42 +7066,42 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>59.32</t>
+          <t>52.76</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-com-piscina-bairro-novo-olinda-pe-59m2-id-2905566215/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-rosarinho-bairros-recife-com-garagem-87m2-aluguel-RS4590-id-2913430257/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -7105,7 +7109,7 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -7113,22 +7117,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Parnamirim</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Avenida Parnamirim</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4700.0</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7143,7 +7147,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4700.0</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7153,7 +7157,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>78.33</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -7163,7 +7167,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7178,17 +7182,17 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-mobiliado-bairro-novo-olinda-pe-60m2-id-2904577437/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-parnamirim-RS4700/id-43942857/</t>
         </is>
       </c>
     </row>
@@ -7196,65 +7200,65 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 56 m² · Torreão</t>
+          <t>Apartamento · 3 quartos · 89 m² · Torre</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rua Cândido Lacerda</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Torreão</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>5500.0</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>3502.0</t>
+          <t>5500.0</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>62.54</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7264,2113 +7268,20 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-torreao-bairros-recife-com-garagem-56m2-aluguel-RS3500-id-2913434332/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr"/>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>CTI Imobiliária, Chaves na Mão Recife</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>2</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Boa Vista</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Avenida Governador Carlos De Lima Cavalcanti, 60</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Boa Vista</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>2800.0</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>553.0</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>174.0</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>3527.0</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>80.16</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>44.0</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6519</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr"/>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>CTI Imobiliária</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>1</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 41 m² · Boa Vista</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Boa Vista</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>2800.0</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>550.0</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>3542.0</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>86.39</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>41.0</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R77" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6210</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr"/>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Recife</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>1</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Parnamirim</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Avenida Parnamirim, 375</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Parnamirim</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>112.5</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>32.0</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R78" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-32m2-RS3600/id-41530823/</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Recife</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>1</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Apartamento · 1 quarto · 34 m² · 1 vaga · Parnamirim</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Avenida Parnamirim, 375</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Parnamirim</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>600.0</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>105.88</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>34.0</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R79" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-55m2-RS3000/id-46882194/</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Viva Real, Zap Imóveis</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>2</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Apartamento · 4 quartos · 120 m² · Boa Vista</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Rua Dom Carlos Coelho</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Boa Vista</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>120.0</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-boa-vista-bairros-recife-com-garagem-120m2-aluguel-RS3600-id-2913416134/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Portal CRECI Brasil</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>1</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · Encruzilhada</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Encruzilhada</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>3700.0</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>3700.0</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R81" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-encruzilhada-recife--pe_33362592</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Portal CRECI Brasil</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>1</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · Rosarinho</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Rosarinho</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>3800.0</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>3800.0</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-rosarinho-recife--pe_33388298</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr"/>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Viva Real, Zap Imóveis</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>2</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Rua José de Holanda</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Torre</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>3800.0</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>3800.0</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>84.44</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>45.0</t>
-        </is>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R83" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-torre-bairros-recife-com-garagem-45m2-aluguel-RS3800-id-2913001614/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>2</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Rua Joana D'Arc Sampaio</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>3900.0</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>3901.0</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>65.02</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3900-id-2913026520/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr"/>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>1</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Apartamento · 4 quartos · 160 m² · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>4000.0</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>4000.0</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>160.0</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R85" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-casa-caiada-bairros-olinda-com-garagem-160m2-aluguel-RS4000-id-2909290334/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr"/>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Recife</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>1</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 74 m² · 1 vaga · Aflitos</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Rua Da Angustura, 195</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Aflitos</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>2700.0</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>191.0</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>4091.0</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>55.28</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R86" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-aflitos-74m2-RS2700/id-46898128/</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr"/>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda, Rogério Corretor</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>2</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 145 m² · 2 vagas · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Avenida Min. Marcos Freire, 3495</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>4100.0</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>4100.0</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>28.28</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>145.0</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4100/id-46901493/</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr"/>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Recife</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>1</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Aflitos</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Avenida Conselheiro Rosa E Silva, 801</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Aflitos</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>4141.0</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>4142.0</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>75.31</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R88" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-aflitos-55m2-RS4141/id-45283901/</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr"/>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Portal CRECI Brasil</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>1</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 43 m² · Casa Amarela</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Casa Amarela</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>4200.0</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>4200.0</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>97.67</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>43.0</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R89" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-43m2-casa-amarela-recife--pe_33376830</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr"/>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Rogério Corretor</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>1</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 80 m² · Aflitos</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Aflitos</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>750.0</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>4350.0</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>54.38</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R90" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>https://www.rogeriocorretor.com/imovel/apartamento-2-quartos-aflitos-recife-1-vaga-80m2-code-695</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr"/>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>1</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Avenida Governador Carlos De Lima Cavalcante</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>3200.0</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>1195.0</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>4395.0</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>79.91</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R91" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-55m2-RS3200/id-46174975/</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr"/>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>1</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 85 m² · 2 vagas · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Avenida Ministro Marcos Freire</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>52.94</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R92" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-110m2-RS4500/id-42417501/</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr"/>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>3</v>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 97 m² · 2 vagas · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Avenida Ministro Marcos Freire</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>46.39</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>97.0</t>
-        </is>
-      </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R93" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4500/id-46421413/</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr"/>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Recife</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>1</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 56 m² · 1 vaga · Espinheiro</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Rua São Salvador, 200</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Espinheiro</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>80.36</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>56.0</t>
-        </is>
-      </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R94" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-espinheiro-70m2-RS4500/id-46923849/</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr"/>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Rogério Corretor</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>1</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Apartamento · 4 quartos · 90 m² · Torre</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Torre</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>https://www.rogeriocorretor.com/imovel/casa-4-quartos-torre-recife-90m2-code-736</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr"/>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Viva Real, Zap Imóveis</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>2</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Apartamento · 4 quartos · 87 m² · Rosarinho</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Rua Hipólito Braga</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Rosarinho</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>4590.0</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>4590.0</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>52.76</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R96" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-rosarinho-bairros-recife-com-garagem-87m2-aluguel-RS4590-id-2913430257/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr"/>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Recife</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>1</v>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Parnamirim</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Avenida Parnamirim</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Parnamirim</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>4700.0</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>4700.0</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>78.33</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R97" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-parnamirim-RS4700/id-43942857/</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr"/>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Portal CRECI Brasil</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>1</v>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 89 m² · Torre</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Torre</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>5500.0</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>5500.0</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>61.8</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>89.0</t>
-        </is>
-      </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R98" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="S98" t="inlineStr">
         <is>
           <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-89m2-torre-recife--pe_33386591</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S75"/>
+  <dimension ref="A1:S93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -561,59 +561,59 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 43 m² · Santana</t>
+          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Torre</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Rua Nestor Silva</t>
+          <t>Rua José De Holanda, 854</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Santana</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>3020.0</t>
+          <t>3601.0</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>70.23</t>
+          <t>81.84</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -621,7 +621,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-santana-bairros-recife-com-garagem-43m2-aluguel-RS3000-id-2913452276/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-RS3600/id-40119104/</t>
         </is>
       </c>
     </row>
@@ -648,55 +648,55 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 51 m² · Aflitos</t>
+          <t>Apartamento · 2 quartos · 51 m² · Casa Forte</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Jacó Velosino</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Casa Forte</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>3990.0</t>
+          <t>3700.0</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>3990.0</t>
+          <t>3702.0</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>78.24</t>
+          <t>72.59</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/307-manuel-de-carvalho-edificio-praca-das-cerejeiras/850721013-37</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-forte-bairros-recife-com-garagem-51m2-aluguel-RS3700-id-2912181527/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -739,30 +739,30 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 58 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 57 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rua Norberto Pessoa, 238</t>
+          <t>Rua Pintor Manoel Bandeira</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1300.0</t>
+          <t>900.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1300.0</t>
+          <t>900.0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -787,12 +787,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -807,22 +807,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1300/id-46461545/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-jardim-fragoso-bairros-olinda-com-garagem-57m2-aluguel-RS900-id-2652006870/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -838,12 +838,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 41 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 58 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rua Professor Marculino Botelho, 404</t>
+          <t>Rua Norberto Pessoa, 238</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -853,44 +853,44 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1200.0</t>
+          <t>1300.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1400.0</t>
+          <t>1300.0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>34.15</t>
+          <t>22.41</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O5" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -898,22 +898,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-pe-olinda-bairro-novo-41m2-RS1200/id-45673360/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1300/id-46461545/</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -929,37 +929,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · Boa Vista</t>
+          <t>Apartamento · 1 quarto · 41 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Professor Marculino Botelho, 404</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1100.0</t>
+          <t>1200.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>97.38</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1447.38</t>
+          <t>1400.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -969,17 +969,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>34.15</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/224/apartamento-2-quartos-jose-mariano-boa-vista-recife/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-pe-olinda-bairro-novo-41m2-RS1200/id-45673360/</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 40 m² · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 50 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1040,17 +1040,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>505.0</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>97.38</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1677.0</t>
+          <t>1447.38</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1080,22 +1080,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/2553/apartamento-1-quarto-arpege-boa-vista-recife/</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/224/apartamento-2-quartos-jose-mariano-boa-vista-recife/</t>
         </is>
       </c>
     </row>
@@ -1103,30 +1103,30 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 30 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Rua Carlos Nigro</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1449.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1449.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1171,22 +1171,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1700/id-45733416/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-30m2-aluguel-RS1449-id-2906060215/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1194,65 +1194,65 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · Santo Amaro</t>
+          <t>Apartamento · 1 quarto · 30 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Carlos Nigro</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1450.0</t>
+          <t>1499.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>405.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>80.96</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1935.96</t>
+          <t>1499.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>38.72</t>
+          <t>49.97</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/6691/apartamento-2-quartos-santo-amaro-recife/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-30m2-aluguel-RS1499-id-2912697216/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1293,57 +1293,57 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 57 m² · Arruda</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rua Coronel Alberto Lundgren, 604</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Arruda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1600.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1600.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1353,22 +1353,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS1800/id-46397377/</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/850301025-80</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1384,37 +1384,37 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 40 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rua Coronel Alberto Lundgren, 604</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1100.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>505.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>1677.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1434,32 +1434,32 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS2000/id-46397376/</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/2553/apartamento-1-quarto-arpege-boa-vista-recife/</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua Professor José Cândido Pessoa</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1495,37 +1495,37 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>684.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2477.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>68.81</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1535,22 +1535,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-720m2-RS1700/id-43805924/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1700/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1566,22 +1566,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 33 m² · Encruzilhada</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>1750.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>1750.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>53.03</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1626,22 +1626,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/123-rua-carlos-borromeu-de-frente-para-o-mercado-da-encruzilhada/850471068-78</t>
         </is>
       </c>
     </row>
@@ -1649,35 +1649,35 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 49 m² · Espinheiro</t>
+          <t>Apartamento · 1 quarto · 1625 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rua Da Hora, 235</t>
+          <t>Rua Doutor Manoel de Barros Lima</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1850.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>500.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1687,22 +1687,22 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>1850.0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1717,22 +1717,22 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>1625.0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-pe-recife-espinheiro-49m2-RS2000/id-44279997/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-bairro-novo-bairros-olinda-1625m2-aluguel-RS1850-id-2912186542/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1748,37 +1748,37 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 50 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Avenida Presidente Getúlio Vargas, 1748</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1450.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>683.0</t>
+          <t>405.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>80.96</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2576.0</t>
+          <t>1935.96</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1788,17 +1788,17 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>71.56</t>
+          <t>38.72</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1808,22 +1808,22 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-36m2-RS1800/id-45673358/</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/6691/apartamento-2-quartos-santo-amaro-recife/</t>
         </is>
       </c>
     </row>
@@ -1831,55 +1831,55 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · Ilha do Leite</t>
+          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rua Jornalista Trajano Chacon</t>
+          <t>Rua Coronel Alberto Lundgren</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ilha do Leite</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2600.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2600.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>74.29</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1899,22 +1899,22 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-ilha-do-leite-bairros-recife-com-garagem-35m2-aluguel-RS2600-id-2913377274/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS1800/id-46397377/</t>
         </is>
       </c>
     </row>
@@ -1922,45 +1922,45 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · Aflitos</t>
+          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Doutor José Augusto Moreira</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2691.0</t>
+          <t>2002.0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1970,17 +1970,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>33.37</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1990,22 +1990,22 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-aflitos-recife--pe_33374631</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-60m2-aluguel-RS2000-id-2910983844/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2013,7 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Josinildo Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2021,57 +2021,57 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 74 m² · Aflitos</t>
+          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Coronel Alberto Lundgren, 604</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2081,22 +2081,22 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>https://josinildoimoveis.com.br/imovel/apartamento-para-alugar-no-bairro-aflitos-em-recife-pe/PARJI47</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS2000/id-46397376/</t>
         </is>
       </c>
     </row>
@@ -2104,35 +2104,35 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 65 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa Monteiro, 93</t>
+          <t>Rua Professor José Cândido Pessoa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1526.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1178.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2142,17 +2142,17 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2704.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2172,22 +2172,22 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1526/id-45586419/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-65m2-aluguel-RS2200-id-2897302602/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2195,7 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CTI Imobiliária</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2203,37 +2203,37 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Graças</t>
+          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Professor José Cândido Pessoa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1600.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>953.0</t>
+          <t>684.0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2747.0</t>
+          <t>2477.0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2243,17 +2243,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>34.34</t>
+          <t>68.81</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2263,22 +2263,22 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-gracas-recife-pe/6882</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-720m2-RS1700/id-43805924/</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2294,22 +2294,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 31 m² · Parnamirim</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2850.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2850.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2334,19 +2334,19 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>91.94</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="O21" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>34</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/n%C2%BA-50-rua-condado-perto-do-cafe-sao-braz/850091040-261</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CTI Imobiliária</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2385,39 +2385,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
+          <t>Apartamento · 2 quartos · 49 m² · Espinheiro</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Da Hora, 235</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>380.0</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2880.0</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>SIM</t>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-torre-recife-pe/1353</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-pe-recife-espinheiro-49m2-RS2000/id-44279997/</t>
         </is>
       </c>
     </row>
@@ -2468,90 +2468,90 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
+          <t>Apartamento · 1 quarto · 38 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>380.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>176.42</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2956.42</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.79</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/6596/apartamento-2-quartos-torre-recife/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-38m2-aluguel-RS2500-id-2698090477/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2567,47 +2567,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 40 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos De Lima Cavalcante, 2595</t>
+          <t>Avenida Presidente Getúlio Vargas, 1748</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>683.0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>2576.0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>71.56</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-40m2-RS3000/id-45710865/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-36m2-RS1800/id-45673358/</t>
         </is>
       </c>
     </row>
@@ -2650,30 +2650,30 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 42 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 35 m² · Ilha do Leite</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Avenida Doutor José Augusto Moreira, 900</t>
+          <t>Rua Jornalista Trajano Chacon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Ilha do Leite</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>74.29</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2718,22 +2718,22 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-RS3000/id-44380568/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-ilha-do-leite-bairros-recife-com-garagem-35m2-aluguel-RS2600-id-2913377274/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2741,35 +2741,35 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 35 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa Monteiro, 93</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1822.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1178.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2779,22 +2779,22 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>32.26</t>
+          <t>74.29</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2804,27 +2804,27 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1822/id-45585830/</t>
+          <t>https://www.vivareal.com.br/imovel/flat-1-quartos-bairro-novo-bairros-olinda-com-garagem-35m2-aluguel-RS2600-id-2912188115/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2840,22 +2840,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 92 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 55 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Avenida Carlos De Lima Cavalcante</t>
+          <t>Rua Professor José Cândido Pessoa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2880,17 +2880,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>47.27</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2900,22 +2900,22 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS3000/id-42437394/</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-bairro-novo-olinda-pe-55m2-id-2912341217/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2923,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2931,37 +2931,37 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 3 quartos · Aflitos</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rua Cardeal Arcoverde, 276</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2332.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>550.0</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>2691.0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>93.75</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2991,22 +2991,22 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS2332/id-46081872/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-aflitos-recife--pe_33374631</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>Josinildo Imóveis</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3022,22 +3022,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · Rosarinho</t>
+          <t>Apartamento · 3 quartos · 74 m² · Aflitos</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rua Engenheiro Sampaio</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosarinho</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3062,42 +3062,42 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>36.49</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/flat-1-quartos-rosarinho-bairros-recife-com-garagem-35m2-aluguel-RS3000-id-2913427019/?source=ranking%2Crp</t>
+          <t>https://josinildoimoveis.com.br/imovel/apartamento-para-alugar-no-bairro-aflitos-em-recife-pe/PARJI47</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3105,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Josinildo Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -3113,27 +3113,27 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 42 m² · Torre</t>
+          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Otaviano Pessoa Monteiro, 93</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>1526.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1178.0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>2704.0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>29.08</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3173,22 +3173,22 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>https://josinildoimoveis.com.br/imovel/edf-green-life-torre/PARJI03</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1526/id-45586419/</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>CTI Imobiliária</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 2 quartos · 80 m² · Graças</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rua Amélia, 623</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3219,42 +3219,42 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>1600.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>953.0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>2747.0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>34.34</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3264,22 +3264,22 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>63</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-RS3200/id-45197779/</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-gracas-recife-pe/6882</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Newville</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 52 m² · Torre</t>
+          <t>Apartamento · 2 quartos · 63 m² · Aflitos</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3355,22 +3355,22 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>https://newville.com.br/imovel/apartamento_2_quartos--torre--recife--pe--locacao--cod-6391</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/850251137-34</t>
         </is>
       </c>
     </row>
@@ -3378,30 +3378,30 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 38 m² · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 60 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3426,17 +3426,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3446,22 +3446,22 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-1-quarto-alugar-38m2-boa-vista-recife--pe_33378812</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-60m2-aluguel-RS2800-id-2912116616/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3469,30 +3469,30 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 40 m² · Santana</t>
+          <t>Apartamento · 40 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Santana</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3517,19 +3517,19 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="O34" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -3542,17 +3542,17 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/70-rua-samuel-de-farias/850091105-39</t>
+          <t>https://www.vivareal.com.br/imovel/kitnet-casa-caiada-bairros-olinda-com-garagem-40m2-aluguel-RS2800-id-2910716413/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3568,22 +3568,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · Encruzilhada</t>
+          <t>Apartamento · 3 quartos · 71 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Gildo Branco</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3608,42 +3608,42 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>91.43</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/68-rua-engenheiro-sampaio/850701030-102</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-com-piscina-casa-caiada-olinda-pe-71m2-id-2911301943/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>CTI Imobiliária</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3659,27 +3659,27 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 37 m² · Espinheiro</t>
+          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rua Barão de Itamaracá</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>380.0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3689,27 +3689,27 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>2880.0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>86.49</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3719,22 +3719,22 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-espinheiro-bairros-recife-com-garagem-37m2-aluguel-RS3200-id-2913453536/?source=ranking%2Crp</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-torre-recife-pe/1353</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · 1 vaga · Casa Amarela</t>
+          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3760,27 +3760,27 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>380.0</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>237.0</t>
+          <t>176.42</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>3202.0</t>
+          <t>2956.42</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>45.74</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-amarela-70m2-RS2000/id-43758789/</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/6596/apartamento-2-quartos-torre-recife/</t>
         </is>
       </c>
     </row>
@@ -3833,30 +3833,30 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 66 m² · 1 vaga · Campo Grande</t>
+          <t>Apartamento · 2 quartos · 42 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rua Barão De Vera Cruz</t>
+          <t>Rua Ulisses Tenório de Albuquerque</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Campo Grande</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>2998.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>2998.0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3881,12 +3881,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>71.38</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3901,22 +3901,22 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-campo-grande-79m2-RS3300/id-44353442/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-42m2-aluguel-RS2998-id-2911376544/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3932,52 +3932,52 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 65 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 40 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rua Eduardo De Moraes</t>
+          <t>Avenida Governador Carlos De Lima Cavalcante, 2595</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>422.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>3317.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>51.03</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3992,22 +3992,22 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-1038m2-RS2700/id-27611651/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-40m2-RS3000/id-45710865/</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4015,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -4023,57 +4023,57 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 75 m² · Graças</t>
+          <t>Apartamento · 1 quarto · 42 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Doutor José Augusto Moreira, 900</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>588.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>109.04</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>3397.04</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>45.29</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4083,22 +4083,22 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/3178/apartamento-2-quartos-celina-gonçalves-de-oliveira-graças-recife/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-RS3000/id-44380568/</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -4114,27 +4114,27 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 37 m² · Rosarinho</t>
+          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rua Doutor José Maria</t>
+          <t>Rua Otaviano Pessoa Monteiro, 93</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosarinho</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>3400.0</t>
+          <t>1822.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1178.0</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4144,52 +4144,52 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>3400.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>91.89</t>
+          <t>32.26</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-rosarinho-bairros-recife-com-garagem-37m2-aluguel-RS3400-id-2913418918/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1822/id-45585830/</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4197,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -4205,22 +4205,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · Ilha do Leite</t>
+          <t>Apartamento · 3 quartos · 92 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rua Jornalista Trajano Chacon</t>
+          <t>Avenida Carlos De Lima Cavalcante</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ilha do Leite</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>3450.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>3450.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4245,42 +4245,42 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>95.83</t>
+          <t>32.61</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-ilha-do-leite-bairros-recife-com-garagem-36m2-aluguel-RS3450-id-2913191116/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS3000/id-42437394/</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4288,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -4296,82 +4296,82 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 59 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rua Pereira Simões, 1529 - 2</t>
+          <t>Rua Cardeal Arcoverde, 276</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>2332.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>550.0</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>59.32</t>
+          <t>93.75</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-59m2-RS3500/id-45711136/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS2332/id-46081872/</t>
         </is>
       </c>
     </row>
@@ -4379,30 +4379,30 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 57 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 59 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rua Francisco Ambrósio De Barros Leite, 1225</t>
+          <t>Rua Dom Pedro Henrique</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4427,12 +4427,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>50.85</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4442,27 +4442,27 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-RS3500/id-42986293/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-santo-amaro-bairros-recife-com-garagem-59m2-aluguel-RS3000-id-2913400521/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4470,30 +4470,30 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · 1 vaga · Torre</t>
+          <t>Apartamento · 2 quartos · 68 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rua Real Da Torre</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>44.12</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4528,32 +4528,32 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-50m2-RS3500/id-46933917/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-68m2-aluguel-RS3000-id-2913457037/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife, Rogério Corretor</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4569,22 +4569,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 3 quartos · 60 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rua Cardeal Arcoverde, 1</t>
+          <t>Rua Professor Francisco Xavier Paes Barreto</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4609,42 +4609,42 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>106.06</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS3500/id-45844382/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3000-id-2912144534/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4652,7 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Zap Imóveis</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4660,27 +4660,27 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · Tamarineira</t>
+          <t>Apartamento · 1 quarto · 34 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Agamenon Magalhães</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tamarineira</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4690,52 +4690,52 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-70m2-tamarineira-recife--pe_33364198</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-1-quarto-com-piscina-boa-vista-recife-pe-34m2-id-2913394619/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4743,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -4751,57 +4751,57 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · Torre</t>
+          <t>Apartamento · 1 quarto · 43 m² · Santana</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Nestor Silva</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Santana</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3020.0</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>70.23</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4811,22 +4811,22 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-77m2-torre-recife--pe_33379670</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-santana-bairros-recife-com-garagem-43m2-aluguel-RS3000-id-2913452276/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Josinildo Imóveis</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 82 m² · Casa Forte</t>
+          <t>Apartamento · 2 quartos · 42 m² · Torre</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4852,17 +4852,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Casa Forte</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4872,17 +4872,17 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>42.68</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4902,22 +4902,22 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-82m2-casa-forte-recife--pe_33364920</t>
+          <t>https://josinildoimoveis.com.br/imovel/edf-green-life-torre/PARJI03</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4925,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -4933,22 +4933,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 83 m² · Aflitos</t>
+          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Amélia, 623</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4973,17 +4973,17 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>42.09</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4993,22 +4993,22 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>83.15</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/850191006-42</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-RS3200/id-45197779/</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>Newville</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -5024,47 +5024,47 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 56 m² · Torreão</t>
+          <t>Apartamento · 2 quartos · 52 m² · Torre</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rua Cândido Lacerda</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Torreão</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>3502.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>62.54</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5084,22 +5084,22 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-torreao-bairros-recife-com-garagem-56m2-aluguel-RS3500-id-2913434332/?source=ranking%2Crp</t>
+          <t>https://newville.com.br/imovel/apartamento_2_quartos--torre--recife--pe--locacao--cod-6391</t>
         </is>
       </c>
     </row>
@@ -5107,20 +5107,20 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CTI Imobiliária, Chaves na Mão Recife</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Boa Vista</t>
+          <t>Apartamento · 1 quarto · 38 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos De Lima Cavalcanti, 60</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5130,42 +5130,42 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>553.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>3527.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>80.16</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6519</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-1-quarto-alugar-38m2-boa-vista-recife--pe_33378812</t>
         </is>
       </c>
     </row>
@@ -5198,65 +5198,65 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CTI Imobiliária</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 41 m² · Boa Vista</t>
+          <t>Apartamento · 1 quarto · 37 m² · Espinheiro</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Barão de Itamaracá</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>550.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>3542.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>86.39</t>
+          <t>86.49</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6210</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-espinheiro-bairros-recife-com-garagem-37m2-aluguel-RS3200-id-2913453536/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5289,30 +5289,30 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Parnamirim</t>
+          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Avenida Parnamirim, 375</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5337,19 +5337,19 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O54" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -5357,22 +5357,22 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-32m2-RS3600/id-41530823/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3200-id-2906163316/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5380,35 +5380,35 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 34 m² · 1 vaga · Parnamirim</t>
+          <t>Apartamento · 2 quartos · 57 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Avenida Parnamirim, 375</t>
+          <t>Rua Pereira Simões</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>600.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5418,52 +5418,52 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>105.88</t>
+          <t>56.14</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-55m2-RS3000/id-46882194/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-57m2-aluguel-RS3200-id-2901326206/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5471,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -5479,52 +5479,52 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Apartamento · 4 quartos · 120 m² · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 70 m² · 1 vaga · Casa Amarela</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rua Dom Carlos Coelho</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>237.0</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3202.0</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>45.74</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -5539,22 +5539,22 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-boa-vista-bairros-recife-com-garagem-120m2-aluguel-RS3600-id-2913416134/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-amarela-70m2-RS2000/id-43758789/</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -5570,22 +5570,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 51 m² · Aflitos</t>
+          <t>Apartamento · 3 quartos · 66 m² · 1 vaga · Campo Grande</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Barão De Vera Cruz</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Campo Grande</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>3699.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>3699.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5610,17 +5610,17 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>72.53</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5630,22 +5630,22 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/307-rua-manuel-de-carvalho/850701030-101</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-campo-grande-79m2-RS3300/id-44353442/</t>
         </is>
       </c>
     </row>
@@ -5653,35 +5653,35 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · Encruzilhada</t>
+          <t>Apartamento · 2 quartos · 58 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Pereira Simões</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>3700.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5691,27 +5691,27 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>3700.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5721,22 +5721,22 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-encruzilhada-recife--pe_33362592</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-58m2-aluguel-RS3300-id-2913435980/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5744,7 +5744,7 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -5752,57 +5752,57 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · Rosarinho</t>
+          <t>Apartamento · 2 quartos · 65 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Eduardo De Moraes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosarinho</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>3800.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>422.0</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>3800.0</t>
+          <t>3317.0</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-rosarinho-recife--pe_33388298</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-1038m2-RS2700/id-27611651/</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5835,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · Encruzilhada</t>
+          <t>Apartamento · 2 quartos · 75 m² · Graças</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5853,37 +5853,37 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>3800.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>588.0</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>109.04</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>3800.0</t>
+          <t>3397.04</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>54.29</t>
+          <t>45.29</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5903,22 +5903,22 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/edf-arcadia/850091082-77</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/3178/apartamento-2-quartos-celina-gonçalves-de-oliveira-graças-recife/</t>
         </is>
       </c>
     </row>
@@ -5926,30 +5926,30 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
+          <t>Apartamento · 1 quarto · 37 m² · Rosarinho</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rua José de Holanda</t>
+          <t>Rua Doutor José Maria</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Rosarinho</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>3800.0</t>
+          <t>3400.0</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>3800.0</t>
+          <t>3400.0</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -5974,12 +5974,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>84.44</t>
+          <t>91.89</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -5994,22 +5994,22 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-torre-bairros-recife-com-garagem-45m2-aluguel-RS3800-id-2913001614/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-rosarinho-bairros-recife-com-garagem-37m2-aluguel-RS3400-id-2913418918/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -6017,75 +6017,75 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 74 m² · 1 vaga · Aflitos</t>
+          <t>Apartamento · 1 quarto · 36 m² · Ilha do Leite</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rua Da Angustura, 195</t>
+          <t>Rua Jornalista Trajano Chacon</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Ilha do Leite</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>3450.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>1200.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>4091.0</t>
+          <t>3450.0</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>55.28</t>
+          <t>95.83</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-aflitos-74m2-RS2700/id-46898128/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-ilha-do-leite-bairros-recife-com-garagem-36m2-aluguel-RS3450-id-2913191116/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -6108,30 +6108,30 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Rogério Corretor</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 145 m² · 2 vagas · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 58 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Avenida Min. Marcos Freire, 3495</t>
+          <t>Rua Pereira Simões, 1529 - 2</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>4100.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>4100.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6156,17 +6156,17 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>60.34</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6176,22 +6176,22 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4100/id-46901493/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-59m2-RS3500/id-45711136/</t>
         </is>
       </c>
     </row>
@@ -6199,7 +6199,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -6207,22 +6207,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Aflitos</t>
+          <t>Apartamento · 2 quartos · 57 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Avenida Conselheiro Rosa E Silva, 801</t>
+          <t>Rua Francisco Ambrósio De Barros Leite, 1225</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>4141.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>4142.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>75.31</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6267,22 +6267,22 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-aflitos-55m2-RS4141/id-45283901/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-RS3500/id-42986293/</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -6298,27 +6298,27 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 43 m² · Casa Amarela</t>
+          <t>Apartamento · 2 quartos · 50 m² · 1 vaga · Torre</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Real Da Torre</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>4200.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6328,17 +6328,17 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>4200.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>97.67</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -6358,22 +6358,22 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-43m2-casa-amarela-recife--pe_33376830</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-50m2-RS3500/id-46933917/</t>
         </is>
       </c>
     </row>
@@ -6381,30 +6381,30 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Chaves na Mão Recife, Rogério Corretor</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 58 m² · Espinheiro</t>
+          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Cardeal Arcoverde, 1</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>4200.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>4200.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6429,17 +6429,17 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>106.06</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6449,22 +6449,22 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/862-rua-da-hora/850251129-67</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS3500/id-45844382/</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Rogério Corretor</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Aflitos</t>
+          <t>Apartamento · 2 quartos · 70 m² · Tamarineira</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6490,17 +6490,17 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Tamarineira</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>4350.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6520,7 +6520,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>54.38</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>https://www.rogeriocorretor.com/imovel/apartamento-2-quartos-aflitos-recife-1-vaga-80m2-code-695</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-70m2-tamarineira-recife--pe_33364198</t>
         </is>
       </c>
     </row>
@@ -6563,7 +6563,7 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -6571,27 +6571,27 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 77 m² · Torre</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos De Lima Cavalcante</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1195.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6601,27 +6601,27 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>4395.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>79.91</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6631,22 +6631,22 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-55m2-RS3200/id-46174975/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-77m2-torre-recife--pe_33379670</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -6662,27 +6662,27 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · 2 vagas · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 82 m² · Casa Forte</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Avenida Ministro Marcos Freire</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Casa Forte</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6692,27 +6692,27 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>52.94</t>
+          <t>42.68</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-110m2-RS4500/id-42417501/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-82m2-casa-forte-recife--pe_33364920</t>
         </is>
       </c>
     </row>
@@ -6745,30 +6745,30 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 97 m² · 2 vagas · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 60 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Avenida Ministro Marcos Freire, 3291</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -6793,17 +6793,17 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>46.39</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6813,22 +6813,22 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4500/id-46421413/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-60m2-aluguel-RS3500-id-2904577437/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -6836,55 +6836,55 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 56 m² · 1 vaga · Espinheiro</t>
+          <t>Apartamento · 2 quartos · 56 m² · Torreão</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rua São Salvador, 200</t>
+          <t>Rua Cândido Lacerda</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Torreão</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>3502.0</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>80.36</t>
+          <t>62.54</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -6909,17 +6909,17 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-espinheiro-70m2-RS4500/id-46923849/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-torreao-bairros-recife-com-garagem-56m2-aluguel-RS3500-id-2913434332/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -6927,65 +6927,65 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Rogério Corretor</t>
+          <t>CTI Imobiliária, Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Apartamento · 4 quartos · 90 m² · Torre</t>
+          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Boa Vista</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos De Lima Cavalcanti, 60</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>553.0</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>174.0</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>3527.0</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>80.16</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -6995,22 +6995,22 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>https://www.rogeriocorretor.com/imovel/casa-4-quartos-torre-recife-90m2-code-736</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6519</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>CTI Imobiliária</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -7026,57 +7026,57 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Apartamento · 4 quartos · 87 m² · Rosarinho</t>
+          <t>Apartamento · 2 quartos · 41 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rua Hipólito Braga</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosarinho</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>4590.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>550.0</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>4590.0</t>
+          <t>3542.0</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>52.76</t>
+          <t>86.39</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-rosarinho-bairros-recife-com-garagem-87m2-aluguel-RS4590-id-2913430257/?source=ranking%2Crp</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6210</t>
         </is>
       </c>
     </row>
@@ -7117,12 +7117,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Parnamirim</t>
+          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Parnamirim</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Avenida Parnamirim</t>
+          <t>Avenida Parnamirim, 375</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>4700.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>4700.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7157,42 +7157,42 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>78.33</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-parnamirim-RS4700/id-43942857/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-32m2-RS3600/id-41530823/</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -7208,80 +7208,1718 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t>Apartamento · 1 quarto · 34 m² · 1 vaga · Parnamirim</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Avenida Parnamirim, 375</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Parnamirim</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>600.0</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>105.88</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-55m2-RS3000/id-46882194/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Viva Real, Zap Imóveis</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>2</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Apartamento · 4 quartos · 120 m² · Boa Vista</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Rua Dom Carlos Coelho</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Boa Vista</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>120.0</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-boa-vista-bairros-recife-com-garagem-120m2-aluguel-RS3600-id-2913416134/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Portal CRECI Brasil</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · Encruzilhada</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Encruzilhada</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>3700.0</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>3700.0</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-encruzilhada-recife--pe_33362592</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Portal CRECI Brasil</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · Rosarinho</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Rosarinho</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>3800.0</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>3800.0</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-rosarinho-recife--pe_33388298</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>2</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Rua Joana D'Arc Sampaio</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>3900.0</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>3901.0</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>65.02</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3900-id-2913026520/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Recife</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 74 m² · 1 vaga · Aflitos</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Rua Da Angustura, 195</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Aflitos</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2700.0</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>191.0</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>4091.0</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>55.28</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-aflitos-74m2-RS2700/id-46898128/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Olinda, Rogério Corretor</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 145 m² · 2 vagas · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Avenida Min. Marcos Freire, 3495</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>4100.0</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>4100.0</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>28.28</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4100/id-46901493/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Recife</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Aflitos</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Avenida Conselheiro Rosa E Silva, 801</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Aflitos</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>4141.0</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>4142.0</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>75.31</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-aflitos-55m2-RS4141/id-45283901/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Portal CRECI Brasil</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 43 m² · Casa Amarela</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Casa Amarela</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>4200.0</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>4200.0</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>97.67</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>43.0</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-43m2-casa-amarela-recife--pe_33376830</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Rogério Corretor</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 80 m² · Aflitos</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Aflitos</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>750.0</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>4350.0</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>54.38</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>https://www.rogeriocorretor.com/imovel/apartamento-2-quartos-aflitos-recife-1-vaga-80m2-code-695</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Olinda</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Avenida Governador Carlos De Lima Cavalcante</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>3200.0</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>1195.0</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>4395.0</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>79.91</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-55m2-RS3200/id-46174975/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Olinda</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 85 m² · 2 vagas · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Avenida Ministro Marcos Freire</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>4500.0</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>4500.0</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>52.94</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-110m2-RS4500/id-42417501/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>3</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 97 m² · 2 vagas · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Avenida Ministro Marcos Freire</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>4500.0</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>4500.0</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>46.39</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4500/id-46421413/</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Recife</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 56 m² · 1 vaga · Espinheiro</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Rua São Salvador, 200</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Espinheiro</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>4500.0</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>4500.0</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>80.36</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>56.0</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-espinheiro-70m2-RS4500/id-46923849/</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Rogério Corretor</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Apartamento · 4 quartos · 90 m² · Torre</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Torre</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>4500.0</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>4500.0</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>https://www.rogeriocorretor.com/imovel/casa-4-quartos-torre-recife-90m2-code-736</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Zap Imóveis</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 51 m² · Graças</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Rua Amélia</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Graças</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>4500.0</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>4500.0</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>88.24</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>51.0</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-mobiliado-gracas-recife-pe-51m2-id-2912084621/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Viva Real, Zap Imóveis</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>2</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Apartamento · 4 quartos · 87 m² · Rosarinho</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Rua Hipólito Braga</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Rosarinho</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>4590.0</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>4590.0</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>52.76</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-rosarinho-bairros-recife-com-garagem-87m2-aluguel-RS4590-id-2913430257/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Recife</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Parnamirim</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Avenida Parnamirim</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Parnamirim</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>4700.0</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>4700.0</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>78.33</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-parnamirim-RS4700/id-43942857/</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Portal CRECI Brasil</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
           <t>Apartamento · 3 quartos · 89 m² · Torre</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
         <is>
           <t>Torre</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>5500.0</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
         <is>
           <t>5500.0</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t>61.8</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
         <is>
           <t>89.0</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="Q93" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="R93" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="S93" t="inlineStr">
         <is>
           <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-89m2-torre-recife--pe_33386591</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S93"/>
+  <dimension ref="A1:S91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -553,60 +553,60 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Torre</t>
+          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Rua José De Holanda, 854</t>
+          <t>Rua Professor José Cândido Pessoa</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>684.0</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>3601.0</t>
+          <t>2477.0</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>81.84</t>
+          <t>68.81</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -621,22 +621,22 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-RS3600/id-40119104/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-720m2-RS1700/id-43805924/</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -656,264 +656,272 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 51 m² · Casa Forte</t>
+          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Rua Jacó Velosino</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Casa Forte</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>3700.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>3702.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>23.36</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-bairros-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>72.59</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>51.0</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>REMAX Recife e Olinda</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 1 quarto · 34 m² · Santo Amaro</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Santo Amaro</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>88.24</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-forte-bairros-recife-com-garagem-51m2-aluguel-RS3700-id-2912181527/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/185-rua-dom-pedro-henrique-prox-a-catolica/850301004-158</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Recife, Josinildo Imóveis</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 57 m² · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Rua Pintor Manoel Bandeira</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>900.0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>900.0</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 74 m² · 1 vaga · Aflitos</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Rua Da Angustura, 195</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Aflitos</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4091.0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>4091.0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>15.79</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>57.0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-jardim-fragoso-bairros-olinda-com-garagem-57m2-aluguel-RS900-id-2652006870/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 58 m² · 1 vaga · Bairro Novo</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Rua Norberto Pessoa, 238</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Bairro Novo</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1300.0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>1300.0</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>22.41</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>55.28</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>58.0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1300/id-46461545/</t>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-aflitos-74m2-RS4091/id-46898128/</t>
         </is>
       </c>
     </row>
@@ -929,12 +937,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 41 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 58 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rua Professor Marculino Botelho, 404</t>
+          <t>Rua Norberto Pessoa, 238</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -944,44 +952,44 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1200.0</t>
+          <t>1300.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1400.0</t>
+          <t>1300.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>34.15</t>
+          <t>22.41</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -989,22 +997,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-pe-olinda-bairro-novo-41m2-RS1200/id-45673360/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1300/id-46461545/</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1020,7 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1020,37 +1028,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · Boa Vista</t>
+          <t>Apartamento · 1 quarto · 41 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Professor Marculino Botelho, 404</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1100.0</t>
+          <t>1200.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>97.38</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1447.38</t>
+          <t>1400.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1060,17 +1068,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>34.15</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1080,7 +1088,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1095,7 +1103,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/224/apartamento-2-quartos-jose-mariano-boa-vista-recife/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-pe-olinda-bairro-novo-41m2-RS1200/id-45673360/</t>
         </is>
       </c>
     </row>
@@ -1103,65 +1111,65 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 50 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rua Carlos Nigro</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1449.0</t>
+          <t>1100.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>97.38</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1449.0</t>
+          <t>1447.38</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1171,22 +1179,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-30m2-aluguel-RS1449-id-2906060215/?source=ranking%2Crp</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/224/apartamento-2-quartos-jose-mariano-boa-vista-recife/</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1293,7 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1293,7 +1301,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 57 m² · Arruda</t>
+          <t>Apartamento · 1 quarto · 40 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1303,42 +1311,42 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arruda</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1600.0</t>
+          <t>1100.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>505.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1600.0</t>
+          <t>1677.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1353,22 +1361,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/850301025-80</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/2553/apartamento-1-quarto-arpege-boa-vista-recife/</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1384,7 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1384,57 +1392,57 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 40 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1100.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>505.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1677.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1444,22 +1452,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/2553/apartamento-1-quarto-arpege-boa-vista-recife/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1700/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1475,7 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1475,57 +1483,57 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 50 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1450.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>405.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>80.96</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1935.96</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>38.72</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1535,22 +1543,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1700/id-45733416/</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/6691/apartamento-2-quartos-santo-amaro-recife/</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1566,7 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1566,47 +1574,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · Encruzilhada</t>
+          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Coronel Alberto Lundgren, 604</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1750.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1750.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>53.03</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1616,7 +1624,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1626,22 +1634,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/123-rua-carlos-borromeu-de-frente-para-o-mercado-da-encruzilhada/850471068-78</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS1800/id-46397377/</t>
         </is>
       </c>
     </row>
@@ -1657,59 +1665,59 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 1625 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rua Doutor Manoel de Barros Lima</t>
+          <t>Avenida Doutor José Augusto Moreira</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1850.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1850.0</t>
+          <t>2002.0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>33.37</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -1717,22 +1725,22 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1625.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-bairro-novo-bairros-olinda-1625m2-aluguel-RS1850-id-2912186542/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-60m2-aluguel-RS2000-id-2910983844/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1748,7 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1748,37 +1756,37 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · Santo Amaro</t>
+          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Coronel Alberto Lundgren, 604</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1450.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>405.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>80.96</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1935.96</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1788,17 +1796,17 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>38.72</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1808,22 +1816,22 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/6691/apartamento-2-quartos-santo-amaro-recife/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS2000/id-46397376/</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1839,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1839,12 +1847,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 65 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rua Coronel Alberto Lundgren</t>
+          <t>Rua Professor José Cândido Pessoa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1854,42 +1862,42 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1899,22 +1907,22 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS1800/id-46397377/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-65m2-aluguel-RS2200-id-2897302602/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1922,20 +1930,20 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Avenida Doutor José Augusto Moreira</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1945,37 +1953,37 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2002.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>33.37</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1990,22 +1998,22 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>34</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-60m2-aluguel-RS2000-id-2910983844/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2021,7 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2021,17 +2029,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 49 m² · Espinheiro</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rua Coronel Alberto Lundgren, 604</t>
+          <t>Rua Da Hora, 235</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2041,17 +2049,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>500.0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2061,19 +2069,19 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O18" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -2081,7 +2089,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2096,7 +2104,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS2000/id-46397376/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-pe-recife-espinheiro-49m2-RS2000/id-44279997/</t>
         </is>
       </c>
     </row>
@@ -2112,22 +2120,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 65 m² · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 38 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rua Professor José Cândido Pessoa</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2142,7 +2150,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2152,42 +2160,42 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>33.85</t>
+          <t>65.79</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-65m2-aluguel-RS2200-id-2897302602/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-38m2-aluguel-RS2500-id-2698090477/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2216,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rua Professor José Cândido Pessoa</t>
+          <t>Avenida Presidente Getúlio Vargas, 1748</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2218,12 +2226,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>684.0</t>
+          <t>683.0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2233,7 +2241,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2477.0</t>
+          <t>2576.0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2243,7 +2251,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>68.81</t>
+          <t>71.56</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2268,17 +2276,17 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-720m2-RS1700/id-43805924/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-36m2-RS1800/id-45673358/</t>
         </is>
       </c>
     </row>
@@ -2286,30 +2294,30 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 35 m² · Ilha do Leite</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua Jornalista Trajano Chacon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Ilha do Leite</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2324,7 +2332,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2334,12 +2342,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>74.29</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2354,22 +2362,22 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-ilha-do-leite-bairros-recife-com-garagem-35m2-aluguel-RS2600-id-2913377274/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2377,35 +2385,35 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 49 m² · Espinheiro</t>
+          <t>Apartamento · 2 quartos · 55 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rua Da Hora, 235</t>
+          <t>Rua Professor José Cândido Pessoa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>500.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2415,17 +2423,17 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>47.27</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2445,22 +2453,22 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-pe-recife-espinheiro-49m2-RS2000/id-44279997/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-55m2-aluguel-RS2600-id-2912341217/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2468,25 +2476,25 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 38 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · Aflitos</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2496,7 +2504,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2506,52 +2514,52 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2691.0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>65.79</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-38m2-aluguel-RS2500-id-2698090477/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-aflitos-recife--pe_33374631</t>
         </is>
       </c>
     </row>
@@ -2567,69 +2575,69 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Avenida Presidente Getúlio Vargas, 1748</t>
+          <t>Rua Otaviano Pessoa Monteiro, 93</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1526.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>683.0</t>
+          <t>1178.0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2704.0</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>29.08</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
           <t>93.0</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2576.0</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>71.56</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>36.0</t>
-        </is>
-      </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>19</t>
@@ -2642,7 +2650,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-36m2-RS1800/id-45673358/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1526/id-45586419/</t>
         </is>
       </c>
     </row>
@@ -2650,65 +2658,65 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>CTI Imobiliária</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · Ilha do Leite</t>
+          <t>Apartamento · 2 quartos · 80 m² · Graças</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rua Jornalista Trajano Chacon</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ilha do Leite</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2600.0</t>
+          <t>1600.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>953.0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2600.0</t>
+          <t>2747.0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>74.29</t>
+          <t>34.34</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2718,22 +2726,22 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>63</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-ilha-do-leite-bairros-recife-com-garagem-35m2-aluguel-RS2600-id-2913377274/?source=ranking%2Crp</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-gracas-recife-pe/6882</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2749,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2749,22 +2757,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 63 m² · Aflitos</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Rua Samuel Campelo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2600.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2779,7 +2787,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2600.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2789,42 +2797,42 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>74.29</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/flat-1-quartos-bairro-novo-bairros-olinda-com-garagem-35m2-aluguel-RS2600-id-2912188115/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-aflitos-bairros-recife-com-garagem-63m2-aluguel-RS2800-id-2912913421/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2832,30 +2840,30 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Zap Imóveis Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 55 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 71 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rua Professor José Cândido Pessoa</t>
+          <t>Rua Gildo Branco</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2600.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2870,7 +2878,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2600.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2880,19 +2888,19 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>47.27</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O27" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -2900,22 +2908,22 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-bairro-novo-olinda-pe-55m2-id-2912341217/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-71m2-aluguel-RS2800-id-2911301943/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2923,35 +2931,35 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · Aflitos</t>
+          <t>Apartamento · 1 quarto · 36 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2961,52 +2969,52 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2691.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-aflitos-recife--pe_33374631</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-36m2-aluguel-RS2800-id-2705654338/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3014,30 +3022,30 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Josinildo Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 74 m² · Aflitos</t>
+          <t>Apartamento · 40 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3052,7 +3060,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3062,17 +3070,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3082,22 +3090,22 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>https://josinildoimoveis.com.br/imovel/apartamento-para-alugar-no-bairro-aflitos-em-recife-pe/PARJI47</t>
+          <t>https://www.vivareal.com.br/imovel/kitnet-casa-caiada-bairros-olinda-com-garagem-40m2-aluguel-RS2800-id-2910716413/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3113,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -3113,27 +3121,27 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 31 m² · Parnamirim</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa Monteiro, 93</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1526.0</t>
+          <t>2850.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1178.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3143,27 +3151,27 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2704.0</t>
+          <t>2850.0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>91.94</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3173,22 +3181,22 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1526/id-45586419/</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/n%C2%BA-50-rua-condado-perto-do-cafe-sao-braz/850091040-261</t>
         </is>
       </c>
     </row>
@@ -3196,67 +3204,67 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CTI Imobiliária</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Graças</t>
+          <t>Apartamento · 3 quartos · 71 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Gildo Branco</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1600.0</t>
+          <t>2850.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>953.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2747.0</t>
+          <t>2850.0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>34.34</t>
+          <t>40.14</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="O31" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -3264,22 +3272,22 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-gracas-recife-pe/6882</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-71m2-aluguel-RS2850-id-2911876830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3295,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>CTI Imobiliária</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -3295,7 +3303,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 63 m² · Aflitos</t>
+          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3305,17 +3313,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>380.0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3325,17 +3333,17 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>2880.0</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3355,22 +3363,22 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/850251137-34</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-torre-recife-pe/1353</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3386,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -3386,22 +3394,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 35 m² · Aflitos</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Rua Samuel Campelo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>2900.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3416,7 +3424,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>2900.0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3426,42 +3434,42 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>82.86</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-60m2-aluguel-RS2800-id-2912116616/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-aflitos-bairros-recife-com-garagem-35m2-aluguel-RS2900-id-2913410942/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3469,65 +3477,65 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Apartamento · 40 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>380.0</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>176.42</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>2956.42</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3537,22 +3545,22 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/kitnet-casa-caiada-bairros-olinda-com-garagem-40m2-aluguel-RS2800-id-2910716413/?source=ranking%2Crp</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/6596/apartamento-2-quartos-torre-recife/</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3568,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3568,12 +3576,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 71 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 40 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rua Gildo Branco</t>
+          <t>Avenida Governador Carlos De Lima Cavalcante, 2595</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3583,7 +3591,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3598,7 +3606,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3608,42 +3616,42 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-com-piscina-casa-caiada-olinda-pe-71m2-id-2911301943/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-40m2-RS3000/id-45710865/</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3659,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CTI Imobiliária</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3659,27 +3667,27 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
+          <t>Apartamento · 1 quarto · 42 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Doutor José Augusto Moreira, 900</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>380.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3689,27 +3697,27 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2880.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3719,7 +3727,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3734,7 +3742,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-torre-recife-pe/1353</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-RS3000/id-44380568/</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3750,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3750,37 +3758,37 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
+          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Otaviano Pessoa Monteiro, 93</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>1822.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>380.0</t>
+          <t>1178.0</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>176.42</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2956.42</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3790,7 +3798,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>32.26</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3800,7 +3808,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3810,7 +3818,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -3825,7 +3833,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/6596/apartamento-2-quartos-torre-recife/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1822/id-45585830/</t>
         </is>
       </c>
     </row>
@@ -3833,20 +3841,20 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 42 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 92 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rua Ulisses Tenório de Albuquerque</t>
+          <t>Avenida Carlos De Lima Cavalcante</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3856,7 +3864,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2998.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3871,7 +3879,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2998.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3881,19 +3889,19 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>71.38</t>
+          <t>32.61</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O38" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -3901,22 +3909,22 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-42m2-aluguel-RS2998-id-2911376544/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS3000/id-42437394/</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3932,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3932,47 +3940,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 40 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos De Lima Cavalcante, 2595</t>
+          <t>Rua Cardeal Arcoverde, 276</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
+          <t>2332.0</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>550.0</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>118.0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
           <t>3000.0</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>93.75</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3992,22 +4000,22 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-40m2-RS3000/id-45710865/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS2332/id-46081872/</t>
         </is>
       </c>
     </row>
@@ -4015,25 +4023,25 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 42 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 68 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Avenida Doutor José Augusto Moreira, 900</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4063,42 +4071,42 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>44.12</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-RS3000/id-44380568/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-68m2-aluguel-RS3000-id-2913457037/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4106,20 +4114,20 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 62 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa Monteiro, 93</t>
+          <t>Rua Otaviano Pessoa Monteiro</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4129,12 +4137,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1822.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1178.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4149,12 +4157,12 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>32.26</t>
+          <t>48.39</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4164,7 +4172,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4174,22 +4182,22 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1822/id-45585830/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-62m2-aluguel-RS3000-id-2911451041/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4205,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Josinildo Imóveis</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -4205,22 +4213,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 92 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 42 m² · Torre</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Avenida Carlos De Lima Cavalcante</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4235,7 +4243,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4245,17 +4253,17 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4265,22 +4273,22 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS3000/id-42437394/</t>
+          <t>https://josinildoimoveis.com.br/imovel/edf-green-life-torre/PARJI03</t>
         </is>
       </c>
     </row>
@@ -4296,12 +4304,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rua Cardeal Arcoverde, 276</t>
+          <t>Rua Amélia, 623</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4311,32 +4319,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2332.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>550.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>93.75</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4356,22 +4364,22 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS2332/id-46081872/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-RS3200/id-45197779/</t>
         </is>
       </c>
     </row>
@@ -4379,30 +4387,30 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Newville</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 59 m² · Santo Amaro</t>
+          <t>Apartamento · 2 quartos · 52 m² · Torre</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rua Dom Pedro Henrique</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4417,7 +4425,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4427,42 +4435,42 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>50.85</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-santo-amaro-bairros-recife-com-garagem-59m2-aluguel-RS3000-id-2913400521/?source=ranking%2Crp</t>
+          <t>https://newville.com.br/imovel/apartamento_2_quartos--torre--recife--pe--locacao--cod-6391</t>
         </is>
       </c>
     </row>
@@ -4470,30 +4478,30 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 68 m² · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 38 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4508,7 +4516,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4518,17 +4526,17 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>44.12</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4538,22 +4546,22 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-68m2-aluguel-RS3000-id-2913457037/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-1-quarto-alugar-38m2-boa-vista-recife--pe_33378812</t>
         </is>
       </c>
     </row>
@@ -4561,30 +4569,30 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 60 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 40 m² · Santana</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rua Professor Francisco Xavier Paes Barreto</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Santana</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4599,7 +4607,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4609,42 +4617,42 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3000-id-2912144534/?source=ranking%2Crp</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/70-rua-samuel-de-farias/850091105-39</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4660,7 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Zap Imóveis</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4660,22 +4668,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 34 m² · Boa Vista</t>
+          <t>Apartamento · 1 quarto · 35 m² · Encruzilhada</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Avenida Governador Agamenon Magalhães</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4690,7 +4698,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4700,7 +4708,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>91.43</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4710,32 +4718,32 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-1-quarto-com-piscina-boa-vista-recife-pe-34m2-id-2913394619/?source=ranking%2Crp</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/68-rua-engenheiro-sampaio/850701030-102</t>
         </is>
       </c>
     </row>
@@ -4743,55 +4751,55 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 43 m² · Santana</t>
+          <t>Apartamento · 1 quarto · 35 m² · Paissandu</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rua Nestor Silva</t>
+          <t>Rua Estácio Coimbra</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Santana</t>
+          <t>Paissandu</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>3020.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>70.23</t>
+          <t>91.43</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4811,22 +4819,22 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-santana-bairros-recife-com-garagem-43m2-aluguel-RS3000-id-2913452276/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-paissandu-bairros-recife-com-garagem-35m2-aluguel-RS3200-id-2910117517/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4842,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Josinildo Imóveis</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -4842,22 +4850,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 42 m² · Torre</t>
+          <t>Apartamento · 1 quarto · 37 m² · Espinheiro</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Barão de Itamaracá</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4872,7 +4880,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4882,17 +4890,17 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>86.49</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4902,22 +4910,22 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>https://josinildoimoveis.com.br/imovel/edf-green-life-torre/PARJI03</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-espinheiro-bairros-recife-com-garagem-37m2-aluguel-RS3200-id-2913453536/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4925,25 +4933,25 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rua Amélia, 623</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4973,19 +4981,19 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O50" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -4993,22 +5001,22 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-RS3200/id-45197779/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3200-id-2906163316/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5016,25 +5024,25 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Newville</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 52 m² · Torre</t>
+          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5064,7 +5072,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5074,7 +5082,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5084,22 +5092,22 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>https://newville.com.br/imovel/apartamento_2_quartos--torre--recife--pe--locacao--cod-6391</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3200-id-2686319323/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5115,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -5115,7 +5123,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 38 m² · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 70 m² · 1 vaga · Casa Amarela</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5125,47 +5133,47 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>237.0</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3202.0</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>45.74</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5175,22 +5183,22 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-1-quarto-alugar-38m2-boa-vista-recife--pe_33378812</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-amarela-70m2-RS2000/id-43758789/</t>
         </is>
       </c>
     </row>
@@ -5198,30 +5206,30 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 37 m² · Espinheiro</t>
+          <t>Apartamento · 3 quartos · 66 m² · 1 vaga · Campo Grande</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rua Barão de Itamaracá</t>
+          <t>Rua Barão De Vera Cruz</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Campo Grande</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5236,7 +5244,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5246,19 +5254,19 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>86.49</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O53" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -5266,22 +5274,22 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-espinheiro-bairros-recife-com-garagem-37m2-aluguel-RS3200-id-2913453536/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-campo-grande-79m2-RS3300/id-44353442/</t>
         </is>
       </c>
     </row>
@@ -5297,22 +5305,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 58 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Rua Pereira Simões</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5327,7 +5335,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5337,7 +5345,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5357,22 +5365,22 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3200-id-2906163316/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-58m2-aluguel-RS3300-id-2913435980/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5380,20 +5388,20 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 57 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 65 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rua Pereira Simões</t>
+          <t>Rua Eduardo De Moraes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5403,32 +5411,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>422.0</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3317.0</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>56.14</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5438,32 +5446,32 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>57.0</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-57m2-aluguel-RS3200-id-2901326206/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-1038m2-RS2700/id-27611651/</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5479,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -5479,7 +5487,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · 1 vaga · Casa Amarela</t>
+          <t>Apartamento · 2 quartos · 75 m² · Graças</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5489,27 +5497,27 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>588.0</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>237.0</t>
+          <t>109.04</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>3202.0</t>
+          <t>3397.04</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5519,7 +5527,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>45.74</t>
+          <t>45.29</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5529,7 +5537,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5539,22 +5547,22 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-amarela-70m2-RS2000/id-43758789/</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/3178/apartamento-2-quartos-celina-gonçalves-de-oliveira-graças-recife/</t>
         </is>
       </c>
     </row>
@@ -5562,30 +5570,30 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 66 m² · 1 vaga · Campo Grande</t>
+          <t>Apartamento · 1 quarto · 37 m² · Rosarinho</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rua Barão De Vera Cruz</t>
+          <t>Rua Doutor José Maria</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Campo Grande</t>
+          <t>Rosarinho</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3400.0</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5600,7 +5608,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3400.0</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5610,12 +5618,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>91.89</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -5625,27 +5633,27 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-campo-grande-79m2-RS3300/id-44353442/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-rosarinho-bairros-recife-com-garagem-37m2-aluguel-RS3400-id-2913418918/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5653,20 +5661,20 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 58 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 58 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rua Pereira Simões</t>
+          <t>Rua Pereira Simões, 1529 - 2</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5676,7 +5684,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5691,7 +5699,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5701,7 +5709,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>60.34</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5711,7 +5719,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5726,17 +5734,17 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-58m2-aluguel-RS3300-id-2913435980/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-59m2-RS3500/id-45711136/</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5760,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 65 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 57 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rua Eduardo De Moraes</t>
+          <t>Rua Francisco Ambrósio De Barros Leite, 1225</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5767,32 +5775,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>422.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>3317.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>51.03</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5812,22 +5820,22 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-1038m2-RS2700/id-27611651/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-RS3500/id-42986293/</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5843,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -5843,47 +5851,47 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 75 m² · Graças</t>
+          <t>Apartamento · 2 quartos · 50 m² · 1 vaga · Torre</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Real Da Torre</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>588.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>109.04</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>3397.04</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>45.29</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5893,7 +5901,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5903,22 +5911,22 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/3178/apartamento-2-quartos-celina-gonçalves-de-oliveira-graças-recife/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-50m2-RS3500/id-46933917/</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5934,7 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Chaves na Mão Recife, Rogério Corretor</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -5934,22 +5942,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 37 m² · Rosarinho</t>
+          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rua Doutor José Maria</t>
+          <t>Rua Cardeal Arcoverde, 1</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosarinho</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>3400.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5964,7 +5972,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>3400.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -5974,7 +5982,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>91.89</t>
+          <t>106.06</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5989,27 +5997,27 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-rosarinho-bairros-recife-com-garagem-37m2-aluguel-RS3400-id-2913418918/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS3500/id-45844382/</t>
         </is>
       </c>
     </row>
@@ -6017,35 +6025,35 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · Ilha do Leite</t>
+          <t>Apartamento · 2 quartos · 70 m² · Tamarineira</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rua Jornalista Trajano Chacon</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ilha do Leite</t>
+          <t>Tamarineira</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>3450.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6055,52 +6063,52 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>3450.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>95.83</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-ilha-do-leite-bairros-recife-com-garagem-36m2-aluguel-RS3450-id-2913191116/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-70m2-tamarineira-recife--pe_33364198</t>
         </is>
       </c>
     </row>
@@ -6108,25 +6116,25 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 58 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 77 m² · Torre</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rua Pereira Simões, 1529 - 2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -6156,17 +6164,17 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>60.34</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6176,22 +6184,22 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-59m2-RS3500/id-45711136/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-77m2-torre-recife--pe_33379670</t>
         </is>
       </c>
     </row>
@@ -6199,7 +6207,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -6207,17 +6215,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 57 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 82 m² · Casa Forte</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rua Francisco Ambrósio De Barros Leite, 1225</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Forte</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -6227,7 +6235,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6242,12 +6250,12 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>42.68</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6257,7 +6265,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6267,7 +6275,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -6282,7 +6290,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-RS3500/id-42986293/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-82m2-casa-forte-recife--pe_33364920</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6298,7 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -6298,17 +6306,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · 1 vaga · Torre</t>
+          <t>Apartamento · 3 quartos · 83 m² · Aflitos</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rua Real Da Torre</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -6338,17 +6346,17 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>42.09</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -6358,22 +6366,22 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>83.15</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-50m2-RS3500/id-46933917/</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/850191006-42</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6389,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife, Rogério Corretor</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -6389,17 +6397,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 2 quartos · 59 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rua Cardeal Arcoverde, 1</t>
+          <t>Rua Pereira Simões</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -6429,42 +6437,42 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>106.06</t>
+          <t>59.32</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS3500/id-45844382/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-59m2-aluguel-RS3500-id-2905566215/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -6472,25 +6480,25 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · Tamarineira</t>
+          <t>Apartamento · 2 quartos · 56 m² · Torreão</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Cândido Lacerda</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tamarineira</t>
+          <t>Torreão</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -6500,17 +6508,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3502.0</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6520,7 +6528,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>62.54</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6530,7 +6538,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6540,22 +6548,22 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-70m2-tamarineira-recife--pe_33364198</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-torreao-bairros-recife-com-garagem-56m2-aluguel-RS3500-id-2913434332/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -6563,65 +6571,65 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>CTI Imobiliária, Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · Torre</t>
+          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Boa Vista</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos De Lima Cavalcanti, 60</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>553.0</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>174.0</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3527.0</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>80.16</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6631,7 +6639,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -6646,7 +6654,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-77m2-torre-recife--pe_33379670</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6519</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6662,7 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>CTI Imobiliária</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -6662,7 +6670,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 82 m² · Casa Forte</t>
+          <t>Apartamento · 2 quartos · 41 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6672,27 +6680,27 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Casa Forte</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>550.0</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3542.0</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6702,7 +6710,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>42.68</t>
+          <t>86.39</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -6722,22 +6730,22 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-82m2-casa-forte-recife--pe_33364920</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6210</t>
         </is>
       </c>
     </row>
@@ -6745,30 +6753,30 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Parnamirim</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Avenida Parnamirim, 375</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6783,7 +6791,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -6793,42 +6801,42 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-60m2-aluguel-RS3500-id-2904577437/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-32m2-RS3600/id-41530823/</t>
         </is>
       </c>
     </row>
@@ -6836,45 +6844,45 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 56 m² · Torreão</t>
+          <t>Apartamento · 1 quarto · 34 m² · 1 vaga · Parnamirim</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rua Cândido Lacerda</t>
+          <t>Avenida Parnamirim, 375</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Torreão</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>600.0</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>3502.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -6884,42 +6892,42 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>62.54</t>
+          <t>105.88</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>56.0</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-torreao-bairros-recife-com-garagem-56m2-aluguel-RS3500-id-2913434332/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-55m2-RS3000/id-46882194/</t>
         </is>
       </c>
     </row>
@@ -6927,55 +6935,55 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CTI Imobiliária, Chaves na Mão Recife</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Torre</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos De Lima Cavalcanti, 60</t>
+          <t>Rua José De Holanda, 854</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>553.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>3527.0</t>
+          <t>3601.0</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>80.16</t>
+          <t>81.84</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7000,17 +7008,17 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6519</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-RS3600/id-40119104/</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7026,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CTI Imobiliária</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -7026,7 +7034,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 41 m² · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 51 m² · Aflitos</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7036,37 +7044,37 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3699.0</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>550.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>3542.0</t>
+          <t>3699.0</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>86.39</t>
+          <t>72.53</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -7086,22 +7094,22 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6210</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/307-rua-manuel-de-carvalho/850701030-101</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7117,7 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -7117,27 +7125,27 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Parnamirim</t>
+          <t>Apartamento · 3 quartos · Encruzilhada</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Avenida Parnamirim, 375</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3700.0</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7147,27 +7155,27 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3700.0</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7177,22 +7185,22 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-32m2-RS3600/id-41530823/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-encruzilhada-recife--pe_33362592</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7208,7 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -7208,27 +7216,27 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 34 m² · 1 vaga · Parnamirim</t>
+          <t>Apartamento · 3 quartos · Rosarinho</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Avenida Parnamirim, 375</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Rosarinho</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3800.0</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>600.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7238,27 +7246,27 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3800.0</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>105.88</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7268,7 +7276,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -7283,7 +7291,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-55m2-RS3000/id-46882194/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-rosarinho-recife--pe_33388298</t>
         </is>
       </c>
     </row>
@@ -7291,30 +7299,30 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Apartamento · 4 quartos · 120 m² · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 70 m² · Encruzilhada</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rua Dom Carlos Coelho</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3800.0</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -7329,7 +7337,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3800.0</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7339,17 +7347,17 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>54.29</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7359,22 +7367,22 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-boa-vista-bairros-recife-com-garagem-120m2-aluguel-RS3600-id-2913416134/?source=ranking%2Crp</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/edf-arcadia/850091082-77</t>
         </is>
       </c>
     </row>
@@ -7382,35 +7390,35 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · Encruzilhada</t>
+          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Joana D'Arc Sampaio</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>3700.0</t>
+          <t>3900.0</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7420,7 +7428,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>3700.0</t>
+          <t>3901.0</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -7430,42 +7438,42 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-encruzilhada-recife--pe_33362592</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3900-id-2913026520/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -7473,7 +7481,7 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -7481,7 +7489,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · Rosarinho</t>
+          <t>Apartamento · 2 quartos · 51 m² · Aflitos</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7491,12 +7499,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosarinho</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>3800.0</t>
+          <t>3990.0</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -7511,7 +7519,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>3800.0</t>
+          <t>3990.0</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -7521,12 +7529,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>78.24</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -7541,22 +7549,22 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-rosarinho-recife--pe_33388298</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/307-manuel-de-carvalho-edificio-praca-das-cerejeiras/850721013-37</t>
         </is>
       </c>
     </row>
@@ -7564,7 +7572,7 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda, Rogério Corretor</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -7572,12 +7580,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 145 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Rua Joana D'Arc Sampaio</t>
+          <t>Avenida Min. Marcos Freire, 3495</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -7587,12 +7595,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>3900.0</t>
+          <t>4100.0</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7602,27 +7610,27 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>3901.0</t>
+          <t>4100.0</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -7632,22 +7640,22 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3900-id-2913026520/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4100/id-46901493/</t>
         </is>
       </c>
     </row>
@@ -7663,12 +7671,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 74 m² · 1 vaga · Aflitos</t>
+          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Aflitos</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Rua Da Angustura, 195</t>
+          <t>Avenida Conselheiro Rosa E Silva, 801</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -7678,42 +7686,42 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>4141.0</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>1200.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>4091.0</t>
+          <t>4142.0</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>55.28</t>
+          <t>75.31</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -7723,22 +7731,22 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-aflitos-74m2-RS2700/id-46898128/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-aflitos-55m2-RS4141/id-45283901/</t>
         </is>
       </c>
     </row>
@@ -7746,35 +7754,35 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Rogério Corretor</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 145 m² · 2 vagas · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 43 m² · Casa Amarela</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Avenida Min. Marcos Freire, 3495</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>4100.0</t>
+          <t>4200.0</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7784,27 +7792,27 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>4100.0</t>
+          <t>4200.0</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>97.67</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -7814,22 +7822,22 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4100/id-46901493/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-43m2-casa-amarela-recife--pe_33376830</t>
         </is>
       </c>
     </row>
@@ -7837,7 +7845,7 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -7845,22 +7853,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Aflitos</t>
+          <t>Apartamento · 2 quartos · 58 m² · Espinheiro</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Avenida Conselheiro Rosa E Silva, 801</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>4141.0</t>
+          <t>4200.0</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -7875,7 +7883,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>4142.0</t>
+          <t>4200.0</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -7885,7 +7893,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>75.31</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -7895,32 +7903,32 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>58.0</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-aflitos-55m2-RS4141/id-45283901/</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/862-rua-da-hora/850251129-67</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7936,7 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Rogério Corretor</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -7936,7 +7944,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 43 m² · Casa Amarela</t>
+          <t>Apartamento · 2 quartos · 80 m² · Aflitos</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7946,17 +7954,17 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>4200.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7966,7 +7974,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>4200.0</t>
+          <t>4350.0</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -7976,7 +7984,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>97.67</t>
+          <t>54.38</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -7996,22 +8004,22 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-43m2-casa-amarela-recife--pe_33376830</t>
+          <t>https://www.rogeriocorretor.com/imovel/apartamento-2-quartos-aflitos-recife-1-vaga-80m2-code-695</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8027,7 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Rogério Corretor</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -8027,27 +8035,27 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Aflitos</t>
+          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos De Lima Cavalcante</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>1195.0</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8057,7 +8065,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>4350.0</t>
+          <t>4395.0</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -8067,7 +8075,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>54.38</t>
+          <t>79.91</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -8077,7 +8085,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -8087,7 +8095,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -8102,7 +8110,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>https://www.rogeriocorretor.com/imovel/apartamento-2-quartos-aflitos-recife-1-vaga-80m2-code-695</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-55m2-RS3200/id-46174975/</t>
         </is>
       </c>
     </row>
@@ -8118,12 +8126,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 85 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos De Lima Cavalcante</t>
+          <t>Avenida Ministro Marcos Freire</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -8133,12 +8141,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1195.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8148,27 +8156,27 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>4395.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>79.91</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -8178,7 +8186,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -8193,7 +8201,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-55m2-RS3200/id-46174975/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-110m2-RS4500/id-42417501/</t>
         </is>
       </c>
     </row>
@@ -8201,15 +8209,15 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · 2 vagas · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 97 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8249,7 +8257,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>52.94</t>
+          <t>46.39</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -8269,7 +8277,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -8284,7 +8292,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-110m2-RS4500/id-42417501/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4500/id-46421413/</t>
         </is>
       </c>
     </row>
@@ -8292,25 +8300,25 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 97 m² · 2 vagas · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 56 m² · 1 vaga · Espinheiro</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Avenida Ministro Marcos Freire</t>
+          <t>Rua São Salvador, 200</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -8340,17 +8348,17 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>46.39</t>
+          <t>80.36</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -8360,22 +8368,22 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4500/id-46421413/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-espinheiro-70m2-RS4500/id-46923849/</t>
         </is>
       </c>
     </row>
@@ -8383,7 +8391,7 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Rogério Corretor</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -8391,17 +8399,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 56 m² · 1 vaga · Espinheiro</t>
+          <t>Apartamento · 4 quartos · 90 m² · Torre</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rua São Salvador, 200</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -8431,17 +8439,17 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>80.36</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -8451,22 +8459,22 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-espinheiro-70m2-RS4500/id-46923849/</t>
+          <t>https://www.rogeriocorretor.com/imovel/casa-4-quartos-torre-recife-90m2-code-736</t>
         </is>
       </c>
     </row>
@@ -8474,30 +8482,30 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Rogério Corretor</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Apartamento · 4 quartos · 90 m² · Torre</t>
+          <t>Apartamento · 4 quartos · 87 m² · Rosarinho</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Hipólito Braga</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Rosarinho</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>4590.0</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -8512,7 +8520,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>4590.0</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -8522,7 +8530,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>52.76</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -8532,7 +8540,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -8542,22 +8550,22 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>https://www.rogeriocorretor.com/imovel/casa-4-quartos-torre-recife-90m2-code-736</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-rosarinho-bairros-recife-com-garagem-87m2-aluguel-RS4590-id-2913430257/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -8565,7 +8573,7 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Zap Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -8573,22 +8581,22 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 51 m² · Graças</t>
+          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Parnamirim</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Rua Amélia</t>
+          <t>Avenida Parnamirim</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>4700.0</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -8603,7 +8611,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>4700.0</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -8613,7 +8621,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>78.33</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -8623,32 +8631,32 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-mobiliado-gracas-recife-pe-51m2-id-2912084621/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-parnamirim-RS4700/id-43942857/</t>
         </is>
       </c>
     </row>
@@ -8656,30 +8664,30 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Apartamento · 4 quartos · 87 m² · Rosarinho</t>
+          <t>Apartamento · 3 quartos · 89 m² · Torre</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rua Hipólito Braga</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rosarinho</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>4590.0</t>
+          <t>5500.0</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -8694,7 +8702,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>4590.0</t>
+          <t>5500.0</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -8704,17 +8712,17 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>52.76</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -8724,202 +8732,20 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-rosarinho-bairros-recife-com-garagem-87m2-aluguel-RS4590-id-2913430257/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr"/>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Recife</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>1</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Parnamirim</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Avenida Parnamirim</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Parnamirim</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>4700.0</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>4700.0</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>78.33</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R92" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-parnamirim-RS4700/id-43942857/</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr"/>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Portal CRECI Brasil</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>1</v>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 89 m² · Torre</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Torre</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>5500.0</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>5500.0</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>61.8</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>89.0</t>
-        </is>
-      </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R93" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="S93" t="inlineStr">
         <is>
           <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-89m2-torre-recife--pe_33386591</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S89"/>
+  <dimension ref="A1:S91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -561,22 +561,22 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 35 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Rua Nereu Gomes Maciel</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2499.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2499.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -601,232 +601,224 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>35.0</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/flat-1-quartos-bairro-novo-bairros-olinda-com-garagem-35m2-aluguel-RS2500-id-2901073105/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Olinda</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 58 m² · 1 vaga · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Rua Norberto Pessoa, 238</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1300.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1300.0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>22.41</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-70m2-aluguel-RS2499-id-2903057019/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>58.0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1300/id-46461545/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Olinda</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Apartamento · 1 quarto · 41 m² · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Rua Professor Marculino Botelho, 404</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 60 m² · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Rua Professor Francisco Xavier Paes Barreto</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>3001.0</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>3001.0</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>50.02</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3001-id-2912144534/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 4 quartos · 160 m² · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3500.0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3500.0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>21.88</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>160.0</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-casa-caiada-bairros-olinda-com-garagem-160m2-aluguel-RS3500-id-2909290334/?source=ranking%2Crp</t>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>34.15</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-pe-olinda-bairro-novo-41m2-RS1200/id-45673360/</t>
         </is>
       </c>
     </row>
@@ -834,7 +826,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -842,57 +834,57 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 58 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 50 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rua Norberto Pessoa, 238</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1300.0</t>
+          <t>1100.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>97.38</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1300.0</t>
+          <t>1447.38</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -902,22 +894,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1300/id-46461545/</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/224/apartamento-2-quartos-jose-mariano-boa-vista-recife/</t>
         </is>
       </c>
     </row>
@@ -925,55 +917,55 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 41 m² · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 30 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rua Professor Marculino Botelho, 404</t>
+          <t>Rua Carlos Nigro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1200.0</t>
+          <t>1499.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1400.0</t>
+          <t>1499.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>34.15</t>
+          <t>49.97</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -993,22 +985,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-pe-olinda-bairro-novo-41m2-RS1200/id-45673360/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-30m2-aluguel-RS1499-id-2912697216/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1016,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · Boa Vista</t>
+          <t>Apartamento · 1 quarto · 40 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1044,17 +1036,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>505.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>97.38</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1447.38</t>
+          <t>1677.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1064,42 +1056,42 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/224/apartamento-2-quartos-jose-mariano-boa-vista-recife/</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/2553/apartamento-1-quarto-arpege-boa-vista-recife/</t>
         </is>
       </c>
     </row>
@@ -1107,30 +1099,30 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rua Carlos Nigro</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1499.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1145,7 +1137,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1499.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1155,17 +1147,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>49.97</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1175,22 +1167,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-30m2-aluguel-RS1499-id-2912697216/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1700/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -1198,35 +1190,35 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 52 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 33 m² · Encruzilhada</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rua Caetano Ribeiro</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1300.0</t>
+          <t>1750.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1236,27 +1228,27 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1550.0</t>
+          <t>1750.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>29.81</t>
+          <t>53.03</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1266,22 +1258,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-52m2-aluguel-RS1300-id-2911238418/?source=ranking%2Crp</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/123-rua-carlos-borromeu-de-frente-para-o-mercado-da-encruzilhada/850471068-78</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1289,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 40 m² · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 50 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1307,27 +1299,27 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1100.0</t>
+          <t>1450.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>505.0</t>
+          <t>405.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>80.96</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1677.0</t>
+          <t>1935.96</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1337,12 +1329,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>38.72</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1357,22 +1349,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/2553/apartamento-1-quarto-arpege-boa-vista-recife/</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/6691/apartamento-2-quartos-santo-amaro-recife/</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1380,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Rua Coronel Alberto Lundgren, 604</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1403,42 +1395,42 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1448,22 +1440,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1700/id-45733416/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS1800/id-46397377/</t>
         </is>
       </c>
     </row>
@@ -1471,45 +1463,45 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · Santo Amaro</t>
+          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Doutor José Augusto Moreira</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1450.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>405.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>80.96</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1935.96</t>
+          <t>2002.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1519,7 +1511,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>38.72</t>
+          <t>33.37</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1529,7 +1521,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1539,22 +1531,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/6691/apartamento-2-quartos-santo-amaro-recife/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-60m2-aluguel-RS2000-id-2910983844/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1577,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1600,7 +1592,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1610,7 +1602,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1635,17 +1627,17 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS1800/id-46397377/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS2000/id-46397376/</t>
         </is>
       </c>
     </row>
@@ -1661,47 +1653,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 65 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Avenida Doutor José Augusto Moreira</t>
+          <t>Rua Professor José Cândido Pessoa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2002.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>33.37</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1711,7 +1703,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1721,22 +1713,22 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-60m2-aluguel-RS2000-id-2910983844/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-65m2-aluguel-RS2200-id-2897302602/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1744,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rua Coronel Alberto Lundgren, 604</t>
+          <t>Rua Professor José Cândido Pessoa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1767,22 +1759,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>684.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2477.0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1792,7 +1784,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>68.81</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1812,22 +1804,22 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS2000/id-46397376/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-720m2-RS1700/id-43805924/</t>
         </is>
       </c>
     </row>
@@ -1843,22 +1835,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 65 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 70 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rua Professor José Cândido Pessoa</t>
+          <t>Rua Nereu Gomes Maciel</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2499.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1873,7 +1865,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2499.0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1883,42 +1875,42 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>33.85</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-65m2-aluguel-RS2200-id-2897302602/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-70m2-aluguel-RS2499-id-2903057019/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1934,59 +1926,59 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rua Professor José Cândido Pessoa</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>684.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2477.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>68.81</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O17" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -1994,22 +1986,22 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-720m2-RS1700/id-43805924/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -2017,7 +2009,7 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2025,52 +2017,52 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 49 m² · Espinheiro</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua Da Hora, 235</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2085,22 +2077,22 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-pe-recife-espinheiro-49m2-RS2000/id-44279997/</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2100,7 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2116,27 +2108,27 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 49 m² · Espinheiro</t>
+          <t>Apartamento · 1 quarto · 31 m² · Parnamirim</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rua Da Hora, 235</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>500.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2151,22 +2143,22 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>80.65</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2176,22 +2168,22 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-pe-recife-espinheiro-49m2-RS2000/id-44279997/</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/n%C2%BA-50-rua-condado-perto-do-cafe-sao-braz/850091040-261</t>
         </is>
       </c>
     </row>
@@ -2298,17 +2290,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 30 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2338,17 +2330,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2358,22 +2350,22 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-bairros-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-30m2-aluguel-RS2500-id-2912752809/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2745,7 +2737,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Zap Imóveis</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2753,37 +2745,37 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · Aflitos</t>
+          <t>Apartamento · 1 quarto · 48 m² · Graças</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Esmeraldino Bandeira</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>1778.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>755.0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2691.0</t>
+          <t>2613.0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2793,17 +2785,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>54.44</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2813,7 +2805,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2828,7 +2820,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-aflitos-recife--pe_33374631</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-1-quarto-gracas-recife-pe-48m2-id-2821571718/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2828,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2844,27 +2836,27 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · Aflitos</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa Monteiro, 93</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1526.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1178.0</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2874,7 +2866,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2704.0</t>
+          <t>2691.0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2884,17 +2876,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2904,7 +2896,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2919,7 +2911,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1526/id-45586419/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-aflitos-recife--pe_33374631</t>
         </is>
       </c>
     </row>
@@ -2927,7 +2919,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CTI Imobiliária</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2935,37 +2927,37 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Graças</t>
+          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Otaviano Pessoa Monteiro, 93</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1600.0</t>
+          <t>1526.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>953.0</t>
+          <t>1178.0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2747.0</t>
+          <t>2704.0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2975,7 +2967,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>34.34</t>
+          <t>29.08</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2985,7 +2977,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2995,22 +2987,22 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-gracas-recife-pe/6882</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1526/id-45586419/</t>
         </is>
       </c>
     </row>
@@ -3018,55 +3010,55 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>CTI Imobiliária</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 63 m² · Aflitos</t>
+          <t>Apartamento · 2 quartos · 80 m² · Graças</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rua Samuel Campelo</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>1600.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>953.0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>194.0</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>2747.0</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>34.34</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3076,7 +3068,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3086,22 +3078,22 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>64</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-aflitos-bairros-recife-com-garagem-63m2-aluguel-RS2800-id-2912913421/?source=ranking%2Crp</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-gracas-recife-pe/6882</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3101,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -3117,17 +3109,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 63 m² · Aflitos</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Rua Samuel Campelo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3157,7 +3149,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3177,22 +3169,22 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-60m2-aluguel-RS2800-id-2912116616/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-aflitos-bairros-recife-com-garagem-63m2-aluguel-RS2800-id-2912913421/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3208,17 +3200,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 60 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3248,42 +3240,42 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>36.0</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-36m2-aluguel-RS2800-id-2705654338/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-60m2-aluguel-RS2800-id-2912116616/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3291,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Apartamento · 40 m² · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 36 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3309,7 +3301,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3339,12 +3331,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3354,27 +3346,27 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/kitnet-casa-caiada-bairros-olinda-com-garagem-40m2-aluguel-RS2800-id-2910716413/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-36m2-aluguel-RS2800-id-2705654338/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3390,17 +3382,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 71 m² · Casa Caiada</t>
+          <t>Apartamento · 40 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rua Gildo Branco</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3430,27 +3422,27 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3465,7 +3457,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-71m2-aluguel-RS2800-id-2911301943/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/kitnet-casa-caiada-bairros-olinda-com-garagem-40m2-aluguel-RS2800-id-2910716413/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3465,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Zap Imóveis</t>
+          <t>Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3481,82 +3473,82 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 42 m² · Casa Forte</t>
+          <t>Apartamento · 3 quartos · 71 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rua Engenheiro Oscar Ferreira</t>
+          <t>Rua Gildo Branco</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Casa Forte</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>650.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2804.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>66.76</t>
+          <t>39.44</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-1-quarto-mobiliado-casa-forte-recife-pe-42m2-id-2876277098/?source=ranking%2Crp</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-3-quartos-com-piscina-casa-caiada-olinda-pe-71m2-id-2911301943/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3564,35 +3556,35 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>CTI Imobiliária</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 71 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rua Gildo Branco</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2850.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>380.0</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3602,27 +3594,27 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2850.0</t>
+          <t>2880.0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>40.14</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3632,22 +3624,22 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-71m2-aluguel-RS2850-id-2911876830/?source=ranking%2Crp</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-torre-recife-pe/1353</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3647,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CTI Imobiliária</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3678,7 +3670,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3688,12 +3680,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>176.42</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2880.0</t>
+          <t>2956.42</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3703,7 +3695,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3738,7 +3730,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-torre-recife-pe/1353</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/6596/apartamento-2-quartos-torre-recife/</t>
         </is>
       </c>
     </row>
@@ -3746,55 +3738,55 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
+          <t>Apartamento · 2 quartos · 42 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Ulisses Tenório de Albuquerque</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2998.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>380.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>176.42</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2956.42</t>
+          <t>2998.0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>71.38</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3804,7 +3796,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3814,22 +3806,22 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/6596/apartamento-2-quartos-torre-recife/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-42m2-aluguel-RS2998-id-2911376544/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3837,20 +3829,20 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 42 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 40 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rua Ulisses Tenório de Albuquerque</t>
+          <t>Avenida Governador Carlos De Lima Cavalcante, 2595</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3860,7 +3852,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2998.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3875,7 +3867,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2998.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3885,12 +3877,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>71.38</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3905,22 +3897,22 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-42m2-aluguel-RS2998-id-2911376544/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-40m2-RS3000/id-45710865/</t>
         </is>
       </c>
     </row>
@@ -3936,12 +3928,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 40 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 42 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos De Lima Cavalcante, 2595</t>
+          <t>Avenida Doutor José Augusto Moreira, 900</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3976,7 +3968,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3996,7 +3988,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -4011,7 +4003,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-40m2-RS3000/id-45710865/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-RS3000/id-44380568/</t>
         </is>
       </c>
     </row>
@@ -4027,12 +4019,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 42 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Avenida Doutor José Augusto Moreira, 900</t>
+          <t>Rua Otaviano Pessoa Monteiro, 93</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4042,44 +4034,44 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
+          <t>1822.0</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1178.0</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
           <t>3000.0</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>32.26</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O40" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -4087,7 +4079,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -4102,7 +4094,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-RS3000/id-44380568/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1822/id-45585830/</t>
         </is>
       </c>
     </row>
@@ -4118,12 +4110,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 92 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa Monteiro, 93</t>
+          <t>Avenida Carlos De Lima Cavalcante</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4133,12 +4125,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1822.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1178.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4153,24 +4145,24 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>32.26</t>
+          <t>32.61</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O41" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -4178,7 +4170,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -4193,7 +4185,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1822/id-45585830/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS3000/id-42437394/</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4193,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -4209,82 +4201,82 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 92 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Avenida Carlos De Lima Cavalcante</t>
+          <t>Rua Cardeal Arcoverde, 276</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
+          <t>2332.0</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>550.0</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>118.0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
           <t>3000.0</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>93.75</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS3000/id-42437394/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS2332/id-46081872/</t>
         </is>
       </c>
     </row>
@@ -4292,40 +4284,40 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 2 quartos · 68 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rua Cardeal Arcoverde, 276</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2332.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>550.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4335,22 +4327,22 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>93.75</t>
+          <t>44.12</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4360,22 +4352,22 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS2332/id-46081872/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-68m2-aluguel-RS3000-id-2913457037/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4375,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -4391,22 +4383,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 59 m² · Santo Amaro</t>
+          <t>Apartamento · 3 quartos · 60 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rua Dom Pedro Henrique</t>
+          <t>Rua Professor Francisco Xavier Paes Barreto</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4421,7 +4413,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4431,42 +4423,42 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>50.85</t>
+          <t>50.02</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-santo-amaro-bairros-recife-com-garagem-59m2-aluguel-RS3000-id-2913400521/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3001-id-2912144534/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4474,30 +4466,30 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Josinildo Imóveis</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 68 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 42 m² · Torre</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4512,7 +4504,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4522,7 +4514,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>44.12</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4532,7 +4524,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4542,22 +4534,22 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-68m2-aluguel-RS3000-id-2913457037/?source=ranking%2Crp</t>
+          <t>https://josinildoimoveis.com.br/imovel/edf-green-life-torre/PARJI03</t>
         </is>
       </c>
     </row>
@@ -4565,30 +4557,30 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 62 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa Monteiro</t>
+          <t>Rua Amélia, 623</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4603,7 +4595,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4613,17 +4605,17 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>48.39</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4633,22 +4625,22 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-62m2-aluguel-RS3000-id-2911451041/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-RS3200/id-45197779/</t>
         </is>
       </c>
     </row>
@@ -4656,30 +4648,30 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Newville</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 60 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 52 m² · Torre</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4694,7 +4686,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4704,17 +4696,17 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4724,22 +4716,22 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3000-id-2859906255/?source=ranking%2Crp</t>
+          <t>https://newville.com.br/imovel/apartamento_2_quartos--torre--recife--pe--locacao--cod-6391</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4739,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Josinildo Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -4755,7 +4747,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 42 m² · Torre</t>
+          <t>Apartamento · 1 quarto · 38 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4765,12 +4757,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4785,7 +4777,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4795,12 +4787,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4815,22 +4807,22 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>https://josinildoimoveis.com.br/imovel/edf-green-life-torre/PARJI03</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-1-quarto-alugar-38m2-boa-vista-recife--pe_33378812</t>
         </is>
       </c>
     </row>
@@ -4838,25 +4830,25 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 1 quarto · 37 m² · Espinheiro</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rua Amélia, 623</t>
+          <t>Rua Barão de Itamaracá</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4886,7 +4878,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>86.49</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4906,22 +4898,22 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-RS3200/id-45197779/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-espinheiro-bairros-recife-com-garagem-37m2-aluguel-RS3200-id-2913453536/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4929,25 +4921,25 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Newville</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 52 m² · Torre</t>
+          <t>Apartamento · 1 quarto · 35 m² · Paissandu</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Estácio Coimbra</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Paissandu</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4977,17 +4969,17 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>91.43</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4997,22 +4989,22 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>https://newville.com.br/imovel/apartamento_2_quartos--torre--recife--pe--locacao--cod-6391</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-paissandu-bairros-recife-com-garagem-35m2-aluguel-RS3200-id-2910117517/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5020,25 +5012,25 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 38 m² · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5068,19 +5060,19 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="O51" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -5088,22 +5080,22 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-1-quarto-alugar-38m2-boa-vista-recife--pe_33378812</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3200-id-2906163316/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5103,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -5119,17 +5111,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 37 m² · Espinheiro</t>
+          <t>Apartamento · 2 quartos · 58 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rua Barão de Itamaracá</t>
+          <t>Rua Pereira Simões</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5159,42 +5151,42 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>86.49</t>
+          <t>55.17</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-espinheiro-bairros-recife-com-garagem-37m2-aluguel-RS3200-id-2913453536/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-58m2-aluguel-RS3200-id-2907384719/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5202,55 +5194,55 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 70 m² · 1 vaga · Casa Amarela</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>237.0</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3202.0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>45.74</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5260,7 +5252,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5270,22 +5262,22 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3200-id-2906163316/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-amarela-70m2-RS2000/id-43758789/</t>
         </is>
       </c>
     </row>
@@ -5301,57 +5293,57 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · 1 vaga · Casa Amarela</t>
+          <t>Apartamento · 3 quartos · 66 m² · 1 vaga · Campo Grande</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Barão De Vera Cruz</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Campo Grande</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>237.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>3202.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>45.74</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5361,7 +5353,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -5376,7 +5368,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-amarela-70m2-RS2000/id-43758789/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-campo-grande-79m2-RS3300/id-44353442/</t>
         </is>
       </c>
     </row>
@@ -5384,25 +5376,25 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 66 m² · 1 vaga · Campo Grande</t>
+          <t>Apartamento · 2 quartos · 58 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rua Barão De Vera Cruz</t>
+          <t>Rua Pereira Simões</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Campo Grande</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5432,12 +5424,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -5452,22 +5444,22 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-campo-grande-79m2-RS3300/id-44353442/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-58m2-aluguel-RS3300-id-2913435980/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5475,20 +5467,20 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 58 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 65 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rua Pereira Simões</t>
+          <t>Rua Eduardo De Moraes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5498,32 +5490,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>422.0</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3317.0</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5543,22 +5535,22 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-58m2-aluguel-RS3300-id-2913435980/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-1038m2-RS2700/id-27611651/</t>
         </is>
       </c>
     </row>
@@ -5566,7 +5558,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -5574,17 +5566,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 65 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 75 m² · Graças</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rua Eduardo De Moraes</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5594,17 +5586,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>422.0</t>
+          <t>588.0</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>109.04</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>3317.0</t>
+          <t>3397.04</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5614,7 +5606,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>51.03</t>
+          <t>45.29</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -5624,7 +5616,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5634,22 +5626,22 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-1038m2-RS2700/id-27611651/</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/3178/apartamento-2-quartos-celina-gonçalves-de-oliveira-graças-recife/</t>
         </is>
       </c>
     </row>
@@ -5657,90 +5649,90 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Viva Real, Zap Imóveis</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 75 m² · Graças</t>
+          <t>Apartamento · 1 quarto · 37 m² · Rosarinho</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Doutor José Maria</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Rosarinho</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>3400.0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>588.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>109.04</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>3397.04</t>
+          <t>3400.0</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>45.29</t>
+          <t>91.89</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/3178/apartamento-2-quartos-celina-gonçalves-de-oliveira-graças-recife/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-rosarinho-bairros-recife-com-garagem-37m2-aluguel-RS3400-id-2913418918/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5748,30 +5740,30 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 37 m² · Rosarinho</t>
+          <t>Apartamento · 2 quartos · 59 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rua Doutor José Maria</t>
+          <t>Rua Pereira Simões, 1529 - 2</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosarinho</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>3400.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5786,7 +5778,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>3400.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5796,42 +5788,42 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>91.89</t>
+          <t>59.32</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-rosarinho-bairros-recife-com-garagem-37m2-aluguel-RS3400-id-2913418918/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-59m2-RS3500/id-45711136/</t>
         </is>
       </c>
     </row>
@@ -5847,12 +5839,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 59 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 57 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rua Pereira Simões, 1529 - 2</t>
+          <t>Rua Francisco Ambrósio De Barros Leite, 1225</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5887,7 +5879,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>59.32</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5897,7 +5889,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5907,22 +5899,22 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-59m2-RS3500/id-45711136/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-RS3500/id-42986293/</t>
         </is>
       </c>
     </row>
@@ -5930,7 +5922,7 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -5938,17 +5930,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 57 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 50 m² · 1 vaga · Torre</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rua Francisco Ambrósio De Barros Leite, 1225</t>
+          <t>Rua Real Da Torre</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5978,7 +5970,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5998,22 +5990,22 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-RS3500/id-42986293/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-50m2-RS3500/id-46933917/</t>
         </is>
       </c>
     </row>
@@ -6021,25 +6013,25 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Chaves na Mão Recife, Rogério Corretor</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · 1 vaga · Torre</t>
+          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rua Real Da Torre</t>
+          <t>Rua Cardeal Arcoverde, 1</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -6069,12 +6061,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>106.06</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -6089,22 +6081,22 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-50m2-RS3500/id-46933917/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS3500/id-45844382/</t>
         </is>
       </c>
     </row>
@@ -6112,25 +6104,25 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife, Rogério Corretor</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 2 quartos · 70 m² · Tamarineira</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rua Cardeal Arcoverde, 1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Tamarineira</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -6140,7 +6132,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6155,22 +6147,22 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>106.06</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6180,7 +6172,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -6195,7 +6187,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS3500/id-45844382/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-70m2-tamarineira-recife--pe_33364198</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6203,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · Tamarineira</t>
+          <t>Apartamento · 3 quartos · 77 m² · Torre</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6221,7 +6213,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tamarineira</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -6231,7 +6223,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6246,17 +6238,17 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -6271,22 +6263,22 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-70m2-tamarineira-recife--pe_33364198</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-77m2-torre-recife--pe_33379670</t>
         </is>
       </c>
     </row>
@@ -6302,7 +6294,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · Torre</t>
+          <t>Apartamento · 2 quartos · 82 m² · Casa Forte</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6312,7 +6304,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Forte</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -6322,7 +6314,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6337,17 +6329,17 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>42.68</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -6362,22 +6354,22 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-77m2-torre-recife--pe_33379670</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-82m2-casa-forte-recife--pe_33364920</t>
         </is>
       </c>
     </row>
@@ -6385,25 +6377,25 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 82 m² · Casa Forte</t>
+          <t>Apartamento · 2 quartos · 60 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Casa Forte</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -6413,7 +6405,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6428,12 +6420,12 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>42.68</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6443,7 +6435,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6453,22 +6445,22 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-82m2-casa-forte-recife--pe_33364920</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-60m2-aluguel-RS3500-id-2904577437/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -6931,7 +6923,7 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Zap Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -6939,17 +6931,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Apartamento · 4 quartos · 120 m² · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Torre</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rua Dom Carlos Coelho</t>
+          <t>Rua José De Holanda, 854</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6969,7 +6961,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3601.0</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -6979,42 +6971,42 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>81.84</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>120.0</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-4-quartos-boa-vista-recife-pe-120m2-id-2913416134/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-RS3600/id-40119104/</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7014,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -7030,22 +7022,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Torre</t>
+          <t>Apartamento · 2 quartos · 51 m² · Aflitos</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rua José De Holanda, 854</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3699.0</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7060,7 +7052,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>3601.0</t>
+          <t>3699.0</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -7070,7 +7062,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>81.84</t>
+          <t>72.53</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -7080,7 +7072,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7090,22 +7082,22 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-RS3600/id-40119104/</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/307-rua-manuel-de-carvalho/850701030-101</t>
         </is>
       </c>
     </row>
@@ -7295,25 +7287,25 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 50 m² · Torre</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rua Joana D'Arc Sampaio</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -7323,7 +7315,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7333,17 +7325,17 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>3901.0</t>
+          <t>3900.0</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7353,7 +7345,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7363,22 +7355,22 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3900-id-2913026520/?source=ranking%2Crp</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/211-rua-conselheiro-theodoro/850701030-95</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7378,7 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife, Josinildo Imóveis</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -7394,27 +7386,27 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 74 m² · 1 vaga · Aflitos</t>
+          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Rua Da Angustura, 195</t>
+          <t>Rua Joana D'Arc Sampaio</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>4091.0</t>
+          <t>3900.0</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7424,27 +7416,27 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>4091.0</t>
+          <t>3901.0</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>55.28</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -7454,22 +7446,22 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-aflitos-74m2-RS4091/id-46898128/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3900-id-2913026520/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -7477,30 +7469,30 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Rogério Corretor</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 145 m² · 2 vagas · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 51 m² · Aflitos</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Avenida Min. Marcos Freire, 3495</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>4100.0</t>
+          <t>3990.0</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -7515,7 +7507,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>4100.0</t>
+          <t>3990.0</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -7525,17 +7517,17 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>78.24</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -7545,22 +7537,22 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4100/id-46901493/</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/307-manuel-de-carvalho-edificio-praca-das-cerejeiras/850721013-37</t>
         </is>
       </c>
     </row>
@@ -7568,20 +7560,20 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Chaves na Mão Recife, Josinildo Imóveis</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Aflitos</t>
+          <t>Apartamento · 3 quartos · 74 m² · 1 vaga · Aflitos</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Avenida Conselheiro Rosa E Silva, 801</t>
+          <t>Rua Da Angustura, 195</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -7591,7 +7583,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>4141.0</t>
+          <t>4091.0</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -7606,7 +7598,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>4142.0</t>
+          <t>4091.0</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -7616,17 +7608,17 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>75.31</t>
+          <t>55.28</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -7636,22 +7628,22 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-aflitos-55m2-RS4141/id-45283901/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-aflitos-74m2-RS4091/id-46898128/</t>
         </is>
       </c>
     </row>
@@ -7659,35 +7651,35 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Olinda, Rogério Corretor</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 43 m² · Casa Amarela</t>
+          <t>Apartamento · 3 quartos · 145 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Min. Marcos Freire, 3495</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>4200.0</t>
+          <t>4100.0</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7697,27 +7689,27 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>4200.0</t>
+          <t>4100.0</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>97.67</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -7727,22 +7719,22 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-43m2-casa-amarela-recife--pe_33376830</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4100/id-46901493/</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7742,7 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Rogério Corretor</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -7758,12 +7750,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Aflitos</t>
+          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Aflitos</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Conselheiro Rosa E Silva, 801</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -7773,12 +7765,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>4141.0</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7788,17 +7780,17 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>4350.0</t>
+          <t>4142.0</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>54.38</t>
+          <t>75.31</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7808,7 +7800,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -7818,22 +7810,22 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>https://www.rogeriocorretor.com/imovel/apartamento-2-quartos-aflitos-recife-1-vaga-80m2-code-695</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-aflitos-55m2-RS4141/id-45283901/</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7833,7 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -7849,27 +7841,27 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 43 m² · Casa Amarela</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos De Lima Cavalcante</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>4200.0</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>1195.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7879,7 +7871,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>4395.0</t>
+          <t>4200.0</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -7889,7 +7881,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>79.91</t>
+          <t>97.67</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -7899,7 +7891,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -7909,22 +7901,22 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-55m2-RS3200/id-46174975/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-43m2-casa-amarela-recife--pe_33376830</t>
         </is>
       </c>
     </row>
@@ -7932,7 +7924,7 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Rogério Corretor</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -7940,27 +7932,27 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · 2 vagas · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 80 m² · Aflitos</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Avenida Ministro Marcos Freire</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7970,27 +7962,27 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>4350.0</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>52.94</t>
+          <t>54.38</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -8000,7 +7992,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -8015,7 +8007,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-110m2-RS4500/id-42417501/</t>
+          <t>https://www.rogeriocorretor.com/imovel/apartamento-2-quartos-aflitos-recife-1-vaga-80m2-code-695</t>
         </is>
       </c>
     </row>
@@ -8023,20 +8015,20 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 97 m² · 2 vagas · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Avenida Ministro Marcos Freire</t>
+          <t>Avenida Governador Carlos De Lima Cavalcante</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -8046,12 +8038,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1195.0</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8061,27 +8053,27 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>4395.0</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>46.39</t>
+          <t>79.91</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -8091,7 +8083,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -8106,7 +8098,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4500/id-46421413/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-55m2-RS3200/id-46174975/</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8106,7 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -8122,17 +8114,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 56 m² · 1 vaga · Espinheiro</t>
+          <t>Apartamento · 3 quartos · 85 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Rua São Salvador, 200</t>
+          <t>Avenida Ministro Marcos Freire</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -8162,17 +8154,17 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>80.36</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -8182,22 +8174,22 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-espinheiro-70m2-RS4500/id-46923849/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-110m2-RS4500/id-42417501/</t>
         </is>
       </c>
     </row>
@@ -8205,25 +8197,25 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Rogério Corretor</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Apartamento · 4 quartos · 90 m² · Torre</t>
+          <t>Apartamento · 3 quartos · 97 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Ministro Marcos Freire</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -8253,17 +8245,17 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>46.39</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -8273,7 +8265,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -8288,7 +8280,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>https://www.rogeriocorretor.com/imovel/casa-4-quartos-torre-recife-90m2-code-736</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4500/id-46421413/</t>
         </is>
       </c>
     </row>
@@ -8296,30 +8288,30 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Apartamento · 4 quartos · 87 m² · Rosarinho</t>
+          <t>Apartamento · 2 quartos · 56 m² · 1 vaga · Espinheiro</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rua Hipólito Braga</t>
+          <t>Rua São Salvador, 200</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rosarinho</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>4590.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -8334,7 +8326,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>4590.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -8344,42 +8336,42 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>52.76</t>
+          <t>80.36</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>56.0</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-rosarinho-bairros-recife-com-garagem-87m2-aluguel-RS4590-id-2913430257/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-espinheiro-70m2-RS4500/id-46923849/</t>
         </is>
       </c>
     </row>
@@ -8387,7 +8379,7 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Rogério Corretor</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -8395,22 +8387,22 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Parnamirim</t>
+          <t>Apartamento · 4 quartos · 90 m² · Torre</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Avenida Parnamirim</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>4700.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -8425,7 +8417,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>4700.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -8435,17 +8427,17 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>78.33</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -8455,7 +8447,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
@@ -8470,7 +8462,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-parnamirim-RS4700/id-43942857/</t>
+          <t>https://www.rogeriocorretor.com/imovel/casa-4-quartos-torre-recife-90m2-code-736</t>
         </is>
       </c>
     </row>
@@ -8478,88 +8470,270 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
+          <t>Viva Real, Zap Imóveis</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>2</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Apartamento · 4 quartos · 87 m² · Rosarinho</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Rua Hipólito Braga</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Rosarinho</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>4590.0</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>4590.0</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>52.76</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-rosarinho-bairros-recife-com-garagem-87m2-aluguel-RS4590-id-2913430257/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Recife</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Parnamirim</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Avenida Parnamirim</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Parnamirim</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>4700.0</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>4700.0</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>78.33</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-parnamirim-RS4700/id-43942857/</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
           <t>Portal CRECI Brasil</t>
         </is>
       </c>
-      <c r="C89" t="n">
+      <c r="C91" t="n">
         <v>1</v>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>Apartamento · 3 quartos · 89 m² · Torre</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
         <is>
           <t>Torre</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>5500.0</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
         <is>
           <t>5500.0</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="K91" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t>61.8</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
         <is>
           <t>89.0</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr">
+      <c r="Q91" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr">
+      <c r="R91" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr">
+      <c r="S91" t="inlineStr">
         <is>
           <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-89m2-torre-recife--pe_33386591</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S98"/>
+  <dimension ref="A1:S89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -553,30 +553,30 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Viva Real Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 2222 m² · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 30 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1890.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>1890.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -601,17 +601,17 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2222.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-bairro-novo-bairros-olinda-2222m2-aluguel-RS1890-id-2891974581/?source=showcase%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-30m2-aluguel-RS2700-id-2913849795/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -656,57 +656,57 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Rua Professor José Cândido Pessoa</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>684.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2477.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>68.81</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -716,22 +716,22 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-720m2-RS1700/id-43805924/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3000-id-2913637829/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Viva Real Olinda</t>
+          <t>Zap Imóveis</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -751,22 +751,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 36 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 56 m² · Torreão</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Rua Cândido Lacerda</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Torreão</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3100.0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3100.0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>55.36</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-36m2-aluguel-RS2800-id-2705654338/?source=showcase%2Crp</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-com-piscina-torreao-recife-pe-56m2-id-2889237280/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -838,30 +838,30 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Zap Imóveis</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · Bairro Novo</t>
+          <t>Apartamento · 4 quartos · 130 m² · Casa Amarela</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Rua Conselheiro Nabuco</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -886,17 +886,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>25.38</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-35m2-aluguel-RS3000-id-2913485117/?source=ranking%2Crp</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-4-quartos-nova-descoberta-recife-pe-130m2-id-2913765656/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Rogério Corretor, Viva Real, Zap Imóveis</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -941,59 +941,59 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · Graças</t>
+          <t>Apartamento · 2 quartos · 65 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Rua Ricardo Hardman</t>
+          <t>Rua Eduardo de Moraes</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3400.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>422.0</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3400.0</t>
+          <t>3317.0</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>97.14</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>https://www.rogeriocorretor.com/imovel/apartamento-1-quarto-gracas-recife-1-vaga-34m2-code-726</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-1038m2-RS2700/id-27611651/</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>Zap Imóveis</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -1036,367 +1036,355 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 55 m² · Espinheiro</t>
+          <t>Apartamento · 2 quartos · 55 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Rua São Salvador</t>
+          <t>Avenida João de Barros</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3650.0</t>
+          <t>3800.0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3650.0</t>
+          <t>3802.0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>69.13</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-mobiliado-boa-vista-recife-pe-55m2-id-2913693032/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Olinda</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 58 m² · 1 vaga · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Rua Norberto Pessoa, 238</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1300.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1300.0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>66.36</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>22.41</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>58.0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1300/id-46461545/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Olinda</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Apartamento · 1 quarto · 41 m² · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Rua Professor Marculino Botelho, 404</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>34.15</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-pe-olinda-bairro-novo-41m2-RS1200/id-45673360/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Âncora Imobiliária</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 50 m² · Boa Vista</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Boa Vista</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1100.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>250.0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>97.38</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1447.38</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>28.95</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-espinheiro-bairros-recife-com-garagem-55m2-aluguel-RS3650-id-2913847432/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Zap Imóveis</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 60 m² · Espinheiro</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Rua São Salvador</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Espinheiro</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4100.0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>4100.0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>68.33</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-com-piscina-espinheiro-recife-pe-60m2-id-2913804349/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Viva Real, Zap Imóveis</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 4 quartos · 100 m² · Graças</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Rua das Graças</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Graças</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>45.0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-gracas-bairros-recife-com-garagem-100m2-aluguel-RS4500-id-2913720624/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 140 m² · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Avenida Ministro Marcos Freire</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>32.14</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>140.0</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-140m2-aluguel-RS4500-id-2895454008/?source=showcase%2Crp</t>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>https://ancoraimobiliaria.com.br/imovel/224/apartamento-2-quartos-jose-mariano-boa-vista-recife/</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1392,7 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1412,82 +1400,82 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 58 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 40 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rua Norberto Pessoa, 238</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1300.0</t>
+          <t>1100.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>505.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1300.0</t>
+          <t>1677.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>58.0</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1300/id-46461545/</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/2553/apartamento-1-quarto-arpege-boa-vista-recife/</t>
         </is>
       </c>
     </row>
@@ -1503,12 +1491,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 41 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua Professor Marculino Botelho, 404</t>
+          <t>Rua Otaviano Pessoa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1518,42 +1506,42 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1200.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1400.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>34.15</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1563,22 +1551,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-pe-olinda-bairro-novo-41m2-RS1200/id-45673360/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1700/id-45733416/</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1574,7 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1594,7 +1582,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · Boa Vista</t>
+          <t>Apartamento · 1 quarto · 33 m² · Encruzilhada</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1604,42 +1592,42 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1100.0</t>
+          <t>1750.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>97.38</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1447.38</t>
+          <t>1750.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>53.03</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1654,22 +1642,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/224/apartamento-2-quartos-jose-mariano-boa-vista-recife/</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/123-rua-carlos-borromeu-de-frente-para-o-mercado-da-encruzilhada/850471068-78</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1673,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 40 m² · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 50 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1695,27 +1683,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1100.0</t>
+          <t>1450.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>505.0</t>
+          <t>405.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>80.96</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1677.0</t>
+          <t>1935.96</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1725,12 +1713,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>38.72</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1745,22 +1733,22 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/2553/apartamento-1-quarto-arpege-boa-vista-recife/</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/6691/apartamento-2-quartos-santo-amaro-recife/</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1764,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Rua Coronel Alberto Lundgren, 604</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1791,42 +1779,42 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1836,22 +1824,22 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1700/id-45733416/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS1800/id-46397377/</t>
         </is>
       </c>
     </row>
@@ -1859,65 +1847,65 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · Santo Amaro</t>
+          <t>Apartamento · 1 quarto · 1382 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Doutor Manoel de Barros Lima</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1450.0</t>
+          <t>2150.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>405.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>80.96</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1935.96</t>
+          <t>2150.0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>38.72</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1927,22 +1915,22 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>1382.0</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/6691/apartamento-2-quartos-santo-amaro-recife/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-bairro-novo-bairros-olinda-1382m2-aluguel-RS2150-id-2911542521/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1961,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1988,7 +1976,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1998,7 +1986,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2023,17 +2011,17 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS1800/id-46397377/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS2000/id-46397376/</t>
         </is>
       </c>
     </row>
@@ -2049,47 +2037,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 65 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Avenida Doutor José Augusto Moreira</t>
+          <t>Rua Professor José Cândido Pessoa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2002.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>33.37</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2099,7 +2087,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2109,22 +2097,22 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-60m2-aluguel-RS2000-id-2910983844/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-65m2-aluguel-RS2200-id-2897302602/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2132,20 +2120,20 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 1382 m² · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rua Doutor Manoel de Barros Lima</t>
+          <t>Rua Professor José Cândido Pessoa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2155,32 +2143,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2150.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>684.0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2150.0</t>
+          <t>2477.0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>68.81</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2200,22 +2188,22 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1382.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-bairro-novo-bairros-olinda-1382m2-aluguel-RS2150-id-2911542521/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-720m2-RS1700/id-43805924/</t>
         </is>
       </c>
     </row>
@@ -2223,90 +2211,90 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 70 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rua Coronel Alberto Lundgren, 604</t>
+          <t>Rua Nereu Gomes Maciel</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2499.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2499.0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS2000/id-46397376/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-70m2-aluguel-RS2499-id-2903057019/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2314,30 +2302,30 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 65 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rua Professor José Cândido Pessoa</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2352,7 +2340,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2362,17 +2350,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>33.85</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2382,22 +2370,22 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>36</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-65m2-aluguel-RS2200-id-2897302602/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2393,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2413,52 +2401,52 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 49 m² · Espinheiro</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Rua Da Hora, 235</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2473,22 +2461,22 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-pe-recife-espinheiro-49m2-RS2000/id-44279997/</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2484,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2504,27 +2492,27 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 49 m² · Espinheiro</t>
+          <t>Apartamento · 1 quarto · 31 m² · Parnamirim</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rua Da Hora, 235</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>500.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2539,22 +2527,22 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>80.65</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2564,22 +2552,22 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-pe-recife-espinheiro-49m2-RS2000/id-44279997/</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/n%C2%BA-50-rua-condado-perto-do-cafe-sao-braz/850091040-261</t>
         </is>
       </c>
     </row>
@@ -2587,25 +2575,25 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 31 m² · Parnamirim</t>
+          <t>Apartamento · 1 quarto · 38 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2635,7 +2623,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>80.65</t>
+          <t>65.79</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2645,32 +2633,32 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/n%C2%BA-50-rua-condado-perto-do-cafe-sao-braz/850091040-261</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-38m2-aluguel-RS2500-id-2698090477/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2674,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 38 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 35 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2696,7 +2684,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2726,7 +2714,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>65.79</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2741,27 +2729,27 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-38m2-aluguel-RS2500-id-2698090477/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/flat-1-quartos-bairro-novo-bairros-olinda-com-garagem-35m2-aluguel-RS2500-id-2901073105/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2769,7 +2757,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Viva Real Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2777,12 +2765,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 107 m² · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Avenida Presidente Getúlio Vargas, 1748</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2792,42 +2780,42 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>683.0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2576.0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>71.56</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2837,22 +2825,22 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-bairros-olinda-com-garagem-107m2-aluguel-RS2500-id-2902349299/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-36m2-RS1800/id-45673358/</t>
         </is>
       </c>
     </row>
@@ -2860,65 +2848,65 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 71 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Avenida Presidente Getúlio Vargas, 1748</t>
+          <t>Rua Gildo Branco</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>683.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2576.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>71.56</t>
+          <t>36.62</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2928,22 +2916,22 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-36m2-RS1800/id-45673358/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-71m2-aluguel-RS2600-id-2911301943/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2951,35 +2939,35 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · Aflitos</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2600.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2989,52 +2977,52 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2600.0</t>
+          <t>2691.0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>74.29</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/flat-1-quartos-bairro-novo-bairros-olinda-com-garagem-35m2-aluguel-RS2600-id-2912188115/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-aflitos-recife--pe_33374631</t>
         </is>
       </c>
     </row>
@@ -3042,20 +3030,20 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 71 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rua Gildo Branco</t>
+          <t>Rua Otaviano Pessoa Monteiro, 93</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3065,12 +3053,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2600.0</t>
+          <t>1526.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1178.0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3080,27 +3068,27 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2600.0</t>
+          <t>2704.0</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>36.62</t>
+          <t>29.08</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3110,22 +3098,22 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-71m2-aluguel-RS2600-id-2911301943/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1526/id-45586419/</t>
         </is>
       </c>
     </row>
@@ -3133,35 +3121,35 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · Aflitos</t>
+          <t>Apartamento · 1 quarto · 36 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3171,52 +3159,52 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2691.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-aflitos-recife--pe_33374631</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-36m2-aluguel-RS2800-id-2705654338/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3224,30 +3212,30 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 77 m² · Santana</t>
+          <t>Apartamento · 2 quartos · 60 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Santana</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3262,7 +3250,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3272,7 +3260,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>35.06</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3282,7 +3270,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3292,22 +3280,22 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/458-santanna-proximo-ao-parque-de-santana/850501009-266</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-60m2-aluguel-RS2800-id-2912116616/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3303,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>CTI Imobiliária</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -3323,27 +3311,27 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa Monteiro, 93</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1526.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1178.0</t>
+          <t>380.0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3353,7 +3341,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2704.0</t>
+          <t>2880.0</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3363,7 +3351,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3373,7 +3361,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3383,7 +3371,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3398,7 +3386,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1526/id-45586419/</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-torre-recife-pe/1353</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3394,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -3414,47 +3402,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 63 m² · Aflitos</t>
+          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rua Samuel Campelo</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>380.0</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>176.42</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>2956.42</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3464,7 +3452,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3474,22 +3462,22 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-aflitos-bairros-recife-com-garagem-63m2-aluguel-RS2800-id-2912913421/?source=ranking%2Crp</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/6596/apartamento-2-quartos-torre-recife/</t>
         </is>
       </c>
     </row>
@@ -3505,22 +3493,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 42 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Rua Ulisses Tenório de Albuquerque</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>2998.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3535,7 +3523,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>2998.0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3545,7 +3533,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>71.38</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3555,7 +3543,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3565,22 +3553,22 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-60m2-aluguel-RS2800-id-2912116616/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-42m2-aluguel-RS2998-id-2911376544/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3588,30 +3576,30 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Apartamento · 40 m² · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 40 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Avenida Governador Carlos De Lima Cavalcante, 2595</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3626,7 +3614,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3636,12 +3624,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3661,17 +3649,17 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/kitnet-casa-caiada-bairros-olinda-com-garagem-40m2-aluguel-RS2800-id-2910716413/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-40m2-RS3000/id-45710865/</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3667,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CTI Imobiliária</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3687,27 +3675,27 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
+          <t>Apartamento · 1 quarto · 42 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Doutor José Augusto Moreira, 900</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>380.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3717,27 +3705,27 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2880.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3747,7 +3735,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3762,7 +3750,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-torre-recife-pe/1353</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-RS3000/id-44380568/</t>
         </is>
       </c>
     </row>
@@ -3770,7 +3758,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3778,37 +3766,37 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
+          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Otaviano Pessoa Monteiro, 93</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>1822.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>380.0</t>
+          <t>1178.0</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>176.42</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2956.42</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3818,7 +3806,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>32.26</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3828,7 +3816,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3838,7 +3826,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -3853,7 +3841,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/6596/apartamento-2-quartos-torre-recife/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1822/id-45585830/</t>
         </is>
       </c>
     </row>
@@ -3861,20 +3849,20 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 42 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 92 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rua Ulisses Tenório de Albuquerque</t>
+          <t>Avenida Carlos De Lima Cavalcante</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3884,7 +3872,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2998.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3899,7 +3887,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2998.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3909,19 +3897,19 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>71.38</t>
+          <t>32.61</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O38" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -3929,22 +3917,22 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-42m2-aluguel-RS2998-id-2911376544/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS3000/id-42437394/</t>
         </is>
       </c>
     </row>
@@ -3952,7 +3940,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3960,47 +3948,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 40 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos De Lima Cavalcante, 2595</t>
+          <t>Rua Cardeal Arcoverde, 276</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
+          <t>2332.0</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>550.0</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>118.0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
           <t>3000.0</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>93.75</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4020,22 +4008,22 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-40m2-RS3000/id-45710865/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS2332/id-46081872/</t>
         </is>
       </c>
     </row>
@@ -4043,25 +4031,25 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 42 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 35 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Avenida Doutor José Augusto Moreira, 900</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4091,7 +4079,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4111,22 +4099,22 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-RS3000/id-44380568/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-35m2-aluguel-RS3000-id-2913485117/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4134,35 +4122,35 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 68 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa Monteiro, 93</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1822.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1178.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4177,12 +4165,12 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>32.26</t>
+          <t>44.12</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4192,7 +4180,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4202,22 +4190,22 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1822/id-45585830/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-68m2-aluguel-RS3000-id-2913457037/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4225,20 +4213,20 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 92 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 60 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Avenida Carlos De Lima Cavalcante</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4273,17 +4261,17 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4293,22 +4281,22 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS3000/id-42437394/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3000-id-2859906255/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4316,7 +4304,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Zap Imóveis</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -4324,32 +4312,32 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 1 quarto · 34 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rua Cardeal Arcoverde, 276</t>
+          <t>Avenida Governador Agamenon Magalhães</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2332.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>550.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4359,12 +4347,12 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>93.75</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4379,27 +4367,27 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS2332/id-46081872/</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-1-quarto-com-piscina-boa-vista-recife-pe-34m2-id-2913394619/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4407,7 +4395,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Josinildo Imóveis</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -4415,7 +4403,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 34 m² · Santo Amaro</t>
+          <t>Apartamento · 2 quartos · 42 m² · Torre</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4425,12 +4413,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4445,7 +4433,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4455,12 +4443,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4475,22 +4463,22 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/185-rua-dom-pedro-henrique-prox-a-catolica/850301004-158</t>
+          <t>https://josinildoimoveis.com.br/imovel/edf-green-life-torre/PARJI03</t>
         </is>
       </c>
     </row>
@@ -4498,7 +4486,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Viva Real</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -4506,22 +4494,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 45 m² · Tamarineira</t>
+          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rua Goianésia</t>
+          <t>Rua Amélia, 623</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tamarineira</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4536,7 +4524,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4546,12 +4534,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4566,22 +4554,22 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-tamarineira-bairros-recife-com-garagem-45m2-aluguel-RS3000-id-2904709773/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-RS3200/id-45197779/</t>
         </is>
       </c>
     </row>
@@ -4589,30 +4577,30 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Newville</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 68 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 52 m² · Torre</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4627,7 +4615,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4637,7 +4625,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>44.12</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4647,7 +4635,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4657,22 +4645,22 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-68m2-aluguel-RS3000-id-2913457037/?source=ranking%2Crp</t>
+          <t>https://newville.com.br/imovel/apartamento_2_quartos--torre--recife--pe--locacao--cod-6391</t>
         </is>
       </c>
     </row>
@@ -4680,30 +4668,30 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 62 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 38 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa Monteiro</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4718,7 +4706,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4728,17 +4716,17 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>48.39</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4748,22 +4736,22 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-62m2-aluguel-RS3000-id-2911451041/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-1-quarto-alugar-38m2-boa-vista-recife--pe_33378812</t>
         </is>
       </c>
     </row>
@@ -4779,22 +4767,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 60 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 57 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Rua Pereira Simões</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4809,7 +4797,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4819,42 +4807,42 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>56.14</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3000-id-2859906255/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-57m2-aluguel-RS3200-id-2901326206/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4862,60 +4850,60 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 60 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 70 m² · 1 vaga · Casa Amarela</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rua Professor Francisco Xavier Paes Barreto</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>3001.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>237.0</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>3001.0</t>
+          <t>3202.0</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>50.02</t>
+          <t>45.74</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4925,27 +4913,27 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3001-id-2912144534/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-amarela-70m2-RS2000/id-43758789/</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4941,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Josinildo Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -4961,22 +4949,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 42 m² · Torre</t>
+          <t>Apartamento · 3 quartos · 66 m² · 1 vaga · Campo Grande</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Barão De Vera Cruz</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Campo Grande</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4991,7 +4979,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5001,17 +4989,17 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5021,22 +5009,22 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>https://josinildoimoveis.com.br/imovel/edf-green-life-torre/PARJI03</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-campo-grande-79m2-RS3300/id-44353442/</t>
         </is>
       </c>
     </row>
@@ -5044,30 +5032,30 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 2 quartos · 58 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rua Amélia, 623</t>
+          <t>Rua Pereira Simões</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5082,7 +5070,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5092,19 +5080,19 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O51" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -5112,22 +5100,22 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-RS3200/id-45197779/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-58m2-aluguel-RS3300-id-2913435980/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5123,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Newville</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -5143,22 +5131,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 52 m² · Torre</t>
+          <t>Apartamento · 2 quartos · 59 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Pereira Simões, 1529 - 2</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5173,7 +5161,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5183,7 +5171,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>59.32</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5193,7 +5181,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5203,22 +5191,22 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>https://newville.com.br/imovel/apartamento_2_quartos--torre--recife--pe--locacao--cod-6391</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-59m2-RS3500/id-45711136/</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5214,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -5234,22 +5222,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 38 m² · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 57 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Francisco Ambrósio De Barros Leite, 1225</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5264,7 +5252,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5274,19 +5262,19 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="O53" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -5294,22 +5282,22 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-1-quarto-alugar-38m2-boa-vista-recife--pe_33378812</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-RS3500/id-42986293/</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5305,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -5325,22 +5313,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 40 m² · Santana</t>
+          <t>Apartamento · 2 quartos · 50 m² · 1 vaga · Torre</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Real Da Torre</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Santana</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5355,7 +5343,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5365,19 +5353,19 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="O54" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -5385,7 +5373,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -5400,7 +5388,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/70-rua-samuel-de-farias/850091105-39</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-50m2-RS3500/id-46933917/</t>
         </is>
       </c>
     </row>
@@ -5408,30 +5396,30 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Chaves na Mão Recife, Rogério Corretor</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · Encruzilhada</t>
+          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Cardeal Arcoverde, 1</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5446,7 +5434,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5456,7 +5444,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>91.43</t>
+          <t>106.06</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5466,7 +5454,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5476,22 +5464,22 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/68-rua-engenheiro-sampaio/850701030-102</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS3500/id-45844382/</t>
         </is>
       </c>
     </row>
@@ -5499,35 +5487,35 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 57 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 70 m² · Tamarineira</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rua Pereira Simões</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Tamarineira</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5537,17 +5525,17 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>56.14</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5557,32 +5545,32 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-57m2-aluguel-RS3200-id-2901326206/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-70m2-tamarineira-recife--pe_33364198</t>
         </is>
       </c>
     </row>
@@ -5590,30 +5578,30 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 58 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 77 m² · Torre</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rua Pereira Simões</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5628,7 +5616,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5638,42 +5626,42 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>55.17</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-58m2-aluguel-RS3200-id-2907384719/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-77m2-torre-recife--pe_33379670</t>
         </is>
       </c>
     </row>
@@ -5681,35 +5669,35 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 82 m² · Casa Forte</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Casa Forte</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5719,17 +5707,17 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>42.68</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5739,7 +5727,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5749,22 +5737,22 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3200-id-2906163316/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-82m2-casa-forte-recife--pe_33364920</t>
         </is>
       </c>
     </row>
@@ -5772,55 +5760,55 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · 1 vaga · Casa Amarela</t>
+          <t>Apartamento · 2 quartos · 59 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Pereira Simões</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>237.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>3202.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>45.74</t>
+          <t>59.32</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5835,27 +5823,27 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-amarela-70m2-RS2000/id-43758789/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-59m2-aluguel-RS3500-id-2905566215/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5863,30 +5851,30 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 66 m² · 1 vaga · Campo Grande</t>
+          <t>Apartamento · 4 quartos · 160 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rua Barão De Vera Cruz</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Campo Grande</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5901,7 +5889,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5911,42 +5899,42 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>21.88</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-campo-grande-79m2-RS3300/id-44353442/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-casa-caiada-bairros-olinda-com-garagem-160m2-aluguel-RS3500-id-2909290334/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5950,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 58 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 60 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rua Pereira Simões</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5977,7 +5965,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5992,7 +5980,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6002,7 +5990,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6012,7 +6000,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6022,22 +6010,22 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-58m2-aluguel-RS3300-id-2913435980/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-60m2-aluguel-RS3500-id-2904577437/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -6045,45 +6033,45 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>CTI Imobiliária, Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 65 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Boa Vista</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rua Eduardo De Moraes</t>
+          <t>Avenida Governador Carlos De Lima Cavalcanti, 60</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>422.0</t>
+          <t>553.0</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>174.0</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>3317.0</t>
+          <t>3527.0</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6093,7 +6081,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>51.03</t>
+          <t>80.16</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6113,22 +6101,22 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-1038m2-RS2700/id-27611651/</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6519</t>
         </is>
       </c>
     </row>
@@ -6136,7 +6124,7 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>CTI Imobiliária</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -6144,47 +6132,47 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 59 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 41 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rua Pereira Simões, 1529 - 2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>550.0</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3542.0</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>59.32</t>
+          <t>86.39</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6194,7 +6182,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6204,22 +6192,22 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-59m2-RS3500/id-45711136/</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6210</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6215,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -6235,22 +6223,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 57 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Parnamirim</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rua Francisco Ambrósio De Barros Leite, 1225</t>
+          <t>Avenida Parnamirim, 375</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6265,7 +6253,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6275,12 +6263,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -6295,22 +6283,22 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-RS3500/id-42986293/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-32m2-RS3600/id-41530823/</t>
         </is>
       </c>
     </row>
@@ -6326,27 +6314,27 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · 1 vaga · Torre</t>
+          <t>Apartamento · 1 quarto · 34 m² · 1 vaga · Parnamirim</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rua Real Da Torre</t>
+          <t>Avenida Parnamirim, 375</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>600.0</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6356,22 +6344,22 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>105.88</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -6386,7 +6374,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -6401,7 +6389,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-50m2-RS3500/id-46933917/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-55m2-RS3000/id-46882194/</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6397,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Zap Imóveis</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -6417,22 +6405,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 4 quartos · 120 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rua Cardeal Arcoverde, 1</t>
+          <t>Rua Dom Carlos Coelho</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6447,7 +6435,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6457,42 +6445,42 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>109.38</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS3500/id-45844382/</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-4-quartos-boa-vista-recife-pe-120m2-id-2913416134/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6488,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -6508,27 +6496,27 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · Tamarineira</t>
+          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Torre</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua José De Holanda, 854</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tamarineira</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6538,17 +6526,17 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3601.0</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>81.84</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6558,7 +6546,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6568,22 +6556,22 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-70m2-tamarineira-recife--pe_33364198</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-RS3600/id-40119104/</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6579,7 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -6599,7 +6587,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · Torre</t>
+          <t>Apartamento · 2 quartos · 51 m² · Aflitos</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6609,12 +6597,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3699.0</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6629,7 +6617,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3699.0</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6639,12 +6627,12 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>72.53</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -6659,22 +6647,22 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-77m2-torre-recife--pe_33379670</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/307-rua-manuel-de-carvalho/850701030-101</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6678,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 82 m² · Casa Forte</t>
+          <t>Apartamento · 3 quartos · Encruzilhada</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6700,12 +6688,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Casa Forte</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3700.0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6720,7 +6708,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3700.0</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6730,12 +6718,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>42.68</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -6750,7 +6738,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -6765,7 +6753,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-82m2-casa-forte-recife--pe_33364920</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-encruzilhada-recife--pe_33362592</t>
         </is>
       </c>
     </row>
@@ -6773,7 +6761,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -6781,7 +6769,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 83 m² · Aflitos</t>
+          <t>Apartamento · 3 quartos · 90 m² · Graças</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6791,37 +6779,37 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1300.0</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>185.21</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3785.21</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>42.09</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -6841,22 +6829,22 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>83.15</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/850191006-42</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/2698/apartamento-3-quartos-san-patrick-graças-recife/</t>
         </is>
       </c>
     </row>
@@ -6864,30 +6852,30 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Apartamento · 4 quartos · 160 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · Rosarinho</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Rosarinho</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3800.0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6902,7 +6890,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3800.0</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -6912,42 +6900,42 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>21.88</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>160.0</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-casa-caiada-bairros-olinda-com-garagem-160m2-aluguel-RS3500-id-2909290334/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-rosarinho-recife--pe_33388298</t>
         </is>
       </c>
     </row>
@@ -6963,12 +6951,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 67 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Rua Pereira Simões</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -6978,7 +6966,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3800.0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6993,7 +6981,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3800.0</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7003,7 +6991,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>56.72</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7023,7 +7011,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -7038,7 +7026,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-60m2-aluguel-RS3500-id-2904577437/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-67m2-aluguel-RS3800-id-2906555835/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -7046,55 +7034,55 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CTI Imobiliária, Chaves na Mão Recife</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 50 m² · Torre</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos De Lima Cavalcanti, 60</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3900.0</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>553.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>3527.0</t>
+          <t>3900.0</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>80.16</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -7104,7 +7092,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7114,22 +7102,22 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6519</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/211-rua-conselheiro-theodoro/850701030-95</t>
         </is>
       </c>
     </row>
@@ -7137,45 +7125,45 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CTI Imobiliária</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 41 m² · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Joana D'Arc Sampaio</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3900.0</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>550.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>3542.0</t>
+          <t>3902.0</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7185,7 +7173,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>86.39</t>
+          <t>65.03</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -7195,7 +7183,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7205,22 +7193,22 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6210</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3900-id-2913026520/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -7228,7 +7216,7 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -7236,22 +7224,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Parnamirim</t>
+          <t>Apartamento · 2 quartos · 51 m² · Aflitos</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Avenida Parnamirim, 375</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3990.0</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -7266,7 +7254,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3990.0</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7276,17 +7264,17 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>78.24</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7296,22 +7284,22 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-32m2-RS3600/id-41530823/</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/307-manuel-de-carvalho-edificio-praca-das-cerejeiras/850721013-37</t>
         </is>
       </c>
     </row>
@@ -7319,35 +7307,35 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Chaves na Mão Recife, Josinildo Imóveis</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 34 m² · 1 vaga · Parnamirim</t>
+          <t>Apartamento · 3 quartos · 74 m² · 1 vaga · Aflitos</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Avenida Parnamirim, 375</t>
+          <t>Rua Da Angustura, 195</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>4091.0</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>600.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7357,27 +7345,27 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>4091.0</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>105.88</t>
+          <t>55.28</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7387,22 +7375,22 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-55m2-RS3000/id-46882194/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-aflitos-74m2-RS4091/id-46898128/</t>
         </is>
       </c>
     </row>
@@ -7410,30 +7398,30 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Chaves na Mão Olinda, Rogério Corretor</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Torre</t>
+          <t>Apartamento · 3 quartos · 145 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Rua José De Holanda, 854</t>
+          <t>Avenida Min. Marcos Freire, 3495</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>4100.0</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -7448,7 +7436,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>3601.0</t>
+          <t>4100.0</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -7458,17 +7446,17 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>81.84</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -7478,22 +7466,22 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-RS3600/id-40119104/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4100/id-46901493/</t>
         </is>
       </c>
     </row>
@@ -7501,7 +7489,7 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -7509,12 +7497,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 51 m² · Aflitos</t>
+          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Aflitos</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Conselheiro Rosa E Silva, 801</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -7524,7 +7512,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>3699.0</t>
+          <t>4141.0</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -7539,7 +7527,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>3699.0</t>
+          <t>4142.0</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -7549,7 +7537,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>72.53</t>
+          <t>75.31</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -7559,7 +7547,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -7569,22 +7557,22 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/307-rua-manuel-de-carvalho/850701030-101</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-aflitos-55m2-RS4141/id-45283901/</t>
         </is>
       </c>
     </row>
@@ -7600,7 +7588,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · Encruzilhada</t>
+          <t>Apartamento · 2 quartos · 43 m² · Casa Amarela</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7610,12 +7598,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>3700.0</t>
+          <t>4200.0</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -7630,7 +7618,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>3700.0</t>
+          <t>4200.0</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -7640,12 +7628,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>97.67</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -7660,22 +7648,22 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-encruzilhada-recife--pe_33362592</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-43m2-casa-amarela-recife--pe_33376830</t>
         </is>
       </c>
     </row>
@@ -7683,7 +7671,7 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Zap Imóveis</t>
+          <t>Rogério Corretor</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -7691,37 +7679,37 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 51 m² · Casa Forte</t>
+          <t>Apartamento · 2 quartos · 80 m² · Aflitos</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Rua Jacó Velosino</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Casa Forte</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>3700.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>3702.0</t>
+          <t>4350.0</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -7731,7 +7719,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>72.59</t>
+          <t>54.38</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -7741,7 +7729,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -7751,22 +7739,22 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-mobiliado-casa-forte-recife-pe-51m2-id-2912181527/?source=ranking%2Crp</t>
+          <t>https://www.rogeriocorretor.com/imovel/apartamento-2-quartos-aflitos-recife-1-vaga-80m2-code-695</t>
         </is>
       </c>
     </row>
@@ -7774,7 +7762,7 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -7782,37 +7770,37 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 90 m² · Graças</t>
+          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos De Lima Cavalcante</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>1300.0</t>
+          <t>1195.0</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>185.21</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>3785.21</t>
+          <t>4395.0</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -7822,17 +7810,17 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>42.06</t>
+          <t>79.91</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -7842,22 +7830,22 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/2698/apartamento-3-quartos-san-patrick-graças-recife/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-55m2-RS3200/id-46174975/</t>
         </is>
       </c>
     </row>
@@ -7865,7 +7853,7 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -7873,22 +7861,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · Rosarinho</t>
+          <t>Apartamento · 3 quartos · 85 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Ministro Marcos Freire</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rosarinho</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>3800.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -7903,7 +7891,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>3800.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -7913,7 +7901,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -7923,7 +7911,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -7933,22 +7921,22 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-rosarinho-recife--pe_33388298</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-110m2-RS4500/id-42417501/</t>
         </is>
       </c>
     </row>
@@ -7956,7 +7944,7 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -7964,22 +7952,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · Encruzilhada</t>
+          <t>Apartamento · 3 quartos · 97 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Ministro Marcos Freire, 3291</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>3800.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -7994,7 +7982,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>3800.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -8004,17 +7992,17 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>54.29</t>
+          <t>46.39</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -8024,22 +8012,22 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/edf-arcadia/850091082-77</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4500/id-46421413/</t>
         </is>
       </c>
     </row>
@@ -8047,7 +8035,7 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -8055,22 +8043,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 51 m² · Aflitos</t>
+          <t>Apartamento · 2 quartos · 56 m² · 1 vaga · Espinheiro</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua São Salvador, 200</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>3990.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -8085,7 +8073,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>3990.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -8095,7 +8083,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>78.24</t>
+          <t>80.36</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -8105,7 +8093,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -8115,22 +8103,22 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/307-manuel-de-carvalho-edificio-praca-das-cerejeiras/850721013-37</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-espinheiro-70m2-RS4500/id-46923849/</t>
         </is>
       </c>
     </row>
@@ -8138,30 +8126,30 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife, Josinildo Imóveis</t>
+          <t>Rogério Corretor</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 74 m² · 1 vaga · Aflitos</t>
+          <t>Apartamento · 4 quartos · 90 m² · Torre</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Rua Da Angustura, 195</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>4091.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -8176,7 +8164,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>4091.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -8186,17 +8174,17 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>55.28</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -8206,22 +8194,22 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-aflitos-74m2-RS4091/id-46898128/</t>
+          <t>https://www.rogeriocorretor.com/imovel/casa-4-quartos-torre-recife-90m2-code-736</t>
         </is>
       </c>
     </row>
@@ -8229,30 +8217,30 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Rogério Corretor</t>
+          <t>Zap Imóveis</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 145 m² · 2 vagas · Casa Caiada</t>
+          <t>Apartamento · 4 quartos · 100 m² · Graças</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Avenida Min. Marcos Freire, 3495</t>
+          <t>Rua das Graças</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>4100.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -8267,7 +8255,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>4100.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -8277,19 +8265,19 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="O86" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -8297,22 +8285,22 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4100/id-46901493/</t>
+          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-4-quartos-gracas-recife-pe-100m2-id-2913720624/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -8328,22 +8316,22 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Aflitos</t>
+          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Parnamirim</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Avenida Conselheiro Rosa E Silva, 801</t>
+          <t>Avenida Parnamirim</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>4141.0</t>
+          <t>4700.0</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -8358,7 +8346,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>4142.0</t>
+          <t>4700.0</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -8368,7 +8356,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>75.31</t>
+          <t>78.33</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -8378,7 +8366,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -8388,22 +8376,22 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-aflitos-55m2-RS4141/id-45283901/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-parnamirim-RS4700/id-43942857/</t>
         </is>
       </c>
     </row>
@@ -8411,7 +8399,7 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -8419,27 +8407,27 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 43 m² · Casa Amarela</t>
+          <t>Apartamento · 3 quartos · 115 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Ministro Marcos Freire</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>4200.0</t>
+          <t>5000.0</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8449,27 +8437,27 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>4200.0</t>
+          <t>5000.0</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>97.67</t>
+          <t>43.48</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -8479,22 +8467,22 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-43m2-casa-amarela-recife--pe_33376830</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-115m2-RS5000/id-47073028/</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8490,7 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -8510,7 +8498,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 58 m² · Espinheiro</t>
+          <t>Apartamento · 3 quartos · 89 m² · Torre</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -8520,12 +8508,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>4200.0</t>
+          <t>5500.0</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -8540,7 +8528,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>4200.0</t>
+          <t>5500.0</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -8550,12 +8538,12 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -8570,839 +8558,20 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
-        <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/862-rua-da-hora/850251129-67</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr"/>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Rogério Corretor</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>1</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 80 m² · Aflitos</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Aflitos</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>750.0</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>4350.0</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>54.38</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R90" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>https://www.rogeriocorretor.com/imovel/apartamento-2-quartos-aflitos-recife-1-vaga-80m2-code-695</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr"/>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>1</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Avenida Governador Carlos De Lima Cavalcante</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>3200.0</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>1195.0</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>4395.0</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>79.91</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R91" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-55m2-RS3200/id-46174975/</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr"/>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>1</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 85 m² · 2 vagas · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Avenida Ministro Marcos Freire</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>52.94</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R92" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-110m2-RS4500/id-42417501/</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr"/>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>3</v>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 97 m² · 2 vagas · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Avenida Ministro Marcos Freire</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>46.39</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>97.0</t>
-        </is>
-      </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R93" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4500/id-46421413/</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr"/>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Recife</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>1</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 56 m² · 1 vaga · Espinheiro</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Rua São Salvador, 200</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Espinheiro</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>80.36</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>56.0</t>
-        </is>
-      </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R94" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-espinheiro-70m2-RS4500/id-46923849/</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr"/>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Rogério Corretor</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>1</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Apartamento · 4 quartos · 90 m² · Torre</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Torre</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>https://www.rogeriocorretor.com/imovel/casa-4-quartos-torre-recife-90m2-code-736</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr"/>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Recife</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>1</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Parnamirim</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Avenida Parnamirim</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Parnamirim</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>4700.0</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>4700.0</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>78.33</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R96" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-parnamirim-RS4700/id-43942857/</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr"/>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>1</v>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 115 m² · 2 vagas · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Avenida Ministro Marcos Freire</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>43.48</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R97" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-115m2-RS5000/id-47073028/</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr"/>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Portal CRECI Brasil</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>1</v>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 89 m² · Torre</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Torre</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>5500.0</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>5500.0</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>61.8</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>89.0</t>
-        </is>
-      </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R98" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="S98" t="inlineStr">
         <is>
           <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-89m2-torre-recife--pe_33386591</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S89"/>
+  <dimension ref="A1:S62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -553,20 +553,20 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 36 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Avenida Governador Carlos De Lima Cavalcante</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -601,19 +601,19 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>69.44</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -621,7 +621,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-30m2-aluguel-RS2700-id-2913849795/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-36m2-RS2500/id-47122887/</t>
         </is>
       </c>
     </row>
@@ -648,20 +648,20 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 65 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Rua Eduardo De Moraes, 85</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>421.0</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3316.0</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -731,387 +731,371 @@
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3000-id-2913637829/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-65m2-RS2700/id-47042111/</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Olinda</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Apartamento · 1 quarto · 41 m² · Bairro Novo</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Rua Professor Marculino Botelho, 404</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bairro Novo</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Zap Imóveis</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 56 m² · Torreão</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Rua Cândido Lacerda</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Torreão</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3100.0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3100.0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>55.36</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>56.0</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-com-piscina-torreao-recife-pe-56m2-id-2889237280/?source=ranking%2Crp</t>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>34.15</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-pe-olinda-bairro-novo-41m2-RS1200/id-45673360/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Âncora Imobiliária</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 50 m² · Boa Vista</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Boa Vista</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1100.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>250.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>97.38</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1447.38</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Zap Imóveis</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 4 quartos · 130 m² · Casa Amarela</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Rua Conselheiro Nabuco</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Casa Amarela</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3300.0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3300.0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>25.38</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>28.95</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>130.0</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-4-quartos-nova-descoberta-recife-pe-130m2-id-2913765656/?source=ranking%2Crp</t>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>https://ancoraimobiliaria.com.br/imovel/224/apartamento-2-quartos-jose-mariano-boa-vista-recife/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Âncora Imobiliária</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Apartamento · 1 quarto · 40 m² · Boa Vista</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Boa Vista</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1100.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>505.0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1677.0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 65 m² · 1 vaga · Bairro Novo</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Rua Eduardo de Moraes</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Bairro Novo</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2700.0</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>422.0</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>195.0</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3317.0</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>51.03</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>41.92</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-1038m2-RS2700/id-27611651/</t>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>https://ancoraimobiliaria.com.br/imovel/2553/apartamento-1-quarto-arpege-boa-vista-recife/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Zap Imóveis</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>REMAX Recife e Olinda</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 55 m² · Boa Vista</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Avenida João de Barros</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Boa Vista</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3800.0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3802.0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>69.13</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-2-quartos-mobiliado-boa-vista-recife-pe-55m2-id-2913693032/?source=ranking%2Crp</t>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Apartamento · 1 quarto · 33 m² · Encruzilhada</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Encruzilhada</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1750.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1750.0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>53.03</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>33.0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/123-rua-carlos-borromeu-de-frente-para-o-mercado-da-encruzilhada/850471068-78</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1103,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1127,57 +1111,57 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 58 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 50 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rua Norberto Pessoa, 238</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1300.0</t>
+          <t>1450.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>405.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>80.96</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1300.0</t>
+          <t>1935.96</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>38.72</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1187,22 +1171,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1300/id-46461545/</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/6691/apartamento-2-quartos-santo-amaro-recife/</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1202,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 41 m² · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rua Professor Marculino Botelho, 404</t>
+          <t>Rua Coronel Alberto Lundgren, 604</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1233,22 +1217,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1200.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1400.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1258,7 +1242,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>34.15</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1278,22 +1262,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-pe-olinda-bairro-novo-41m2-RS1200/id-45673360/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS1800/id-46397377/</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1285,7 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1309,37 +1293,37 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · Boa Vista</t>
+          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Coronel Alberto Lundgren, 604</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1100.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>97.38</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1447.38</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1349,17 +1333,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1369,7 +1353,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1384,7 +1368,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/224/apartamento-2-quartos-jose-mariano-boa-vista-recife/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS2000/id-46397376/</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1376,7 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1400,37 +1384,37 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 40 m² · Boa Vista</t>
+          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Professor José Cândido Pessoa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1100.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>505.0</t>
+          <t>684.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1677.0</t>
+          <t>2477.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1440,7 +1424,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>68.81</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1450,7 +1434,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1460,22 +1444,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/2553/apartamento-1-quarto-arpege-boa-vista-recife/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-720m2-RS1700/id-43805924/</t>
         </is>
       </c>
     </row>
@@ -1491,22 +1475,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa</t>
+          <t>Rua João Clementino Montarroyos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1521,7 +1505,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1531,7 +1515,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1541,7 +1525,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1551,22 +1535,22 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>36</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-bairro-novo-RS1700/id-45733416/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1558,7 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1582,27 +1566,27 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · Encruzilhada</t>
+          <t>Apartamento · 2 quartos · 49 m² · Espinheiro</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Da Hora, 235</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1750.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>500.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1612,29 +1596,29 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1750.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>53.03</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="O13" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -1642,22 +1626,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/123-rua-carlos-borromeu-de-frente-para-o-mercado-da-encruzilhada/850471068-78</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-pe-recife-espinheiro-49m2-RS2000/id-44279997/</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1649,7 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1673,7 +1657,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · Santo Amaro</t>
+          <t>Apartamento · 1 quarto · 31 m² · Parnamirim</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1683,42 +1667,42 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1450.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>405.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>80.96</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1935.96</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>38.72</t>
+          <t>80.65</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1733,22 +1717,22 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/6691/apartamento-2-quartos-santo-amaro-recife/</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/n%C2%BA-50-rua-condado-perto-do-cafe-sao-braz/850091040-261</t>
         </is>
       </c>
     </row>
@@ -1764,12 +1748,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rua Coronel Alberto Lundgren, 604</t>
+          <t>Avenida Presidente Getúlio Vargas, 1748</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1784,17 +1768,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>683.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2576.0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1804,7 +1788,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>71.56</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1824,22 +1808,22 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS1800/id-46397377/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-36m2-RS1800/id-45673358/</t>
         </is>
       </c>
     </row>
@@ -1847,35 +1831,35 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 1382 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · Aflitos</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rua Doutor Manoel de Barros Lima</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2150.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1885,27 +1869,27 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2150.0</t>
+          <t>2691.0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1915,22 +1899,22 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1382.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-bairro-novo-bairros-olinda-1382m2-aluguel-RS2150-id-2911542521/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-aflitos-recife--pe_33374631</t>
         </is>
       </c>
     </row>
@@ -1946,37 +1930,37 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rua Coronel Alberto Lundgren, 604</t>
+          <t>Rua Otaviano Pessoa Monteiro, 93</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1526.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>1178.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2704.0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1986,19 +1970,19 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>29.08</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O17" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -2006,7 +1990,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2021,7 +2005,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS2000/id-46397376/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1526/id-45586419/</t>
         </is>
       </c>
     </row>
@@ -2029,35 +2013,35 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>CTI Imobiliária</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 65 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rua Professor José Cândido Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>380.0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2067,17 +2051,17 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2880.0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>33.85</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2087,7 +2071,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2097,22 +2081,22 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-65m2-aluguel-RS2200-id-2897302602/?source=ranking%2Crp</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-torre-recife-pe/1353</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2104,7 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2128,37 +2112,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rua Professor José Cândido Pessoa</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>684.0</t>
+          <t>380.0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>176.42</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2477.0</t>
+          <t>2956.42</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2168,17 +2152,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>68.81</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2188,22 +2172,22 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-720m2-RS1700/id-43805924/</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/6596/apartamento-2-quartos-torre-recife/</t>
         </is>
       </c>
     </row>
@@ -2211,20 +2195,20 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 70 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 40 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rua Nereu Gomes Maciel</t>
+          <t>Avenida Governador Carlos De Lima Cavalcante, 2595</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2234,7 +2218,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2499.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2249,7 +2233,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2499.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2259,42 +2243,42 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-70m2-aluguel-RS2499-id-2903057019/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-40m2-RS3000/id-45710865/</t>
         </is>
       </c>
     </row>
@@ -2310,12 +2294,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 42 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rua João Clementino Montarroyos</t>
+          <t>Avenida Doutor José Augusto Moreira, 900</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2325,7 +2309,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2340,7 +2324,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2350,12 +2334,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2370,22 +2354,22 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-77m2-RS2500/id-45938196/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-RS3000/id-44380568/</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2377,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2401,27 +2385,27 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 49 m² · Espinheiro</t>
+          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rua Da Hora, 235</t>
+          <t>Rua Otaviano Pessoa Monteiro, 93</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1822.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>500.0</t>
+          <t>1178.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2431,7 +2415,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2441,7 +2425,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>32.26</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2461,7 +2445,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2476,7 +2460,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-pe-recife-espinheiro-49m2-RS2000/id-44279997/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1822/id-45585830/</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2468,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2492,22 +2476,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 31 m² · Parnamirim</t>
+          <t>Apartamento · 3 quartos · 92 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Carlos De Lima Cavalcante</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2522,7 +2506,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2532,17 +2516,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>80.65</t>
+          <t>32.61</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2552,22 +2536,22 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/n%C2%BA-50-rua-condado-perto-do-cafe-sao-braz/850091040-261</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS3000/id-42437394/</t>
         </is>
       </c>
     </row>
@@ -2575,55 +2559,55 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 38 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Rua Cardeal Arcoverde, 276</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2332.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>550.0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>65.79</t>
+          <t>93.75</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2638,27 +2622,27 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-38m2-aluguel-RS2500-id-2698090477/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS2332/id-46081872/</t>
         </is>
       </c>
     </row>
@@ -2666,30 +2650,30 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Josinildo Imóveis</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 42 m² · Torre</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2704,7 +2688,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2714,17 +2698,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2734,22 +2718,22 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/flat-1-quartos-bairro-novo-bairros-olinda-com-garagem-35m2-aluguel-RS2500-id-2901073105/?source=ranking%2Crp</t>
+          <t>https://josinildoimoveis.com.br/imovel/edf-green-life-torre/PARJI03</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2741,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2765,47 +2749,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Avenida Presidente Getúlio Vargas, 1748</t>
+          <t>Rua Amélia, 623</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>683.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2576.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>71.56</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2825,7 +2809,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2840,7 +2824,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-36m2-RS1800/id-45673358/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-RS3200/id-45197779/</t>
         </is>
       </c>
     </row>
@@ -2848,30 +2832,30 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Newville</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 71 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 52 m² · Torre</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rua Gildo Branco</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2600.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2886,7 +2870,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2600.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2896,17 +2880,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>36.62</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2916,22 +2900,22 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-71m2-aluguel-RS2600-id-2911301943/?source=ranking%2Crp</t>
+          <t>https://newville.com.br/imovel/apartamento_2_quartos--torre--recife--pe--locacao--cod-6391</t>
         </is>
       </c>
     </row>
@@ -2947,7 +2931,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · Aflitos</t>
+          <t>Apartamento · 1 quarto · 38 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2957,17 +2941,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2977,22 +2961,22 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2691.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3007,22 +2991,22 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-aflitos-recife--pe_33374631</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-1-quarto-alugar-38m2-boa-vista-recife--pe_33378812</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3014,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3038,37 +3022,37 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 70 m² · 1 vaga · Casa Amarela</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa Monteiro, 93</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1526.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1178.0</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>237.0</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2704.0</t>
+          <t>3202.0</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3078,7 +3062,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>45.74</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3088,7 +3072,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3098,7 +3082,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -3113,7 +3097,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1526/id-45586419/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-amarela-70m2-RS2000/id-43758789/</t>
         </is>
       </c>
     </row>
@@ -3121,30 +3105,30 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 66 m² · 1 vaga · Campo Grande</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Rua Barão De Vera Cruz</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Campo Grande</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3159,7 +3143,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3169,42 +3153,42 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-36m2-aluguel-RS2800-id-2705654338/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-campo-grande-79m2-RS3300/id-44353442/</t>
         </is>
       </c>
     </row>
@@ -3212,20 +3196,20 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 65 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Rua Eduardo De Moraes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3235,32 +3219,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>422.0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3317.0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3270,7 +3254,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3280,22 +3264,22 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-60m2-aluguel-RS2800-id-2912116616/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-1038m2-RS2700/id-27611651/</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3287,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CTI Imobiliária</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -3311,27 +3295,27 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
+          <t>Apartamento · 2 quartos · 59 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Pereira Simões, 1529 - 2</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>380.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3341,17 +3325,17 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2880.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>59.32</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3361,7 +3345,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3371,22 +3355,22 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-torre-recife-pe/1353</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-59m2-RS3500/id-45711136/</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3378,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -3402,47 +3386,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
+          <t>Apartamento · 2 quartos · 57 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Francisco Ambrósio De Barros Leite, 1225</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>380.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>176.42</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2956.42</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3452,7 +3436,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3462,7 +3446,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3477,7 +3461,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/6596/apartamento-2-quartos-torre-recife/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-RS3500/id-42986293/</t>
         </is>
       </c>
     </row>
@@ -3485,30 +3469,30 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 42 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 50 m² · 1 vaga · Torre</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rua Ulisses Tenório de Albuquerque</t>
+          <t>Rua Real Da Torre</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2998.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3523,7 +3507,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2998.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3533,7 +3517,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>71.38</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3553,22 +3537,22 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-42m2-aluguel-RS2998-id-2911376544/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-50m2-RS3500/id-46933917/</t>
         </is>
       </c>
     </row>
@@ -3576,30 +3560,30 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Recife, Rogério Corretor</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 40 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos De Lima Cavalcante, 2595</t>
+          <t>Rua Cardeal Arcoverde, 1</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3614,7 +3598,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3624,7 +3608,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>106.06</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3644,7 +3628,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -3659,7 +3643,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-40m2-RS3000/id-45710865/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS3500/id-45844382/</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3651,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3675,27 +3659,27 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 42 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 70 m² · Tamarineira</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Avenida Doutor José Augusto Moreira, 900</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Tamarineira</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3705,27 +3689,27 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3735,7 +3719,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3750,7 +3734,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-RS3000/id-44380568/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-70m2-tamarineira-recife--pe_33364198</t>
         </is>
       </c>
     </row>
@@ -3758,7 +3742,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3766,27 +3750,27 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 77 m² · Torre</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa Monteiro, 93</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1822.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1178.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3796,27 +3780,27 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>32.26</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3826,22 +3810,22 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1822/id-45585830/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-77m2-torre-recife--pe_33379670</t>
         </is>
       </c>
     </row>
@@ -3849,7 +3833,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3857,27 +3841,27 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 92 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 82 m² · Casa Forte</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Avenida Carlos De Lima Cavalcante</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Casa Forte</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3887,27 +3871,27 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>42.68</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3917,7 +3901,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3932,7 +3916,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS3000/id-42437394/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-82m2-casa-forte-recife--pe_33364920</t>
         </is>
       </c>
     </row>
@@ -3940,45 +3924,45 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>CTI Imobiliária, Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Boa Vista</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rua Cardeal Arcoverde, 276</t>
+          <t>Avenida Governador Carlos De Lima Cavalcanti, 60</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2332.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>550.0</t>
+          <t>553.0</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>174.0</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3527.0</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3988,19 +3972,19 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>93.75</t>
+          <t>80.16</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O39" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -4008,22 +3992,22 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS2332/id-46081872/</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6519</t>
         </is>
       </c>
     </row>
@@ -4031,65 +4015,65 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>CTI Imobiliária</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 41 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>550.0</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3542.0</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>86.39</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4099,22 +4083,22 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-35m2-aluguel-RS3000-id-2913485117/?source=ranking%2Crp</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6210</t>
         </is>
       </c>
     </row>
@@ -4122,30 +4106,30 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 68 m² · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Parnamirim</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Avenida Parnamirim, 375</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4160,7 +4144,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4170,17 +4154,17 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>44.12</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4190,22 +4174,22 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-68m2-aluguel-RS3000-id-2913457037/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-32m2-RS3600/id-41530823/</t>
         </is>
       </c>
     </row>
@@ -4213,25 +4197,25 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 60 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 34 m² · 1 vaga · Parnamirim</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Avenida Parnamirim, 375</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4241,7 +4225,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>600.0</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4251,17 +4235,17 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>105.88</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4281,22 +4265,22 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3000-id-2859906255/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-55m2-RS3000/id-46882194/</t>
         </is>
       </c>
     </row>
@@ -4304,7 +4288,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Zap Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -4312,22 +4296,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 34 m² · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Torre</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Avenida Governador Agamenon Magalhães</t>
+          <t>Rua José De Holanda, 854</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4342,7 +4326,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3601.0</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4352,42 +4336,42 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>81.84</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-1-quarto-com-piscina-boa-vista-recife-pe-34m2-id-2913394619/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-RS3600/id-40119104/</t>
         </is>
       </c>
     </row>
@@ -4395,7 +4379,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Josinildo Imóveis</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -4403,7 +4387,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 42 m² · Torre</t>
+          <t>Apartamento · 2 quartos · 51 m² · Aflitos</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4413,12 +4397,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>3699.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4433,7 +4417,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>3699.0</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4443,7 +4427,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>72.53</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4463,22 +4447,22 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>https://josinildoimoveis.com.br/imovel/edf-green-life-torre/PARJI03</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/307-rua-manuel-de-carvalho/850701030-101</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4470,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -4494,27 +4478,27 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 3 quartos · Encruzilhada</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rua Amélia, 623</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3700.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4524,27 +4508,27 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3700.0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4554,7 +4538,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -4569,7 +4553,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-RS3200/id-45197779/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-encruzilhada-recife--pe_33362592</t>
         </is>
       </c>
     </row>
@@ -4577,7 +4561,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Newville</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4585,7 +4569,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 52 m² · Torre</t>
+          <t>Apartamento · 3 quartos · 90 m² · Graças</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4595,42 +4579,42 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>2300.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1300.0</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>185.21</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3785.21</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4645,22 +4629,22 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>https://newville.com.br/imovel/apartamento_2_quartos--torre--recife--pe--locacao--cod-6391</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/2698/apartamento-3-quartos-san-patrick-graças-recife/</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4660,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 38 m² · Boa Vista</t>
+          <t>Apartamento · 3 quartos · Rosarinho</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4686,12 +4670,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Rosarinho</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3800.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4706,7 +4690,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3800.0</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4716,12 +4700,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4736,22 +4720,22 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-1-quarto-alugar-38m2-boa-vista-recife--pe_33378812</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-rosarinho-recife--pe_33388298</t>
         </is>
       </c>
     </row>
@@ -4759,30 +4743,30 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 57 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 50 m² · Torre</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rua Pereira Simões</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3900.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4797,7 +4781,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3900.0</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4807,7 +4791,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>56.14</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4817,32 +4801,32 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-57m2-aluguel-RS3200-id-2901326206/?source=ranking%2Crp</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/211-rua-conselheiro-theodoro/850701030-95</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4834,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -4858,7 +4842,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · 1 vaga · Casa Amarela</t>
+          <t>Apartamento · 2 quartos · 51 m² · Aflitos</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4868,37 +4852,37 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>3990.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>237.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>3202.0</t>
+          <t>3990.0</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>45.74</t>
+          <t>78.24</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4908,32 +4892,32 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>51.0</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-amarela-70m2-RS2000/id-43758789/</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/307-manuel-de-carvalho-edificio-praca-das-cerejeiras/850721013-37</t>
         </is>
       </c>
     </row>
@@ -4941,30 +4925,30 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Chaves na Mão Recife, Josinildo Imóveis</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 66 m² · 1 vaga · Campo Grande</t>
+          <t>Apartamento · 3 quartos · 74 m² · 1 vaga · Aflitos</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rua Barão De Vera Cruz</t>
+          <t>Rua Da Angustura, 195</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Campo Grande</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>4091.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4979,7 +4963,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>4091.0</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4989,7 +4973,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>55.28</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4999,7 +4983,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5009,22 +4993,22 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-campo-grande-79m2-RS3300/id-44353442/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-aflitos-74m2-RS4091/id-46898128/</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5016,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda, Rogério Corretor</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -5040,22 +5024,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 58 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 145 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rua Pereira Simões</t>
+          <t>Avenida Min. Marcos Freire, 3495</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>4100.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5070,7 +5054,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>4100.0</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5080,17 +5064,17 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5100,22 +5084,22 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-58m2-aluguel-RS3300-id-2913435980/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4100/id-46901493/</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5107,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -5131,22 +5115,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 59 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Aflitos</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rua Pereira Simões, 1529 - 2</t>
+          <t>Avenida Conselheiro Rosa E Silva, 801</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4141.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5161,7 +5145,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4142.0</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5171,7 +5155,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>59.32</t>
+          <t>75.31</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5191,22 +5175,22 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-59m2-RS3500/id-45711136/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-aflitos-55m2-RS4141/id-45283901/</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5198,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -5222,27 +5206,27 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 57 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 43 m² · Casa Amarela</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rua Francisco Ambrósio De Barros Leite, 1225</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4200.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5252,17 +5236,17 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4200.0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>97.67</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5272,7 +5256,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5282,22 +5266,22 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-RS3500/id-42986293/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-43m2-casa-amarela-recife--pe_33376830</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5289,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Rogério Corretor</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -5313,27 +5297,27 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · 1 vaga · Torre</t>
+          <t>Apartamento · 2 quartos · 80 m² · Aflitos</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rua Real Da Torre</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5343,17 +5327,17 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4350.0</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>54.38</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5363,7 +5347,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5373,22 +5357,22 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-50m2-RS3500/id-46933917/</t>
+          <t>https://www.rogeriocorretor.com/imovel/apartamento-2-quartos-aflitos-recife-1-vaga-80m2-code-695</t>
         </is>
       </c>
     </row>
@@ -5396,35 +5380,35 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife, Rogério Corretor</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rua Cardeal Arcoverde, 1</t>
+          <t>Avenida Governador Carlos De Lima Cavalcante</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1195.0</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5434,29 +5418,29 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4395.0</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>106.06</t>
+          <t>79.91</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O55" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -5464,7 +5448,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -5479,7 +5463,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS3500/id-45844382/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-55m2-RS3200/id-46174975/</t>
         </is>
       </c>
     </row>
@@ -5487,7 +5471,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -5495,27 +5479,27 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · Tamarineira</t>
+          <t>Apartamento · 3 quartos · 85 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Ministro Marcos Freire</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tamarineira</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5525,27 +5509,27 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5555,7 +5539,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -5570,7 +5554,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-70m2-tamarineira-recife--pe_33364198</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-110m2-RS4500/id-42417501/</t>
         </is>
       </c>
     </row>
@@ -5578,7 +5562,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -5586,22 +5570,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · Torre</t>
+          <t>Apartamento · 3 quartos · 97 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Ministro Marcos Freire, 3291</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5616,7 +5600,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5626,7 +5610,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>46.39</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -5636,7 +5620,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5646,22 +5630,22 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-77m2-torre-recife--pe_33379670</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4500/id-46421413/</t>
         </is>
       </c>
     </row>
@@ -5669,7 +5653,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -5677,27 +5661,27 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 82 m² · Casa Forte</t>
+          <t>Apartamento · 2 quartos · 56 m² · 1 vaga · Espinheiro</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua São Salvador, 200</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Casa Forte</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5707,17 +5691,17 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>42.68</t>
+          <t>80.36</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5727,7 +5711,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5737,22 +5721,22 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-82m2-casa-forte-recife--pe_33364920</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-espinheiro-70m2-RS4500/id-46923849/</t>
         </is>
       </c>
     </row>
@@ -5760,30 +5744,30 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Rogério Corretor</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 59 m² · Bairro Novo</t>
+          <t>Apartamento · 4 quartos · 90 m² · Torre</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rua Pereira Simões</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5798,7 +5782,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4500.0</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5808,42 +5792,42 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>59.32</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-59m2-aluguel-RS3500-id-2905566215/?source=ranking%2Crp</t>
+          <t>https://www.rogeriocorretor.com/imovel/casa-4-quartos-torre-recife-90m2-code-736</t>
         </is>
       </c>
     </row>
@@ -5851,30 +5835,30 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Apartamento · 4 quartos · 160 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Parnamirim</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Avenida Parnamirim</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4700.0</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5889,7 +5873,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>4700.0</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5899,42 +5883,42 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>21.88</t>
+          <t>78.33</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-casa-caiada-bairros-olinda-com-garagem-160m2-aluguel-RS3500-id-2909290334/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-parnamirim-RS4700/id-43942857/</t>
         </is>
       </c>
     </row>
@@ -5942,30 +5926,30 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 115 m² · 2 vagas · Casa Caiada</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Avenida Ministro Marcos Freire</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>5000.0</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5980,7 +5964,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>5000.0</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -5990,17 +5974,17 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>43.48</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6010,22 +5994,22 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-60m2-aluguel-RS3500-id-2904577437/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-115m2-RS5000/id-47073028/</t>
         </is>
       </c>
     </row>
@@ -6033,65 +6017,65 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CTI Imobiliária, Chaves na Mão Recife</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Boa Vista</t>
+          <t>Apartamento · 3 quartos · 89 m² · Torre</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos De Lima Cavalcanti, 60</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>5500.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>553.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>3527.0</t>
+          <t>5500.0</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>80.16</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6101,2477 +6085,20 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
-        <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6519</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>CTI Imobiliária</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 41 m² · Boa Vista</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Boa Vista</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>2800.0</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>550.0</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>192.0</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>3542.0</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>86.39</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>41.0</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6210</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Recife</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Parnamirim</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Avenida Parnamirim, 375</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Parnamirim</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>112.5</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>32.0</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-32m2-RS3600/id-41530823/</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Recife</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Apartamento · 1 quarto · 34 m² · 1 vaga · Parnamirim</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Avenida Parnamirim, 375</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Parnamirim</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>600.0</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>105.88</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>34.0</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-55m2-RS3000/id-46882194/</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Zap Imóveis</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>1</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Apartamento · 4 quartos · 120 m² · Boa Vista</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Rua Dom Carlos Coelho</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Boa Vista</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>120.0</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-4-quartos-boa-vista-recife-pe-120m2-id-2913416134/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr"/>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Recife</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>1</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Torre</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Rua José De Holanda, 854</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Torre</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>3601.0</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>81.84</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>44.0</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-RS3600/id-40119104/</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr"/>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>REMAX Recife e Olinda</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>1</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 51 m² · Aflitos</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Aflitos</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>3699.0</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>3699.0</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>72.53</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>51.0</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/307-rua-manuel-de-carvalho/850701030-101</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr"/>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Portal CRECI Brasil</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>1</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · Encruzilhada</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Encruzilhada</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>3700.0</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>3700.0</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-encruzilhada-recife--pe_33362592</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr"/>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Âncora Imobiliária</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 90 m² · Graças</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Graças</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>2300.0</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>1300.0</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>185.21</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>3785.21</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>42.06</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/2698/apartamento-3-quartos-san-patrick-graças-recife/</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr"/>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Portal CRECI Brasil</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>1</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · Rosarinho</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Rosarinho</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>3800.0</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>3800.0</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-rosarinho-recife--pe_33388298</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr"/>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>2</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 67 m² · Bairro Novo</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Rua Pereira Simões</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Bairro Novo</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>3800.0</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>3800.0</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>56.72</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-67m2-aluguel-RS3800-id-2906555835/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr"/>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>REMAX Recife e Olinda</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>1</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 50 m² · Torre</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Torre</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>3900.0</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>3900.0</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>78.0</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/211-rua-conselheiro-theodoro/850701030-95</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr"/>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>2</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Rua Joana D'Arc Sampaio</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>3900.0</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>3902.0</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>65.03</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3900-id-2913026520/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>REMAX Recife e Olinda</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>1</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 51 m² · Aflitos</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Aflitos</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>3990.0</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>3990.0</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>78.24</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>51.0</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/307-manuel-de-carvalho-edificio-praca-das-cerejeiras/850721013-37</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr"/>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Recife, Josinildo Imóveis</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>2</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 74 m² · 1 vaga · Aflitos</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Rua Da Angustura, 195</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Aflitos</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>4091.0</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>4091.0</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>55.28</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-aflitos-74m2-RS4091/id-46898128/</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr"/>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda, Rogério Corretor</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>2</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 145 m² · 2 vagas · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Avenida Min. Marcos Freire, 3495</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>4100.0</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>4100.0</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>28.28</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>145.0</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R77" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4100/id-46901493/</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr"/>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Recife</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>1</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Aflitos</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Avenida Conselheiro Rosa E Silva, 801</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Aflitos</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>4141.0</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>4142.0</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>75.31</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R78" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-aflitos-55m2-RS4141/id-45283901/</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Portal CRECI Brasil</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>1</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 43 m² · Casa Amarela</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Casa Amarela</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>4200.0</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>4200.0</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>97.67</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>43.0</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R79" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-43m2-casa-amarela-recife--pe_33376830</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Rogério Corretor</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 80 m² · Aflitos</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Aflitos</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>750.0</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>4350.0</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>54.38</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>https://www.rogeriocorretor.com/imovel/apartamento-2-quartos-aflitos-recife-1-vaga-80m2-code-695</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>1</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Avenida Governador Carlos De Lima Cavalcante</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>3200.0</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>1195.0</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>4395.0</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>79.91</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R81" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-55m2-RS3200/id-46174975/</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>1</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 85 m² · 2 vagas · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Avenida Ministro Marcos Freire</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>52.94</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-110m2-RS4500/id-42417501/</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr"/>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>1</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 97 m² · 2 vagas · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Avenida Ministro Marcos Freire, 3291</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>46.39</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>97.0</t>
-        </is>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R83" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4500/id-46421413/</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Recife</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>1</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 56 m² · 1 vaga · Espinheiro</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Rua São Salvador, 200</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Espinheiro</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>80.36</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>56.0</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-espinheiro-70m2-RS4500/id-46923849/</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr"/>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Rogério Corretor</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>1</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Apartamento · 4 quartos · 90 m² · Torre</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Torre</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R85" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>https://www.rogeriocorretor.com/imovel/casa-4-quartos-torre-recife-90m2-code-736</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr"/>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Zap Imóveis</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>1</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Apartamento · 4 quartos · 100 m² · Graças</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Rua das Graças</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Graças</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>4500.0</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>45.0</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R86" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>https://www.zapimoveis.com.br/imovel/aluguel-apartamento-4-quartos-gracas-recife-pe-100m2-id-2913720624/?source=ranking%2Crp</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr"/>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Recife</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>1</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Parnamirim</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Avenida Parnamirim</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Parnamirim</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>4700.0</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>4700.0</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>78.33</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-parnamirim-RS4700/id-43942857/</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr"/>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Chaves na Mão Olinda</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>1</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 115 m² · 2 vagas · Casa Caiada</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Avenida Ministro Marcos Freire</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Casa Caiada</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>43.48</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R88" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-115m2-RS5000/id-47073028/</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr"/>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Portal CRECI Brasil</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>1</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Apartamento · 3 quartos · 89 m² · Torre</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Torre</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>5500.0</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>5500.0</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>61.8</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>89.0</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R89" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="S89" t="inlineStr">
         <is>
           <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-89m2-torre-recife--pe_33386591</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S62"/>
+  <dimension ref="A1:S83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -561,22 +561,22 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 36 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 1322 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos De Lima Cavalcante</t>
+          <t>Rua Doutor Manoel de Barros Lima</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2150.0</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2150.0</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -601,12 +601,12 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>69.44</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>1322.0</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-36m2-RS2500/id-47122887/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-bairro-novo-bairros-olinda-1322m2-aluguel-RS2150-id-2914115768/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -656,59 +656,59 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 65 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 90 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Rua Eduardo De Moraes, 85</t>
+          <t>Rua Coronel João Manguinhos</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>421.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>3316.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -716,7 +716,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-65m2-RS2700/id-47042111/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-bairros-olinda-com-garagem-90m2-aluguel-RS3600-id-2914003157/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · Encruzilhada</t>
+          <t>Apartamento · 2 quartos · 50 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1030,42 +1030,42 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1750.0</t>
+          <t>1450.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>405.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>80.96</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1750.0</t>
+          <t>1935.96</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>53.03</t>
+          <t>38.72</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1080,22 +1080,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/123-rua-carlos-borromeu-de-frente-para-o-mercado-da-encruzilhada/850471068-78</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/6691/apartamento-2-quartos-santo-amaro-recife/</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1111,37 +1111,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · Santo Amaro</t>
+          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Coronel Alberto Lundgren, 604</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1450.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>405.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>80.96</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1935.96</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>38.72</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1171,22 +1171,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/6691/apartamento-2-quartos-santo-amaro-recife/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS1800/id-46397377/</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1267,17 +1267,17 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS1800/id-46397377/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS2000/id-46397376/</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 65 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rua Coronel Alberto Lundgren, 604</t>
+          <t>Rua Professor José Cândido Pessoa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1328,22 +1328,22 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1353,22 +1353,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS2000/id-46397376/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-65m2-aluguel-RS2200-id-2897302602/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1566,27 +1566,27 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 49 m² · Espinheiro</t>
+          <t>Apartamento · 2 quartos · 36 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rua Da Hora, 235</t>
+          <t>Avenida Governador Carlos De Lima Cavalcante</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>500.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>69.44</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1626,22 +1626,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-pe-recife-espinheiro-49m2-RS2000/id-44279997/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-36m2-RS2500/id-47122887/</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1657,59 +1657,59 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 31 m² · Parnamirim</t>
+          <t>Apartamento · 2 quartos · 49 m² · Espinheiro</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Da Hora, 235</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2500.0</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>80.65</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -1717,22 +1717,22 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/n%C2%BA-50-rua-condado-perto-do-cafe-sao-braz/850091040-261</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-pe-recife-espinheiro-49m2-RS2000/id-44279997/</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1748,47 +1748,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 31 m² · Parnamirim</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Avenida Presidente Getúlio Vargas, 1748</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>683.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2576.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>71.56</t>
+          <t>80.65</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1808,22 +1808,22 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-36m2-RS1800/id-45673358/</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/n%C2%BA-50-rua-condado-perto-do-cafe-sao-braz/850091040-261</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1839,37 +1839,37 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · Aflitos</t>
+          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Presidente Getúlio Vargas, 1748</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>191.0</t>
+          <t>683.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2691.0</t>
+          <t>2576.0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1879,17 +1879,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>71.56</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-aflitos-recife--pe_33374631</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-36m2-RS1800/id-45673358/</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1930,27 +1930,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 35 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa Monteiro, 93</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1526.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1178.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1960,22 +1960,22 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2704.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>74.29</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1985,27 +1985,27 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1526/id-45586419/</t>
+          <t>https://www.vivareal.com.br/imovel/flat-1-quartos-bairro-novo-bairros-olinda-com-garagem-35m2-aluguel-RS2600-id-2912188115/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2013,7 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CTI Imobiliária</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2021,27 +2021,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
+          <t>Apartamento · 3 quartos · 71 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Gildo Branco</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>380.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2051,29 +2051,29 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2880.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>36.62</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="O18" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -2081,22 +2081,22 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-torre-recife-pe/1353</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-71m2-aluguel-RS2600-id-2911876830/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2112,59 +2112,59 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
+          <t>Apartamento · 3 quartos · 71 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Gildo Branco</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>380.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>176.42</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2956.42</t>
+          <t>2600.0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>36.62</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
       <c r="O19" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -2172,22 +2172,22 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/6596/apartamento-2-quartos-torre-recife/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-71m2-aluguel-RS2600-id-2911301943/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2195,7 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2203,27 +2203,27 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 40 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · Aflitos</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos De Lima Cavalcante, 2595</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2233,27 +2233,27 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>2691.0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-40m2-RS3000/id-45710865/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-aflitos-recife--pe_33374631</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2294,22 +2294,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 42 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 77 m² · Santana</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Avenida Doutor José Augusto Moreira, 900</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Santana</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2334,42 +2334,42 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>35.06</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-RS3000/id-44380568/</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/458-santanna-proximo-ao-parque-de-santana/850501009-266</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 30 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa Monteiro, 93</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1822.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1178.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2415,22 +2415,22 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>32.26</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2445,22 +2445,22 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1822/id-45585830/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-30m2-aluguel-RS2700-id-2913849795/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2476,12 +2476,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 92 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Avenida Carlos De Lima Cavalcante</t>
+          <t>Rua Otaviano Pessoa Monteiro, 93</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>1526.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1178.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2506,27 +2506,27 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>2704.0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>29.08</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS3000/id-42437394/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1526/id-45586419/</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2567,57 +2567,57 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 2 quartos · 60 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rua Cardeal Arcoverde, 276</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2332.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>550.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>93.75</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2627,22 +2627,22 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS2332/id-46081872/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-60m2-aluguel-RS2800-id-2912116616/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Josinildo Imóveis</t>
+          <t>CTI Imobiliária</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 42 m² · Torre</t>
+          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2673,12 +2673,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>380.0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2688,17 +2688,17 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>2880.0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2718,22 +2718,22 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>https://josinildoimoveis.com.br/imovel/edf-green-life-torre/PARJI03</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-torre-recife-pe/1353</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2749,57 +2749,57 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rua Amélia, 623</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>380.0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>176.42</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>2956.42</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-RS3200/id-45197779/</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/6596/apartamento-2-quartos-torre-recife/</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Newville</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2840,22 +2840,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 52 m² · Torre</t>
+          <t>Apartamento · 2 quartos · 42 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Ulisses Tenório de Albuquerque</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>2998.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>2998.0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>71.38</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2900,22 +2900,22 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>https://newville.com.br/imovel/apartamento_2_quartos--torre--recife--pe--locacao--cod-6391</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-42m2-aluguel-RS2998-id-2911376544/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2923,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2931,22 +2931,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 38 m² · Boa Vista</t>
+          <t>Apartamento · 1 quarto · 40 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos De Lima Cavalcante, 2595</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2991,22 +2991,22 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-1-quarto-alugar-38m2-boa-vista-recife--pe_33378812</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-40m2-RS3000/id-45710865/</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3022,57 +3022,57 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · 1 vaga · Casa Amarela</t>
+          <t>Apartamento · 1 quarto · 42 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Doutor José Augusto Moreira, 900</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>237.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3202.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>45.74</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-amarela-70m2-RS2000/id-43758789/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-casa-caiada-RS3000/id-44380568/</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3105,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -3113,27 +3113,27 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 66 m² · 1 vaga · Campo Grande</t>
+          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rua Barão De Vera Cruz</t>
+          <t>Rua Otaviano Pessoa Monteiro, 93</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Campo Grande</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>1822.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1178.0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3143,22 +3143,22 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>32.26</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-campo-grande-79m2-RS3300/id-44353442/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1822/id-45585830/</t>
         </is>
       </c>
     </row>
@@ -3204,59 +3204,59 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 65 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 92 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rua Eduardo De Moraes</t>
+          <t>Avenida Carlos De Lima Cavalcante</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>422.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>3317.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>51.03</t>
+          <t>32.61</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O31" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -3264,22 +3264,22 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-1038m2-RS2700/id-27611651/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS3000/id-42437394/</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -3295,57 +3295,57 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 59 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rua Pereira Simões, 1529 - 2</t>
+          <t>Rua Cardeal Arcoverde, 276</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>2332.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>550.0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>59.32</t>
+          <t>93.75</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3355,22 +3355,22 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-59m2-RS3500/id-45711136/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS2332/id-46081872/</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -3386,22 +3386,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 57 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 34 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rua Francisco Ambrósio De Barros Leite, 1225</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3426,42 +3426,42 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>57.0</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-RS3500/id-42986293/</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/185-rua-dom-pedro-henrique-prox-a-catolica/850301004-158</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3477,22 +3477,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · 1 vaga · Torre</t>
+          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rua Real Da Torre</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3537,22 +3537,22 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-50m2-RS3500/id-46933917/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3000-id-2913637829/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3560,30 +3560,30 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife, Rogério Corretor</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 1 quarto · 35 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rua Cardeal Arcoverde, 1</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>106.06</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3628,22 +3628,22 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS3500/id-45844382/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-35m2-aluguel-RS3000-id-2913485117/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3659,27 +3659,27 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · Tamarineira</t>
+          <t>Apartamento · 2 quartos · 68 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tamarineira</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3689,17 +3689,17 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>44.12</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3719,22 +3719,22 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-70m2-tamarineira-recife--pe_33364198</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-68m2-aluguel-RS3000-id-2913457037/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Josinildo Imóveis</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · Torre</t>
+          <t>Apartamento · 2 quartos · 42 m² · Torre</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3790,12 +3790,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3810,22 +3810,22 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-77m2-torre-recife--pe_33379670</t>
+          <t>https://josinildoimoveis.com.br/imovel/edf-green-life-torre/PARJI03</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3833,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -3841,27 +3841,27 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 82 m² · Casa Forte</t>
+          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Amélia, 623</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Casa Forte</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3871,27 +3871,27 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>42.68</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-82m2-casa-forte-recife--pe_33364920</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-RS3200/id-45197779/</t>
         </is>
       </c>
     </row>
@@ -3924,55 +3924,55 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CTI Imobiliária, Chaves na Mão Recife</t>
+          <t>Newville</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 52 m² · Torre</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos De Lima Cavalcanti, 60</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>553.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>3527.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>80.16</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3992,22 +3992,22 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6519</t>
+          <t>https://newville.com.br/imovel/apartamento_2_quartos--torre--recife--pe--locacao--cod-6391</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4015,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CTI Imobiliária</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 41 m² · Boa Vista</t>
+          <t>Apartamento · 1 quarto · 38 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4038,37 +4038,37 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>550.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>3542.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>86.39</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4083,22 +4083,22 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6210</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-1-quarto-alugar-38m2-boa-vista-recife--pe_33378812</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -4114,22 +4114,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Parnamirim</t>
+          <t>Apartamento · 1 quarto · 40 m² · Santana</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Avenida Parnamirim, 375</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Santana</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-32m2-RS3600/id-41530823/</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/70-rua-samuel-de-farias/850091105-39</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4197,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -4205,27 +4205,27 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 34 m² · 1 vaga · Parnamirim</t>
+          <t>Apartamento · 1 quarto · 35 m² · Encruzilhada</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Avenida Parnamirim, 375</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>600.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4235,17 +4235,17 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>105.88</t>
+          <t>91.43</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-55m2-RS3000/id-46882194/</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/68-rua-engenheiro-sampaio/850701030-102</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4288,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -4296,22 +4296,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Torre</t>
+          <t>Apartamento · 2 quartos · 57 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rua José De Holanda, 854</t>
+          <t>Rua Pereira Simões</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>3601.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>81.84</t>
+          <t>56.14</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-RS3600/id-40119104/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-57m2-aluguel-RS3200-id-2901326206/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4379,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -4387,22 +4387,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 51 m² · Aflitos</t>
+          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>3699.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>3699.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>72.53</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4447,22 +4447,22 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/307-rua-manuel-de-carvalho/850701030-101</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3200-id-2686319323/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · Encruzilhada</t>
+          <t>Apartamento · 2 quartos · 70 m² · 1 vaga · Casa Amarela</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4488,27 +4488,27 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>3700.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>237.0</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>3700.0</t>
+          <t>3202.0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4518,17 +4518,17 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>45.74</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-encruzilhada-recife--pe_33362592</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-amarela-70m2-RS2000/id-43758789/</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -4569,47 +4569,47 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 90 m² · Graças</t>
+          <t>Apartamento · 3 quartos · 66 m² · 1 vaga · Campo Grande</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Barão De Vera Cruz</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Campo Grande</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2300.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1300.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>185.21</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>3785.21</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>42.06</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4629,22 +4629,22 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/2698/apartamento-3-quartos-san-patrick-graças-recife/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-campo-grande-79m2-RS3300/id-44353442/</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4652,7 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4660,22 +4660,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · Rosarinho</t>
+          <t>Apartamento · 2 quartos · 58 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Pereira Simões</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosarinho</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>3800.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>3800.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4700,42 +4700,42 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>58.0</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-rosarinho-recife--pe_33388298</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-58m2-aluguel-RS3300-id-2913435980/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4743,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -4751,47 +4751,47 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · Torre</t>
+          <t>Apartamento · 2 quartos · 65 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Eduardo De Moraes, 85</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3900.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>421.0</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>3900.0</t>
+          <t>3316.0</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4811,22 +4811,22 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/211-rua-conselheiro-theodoro/850701030-95</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-65m2-RS2700/id-47042111/</t>
         </is>
       </c>
     </row>
@@ -4834,55 +4834,55 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 51 m² · Aflitos</t>
+          <t>Apartamento · 2 quartos · 65 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Eduardo de Moraes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>3990.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>422.0</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>3990.0</t>
+          <t>3317.0</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>78.24</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4902,22 +4902,22 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/307-manuel-de-carvalho-edificio-praca-das-cerejeiras/850721013-37</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-1038m2-RS2700/id-27611651/</t>
         </is>
       </c>
     </row>
@@ -4925,30 +4925,30 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife, Josinildo Imóveis</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 74 m² · 1 vaga · Aflitos</t>
+          <t>Apartamento · 2 quartos · 59 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rua Da Angustura, 195</t>
+          <t>Rua Pereira Simões, 1529 - 2</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>4091.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>4091.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4973,17 +4973,17 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>55.28</t>
+          <t>59.32</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4993,22 +4993,22 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-aflitos-74m2-RS4091/id-46898128/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-59m2-RS3500/id-45711136/</t>
         </is>
       </c>
     </row>
@@ -5016,30 +5016,30 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Rogério Corretor</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 145 m² · 2 vagas · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 57 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Avenida Min. Marcos Freire, 3495</t>
+          <t>Rua Francisco Ambrósio De Barros Leite, 1225</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>4100.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>4100.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5064,17 +5064,17 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5084,22 +5084,22 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4100/id-46901493/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-RS3500/id-42986293/</t>
         </is>
       </c>
     </row>
@@ -5115,22 +5115,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Aflitos</t>
+          <t>Apartamento · 2 quartos · 50 m² · 1 vaga · Torre</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Avenida Conselheiro Rosa E Silva, 801</t>
+          <t>Rua Real Da Torre</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>4141.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>4142.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>75.31</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5175,22 +5175,22 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-aflitos-55m2-RS4141/id-45283901/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-50m2-RS3500/id-46933917/</t>
         </is>
       </c>
     </row>
@@ -5198,35 +5198,35 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Recife, Rogério Corretor</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 43 m² · Casa Amarela</t>
+          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Cardeal Arcoverde, 1</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>4200.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5236,27 +5236,27 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>4200.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>97.67</t>
+          <t>106.06</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5266,22 +5266,22 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-43m2-casa-amarela-recife--pe_33376830</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS3500/id-45844382/</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5289,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Rogério Corretor</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 80 m² · Aflitos</t>
+          <t>Apartamento · 2 quartos · 70 m² · Tamarineira</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5307,17 +5307,17 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Aflitos</t>
+          <t>Tamarineira</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>4350.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>54.38</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://www.rogeriocorretor.com/imovel/apartamento-2-quartos-aflitos-recife-1-vaga-80m2-code-695</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-70m2-tamarineira-recife--pe_33364198</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -5388,27 +5388,27 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 77 m² · Torre</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos De Lima Cavalcante</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1195.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5418,27 +5418,27 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>4395.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>79.91</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5448,22 +5448,22 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-55m2-RS3200/id-46174975/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-77m2-torre-recife--pe_33379670</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5471,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -5479,27 +5479,27 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 85 m² · 2 vagas · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 82 m² · Casa Forte</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Avenida Ministro Marcos Freire</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Casa Forte</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5509,27 +5509,27 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>52.94</t>
+          <t>42.68</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-110m2-RS4500/id-42417501/</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-82m2-casa-forte-recife--pe_33364920</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -5570,22 +5570,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 97 m² · 2 vagas · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 83 m² · Aflitos</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Avenida Ministro Marcos Freire, 3291</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>46.39</t>
+          <t>42.09</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5630,22 +5630,22 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>83.15</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4500/id-46421413/</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/850191006-42</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5653,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real Olinda</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -5661,22 +5661,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 56 m² · 1 vaga · Espinheiro</t>
+          <t>Apartamento · 4 quartos · 103 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rua São Salvador, 200</t>
+          <t>Rua Professor Francisco Xavier Paes Barreto</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>3501.0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>3501.0</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5701,42 +5701,42 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>80.36</t>
+          <t>33.99</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-espinheiro-70m2-RS4500/id-46923849/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-casa-caiada-bairros-olinda-com-garagem-103m2-aluguel-RS3501-id-2909202314/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5744,65 +5744,65 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Rogério Corretor</t>
+          <t>CTI Imobiliária, Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Apartamento · 4 quartos · 90 m² · Torre</t>
+          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Boa Vista</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos De Lima Cavalcanti, 60</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>553.0</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>174.0</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>4500.0</t>
+          <t>3527.0</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>80.16</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5812,22 +5812,22 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>https://www.rogeriocorretor.com/imovel/casa-4-quartos-torre-recife-90m2-code-736</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6519</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5835,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>CTI Imobiliária</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -5843,47 +5843,47 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Parnamirim</t>
+          <t>Apartamento · 2 quartos · 41 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Avenida Parnamirim</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>4700.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>550.0</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>4700.0</t>
+          <t>3542.0</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>78.33</t>
+          <t>86.39</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5903,22 +5903,22 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-parnamirim-RS4700/id-43942857/</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6210</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -5934,22 +5934,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 115 m² · 2 vagas · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Parnamirim</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Avenida Ministro Marcos Freire</t>
+          <t>Avenida Parnamirim, 375</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>5000.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>5000.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -5974,12 +5974,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>43.48</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -5994,22 +5994,22 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>115.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-115m2-RS5000/id-47073028/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-32m2-RS3600/id-41530823/</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6017,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -6025,80 +6025,1991 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t>Apartamento · 1 quarto · 34 m² · 1 vaga · Parnamirim</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Avenida Parnamirim, 375</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Parnamirim</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>600.0</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>105.88</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-55m2-RS3000/id-46882194/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>REMAX Recife e Olinda</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 51 m² · Aflitos</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Aflitos</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>3699.0</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>3699.0</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>72.53</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>51.0</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/307-rua-manuel-de-carvalho/850701030-101</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Recife</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 56 m² · 1 vaga · Torreão</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Rua Cândido Lacerda, 221</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Torreão</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>3500.0</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>3700.0</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>66.07</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>56.0</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torreao-62m2-RS3500/id-46711944/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Portal CRECI Brasil</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · Encruzilhada</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Encruzilhada</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>3700.0</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>3700.0</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-encruzilhada-recife--pe_33362592</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Âncora Imobiliária</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 90 m² · Graças</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Graças</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2300.0</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>1300.0</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>185.21</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>3785.21</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>42.06</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>https://ancoraimobiliaria.com.br/imovel/2698/apartamento-3-quartos-san-patrick-graças-recife/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Portal CRECI Brasil</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · Rosarinho</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Rosarinho</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>3800.0</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>3800.0</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-rosarinho-recife--pe_33388298</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>REMAX Recife e Olinda</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 70 m² · Encruzilhada</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Encruzilhada</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>3800.0</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>3800.0</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>54.29</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/edf-arcadia/850091082-77</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Viva Real Olinda</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Rua Joana D'Arc Sampaio</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>3900.0</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>3902.0</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>65.03</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3900-id-2913026520/?source=ranking%2Crp</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>REMAX Recife e Olinda</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 51 m² · Aflitos</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Aflitos</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>3990.0</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>3990.0</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>78.24</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>51.0</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/307-manuel-de-carvalho-edificio-praca-das-cerejeiras/850721013-37</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Recife, Josinildo Imóveis</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 74 m² · 1 vaga · Aflitos</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Rua Da Angustura, 195</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Aflitos</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>4091.0</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>4091.0</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>55.28</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-recife-aflitos-74m2-RS4091/id-46898128/</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Olinda, Rogério Corretor</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>2</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 145 m² · 2 vagas · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Avenida Min. Marcos Freire, 3495</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>4100.0</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>4100.0</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>28.28</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4100/id-46901493/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Recife</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Aflitos</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Avenida Conselheiro Rosa E Silva, 801</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Aflitos</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>4141.0</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>4142.0</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>75.31</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-aflitos-55m2-RS4141/id-45283901/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Portal CRECI Brasil</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 43 m² · Casa Amarela</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Casa Amarela</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>4200.0</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>4200.0</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>97.67</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>43.0</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-43m2-casa-amarela-recife--pe_33376830</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Rogério Corretor</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 80 m² · Aflitos</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Aflitos</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>750.0</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>4350.0</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>54.38</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>https://www.rogeriocorretor.com/imovel/apartamento-2-quartos-aflitos-recife-1-vaga-80m2-code-695</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Olinda</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 55 m² · 1 vaga · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Avenida Governador Carlos De Lima Cavalcante</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>3200.0</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>1195.0</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>4395.0</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>79.91</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-55m2-RS3200/id-46174975/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Olinda</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 85 m² · 2 vagas · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Avenida Ministro Marcos Freire</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>4500.0</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>4500.0</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>52.94</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-110m2-RS4500/id-42417501/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Olinda</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 97 m² · 2 vagas · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Avenida Ministro Marcos Freire, 3291</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>4500.0</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>4500.0</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>46.39</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-RS4500/id-46421413/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Recife</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 56 m² · 1 vaga · Espinheiro</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Rua São Salvador, 200</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Espinheiro</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>4500.0</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>4500.0</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>80.36</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>56.0</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-espinheiro-70m2-RS4500/id-46923849/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Rogério Corretor</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Apartamento · 4 quartos · 90 m² · Torre</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Torre</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>4500.0</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>4500.0</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>https://www.rogeriocorretor.com/imovel/casa-4-quartos-torre-recife-90m2-code-736</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Recife</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Apartamento · 2 quartos · 60 m² · 1 vaga · Parnamirim</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Avenida Parnamirim</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Parnamirim</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>4700.0</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>4700.0</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>78.33</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-parnamirim-RS4700/id-43942857/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Chaves na Mão Olinda</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Apartamento · 3 quartos · 115 m² · 2 vagas · Casa Caiada</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Avenida Ministro Marcos Freire</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Casa Caiada</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>43.48</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-3-quartos-com-garagem-pe-olinda-casa-caiada-115m2-RS5000/id-47073028/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Portal CRECI Brasil</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
           <t>Apartamento · 3 quartos · 89 m² · Torre</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>Torre</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>5500.0</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
         <is>
           <t>5500.0</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>61.8</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
         <is>
           <t>89.0</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="R83" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-89m2-torre-recife--pe_33386591</t>
         </is>

--- a/saida/apartamentos.xlsx
+++ b/saida/apartamentos.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S90"/>
+  <dimension ref="A1:S91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -724,55 +724,55 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 40 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rua Carlos Nigro</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1449.0</t>
+          <t>1100.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>505.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1449.0</t>
+          <t>1677.0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -792,22 +792,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-30m2-aluguel-RS1449-id-2906060215/?source=ranking%2Crp</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/2553/apartamento-1-quarto-arpege-boa-vista-recife/</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 40 m² · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 50 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -833,27 +833,27 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1100.0</t>
+          <t>1450.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>505.0</t>
+          <t>405.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>80.96</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1677.0</t>
+          <t>1935.96</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -863,12 +863,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>38.72</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -883,22 +883,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/2553/apartamento-1-quarto-arpege-boa-vista-recife/</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/6691/apartamento-2-quartos-santo-amaro-recife/</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -914,47 +914,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · Encruzilhada</t>
+          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Coronel Alberto Lundgren, 604</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1750.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1750.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>53.03</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -974,22 +974,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/123-rua-carlos-borromeu-de-frente-para-o-mercado-da-encruzilhada/850471068-78</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS1800/id-46397377/</t>
         </is>
       </c>
     </row>
@@ -997,65 +997,65 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · Santo Amaro</t>
+          <t>Apartamento · 1 quarto · 1322 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Doutor Manoel de Barros Lima</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1450.0</t>
+          <t>2150.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>405.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>80.96</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1935.96</t>
+          <t>2150.0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>38.72</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>1322.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/6691/apartamento-2-quartos-santo-amaro-recife/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-bairro-novo-bairros-olinda-1322m2-aluguel-RS2150-id-2914115768/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1161,17 +1161,17 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS1800/id-46397377/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS2000/id-46397376/</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 1322 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 65 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rua Doutor Manoel de Barros Lima</t>
+          <t>Rua Professor José Cândido Pessoa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2150.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2150.0</t>
+          <t>2200.0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1227,17 +1227,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1247,22 +1247,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1322.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-bairro-novo-bairros-olinda-1322m2-aluguel-RS2150-id-2914115768/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-65m2-aluguel-RS2200-id-2897302602/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rua Coronel Alberto Lundgren, 604</t>
+          <t>Rua Professor José Cândido Pessoa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1293,22 +1293,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>1700.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>684.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2200.0</t>
+          <t>2477.0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>68.81</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-30m2-RS2000/id-46397376/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-720m2-RS1700/id-43805924/</t>
         </is>
       </c>
     </row>
@@ -1361,90 +1361,90 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 70 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rua Professor José Cândido Pessoa</t>
+          <t>Rua Nereu Gomes Maciel</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1700.0</t>
+          <t>2499.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>684.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2477.0</t>
+          <t>2499.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>68.81</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-olinda-bairro-novo-720m2-RS1700/id-43805924/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-70m2-aluguel-RS2499-id-2903057019/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -1543,25 +1543,25 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 36 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Avenida Governador Carlos De Lima Cavalcante</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1591,37 +1591,37 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>69.44</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>35.0</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1915,17 +1915,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 71 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 35 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rua Gildo Branco</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1955,42 +1955,42 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>36.62</t>
+          <t>74.29</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-71m2-aluguel-RS2600-id-2911301943/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/flat-1-quartos-bairro-novo-bairros-olinda-com-garagem-35m2-aluguel-RS2600-id-2912188115/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2097,17 +2097,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · Bairro Novo</t>
+          <t>Apartamento · 3 quartos · 71 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Rua Gildo Branco</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2137,42 +2137,42 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>74.29</t>
+          <t>36.62</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/flat-1-quartos-bairro-novo-bairros-olinda-com-garagem-35m2-aluguel-RS2600-id-2912188115/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-casa-caiada-bairros-olinda-com-garagem-71m2-aluguel-RS2600-id-2911301943/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2271,25 +2271,25 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 30 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 77 m² · Santana</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Santana</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2319,17 +2319,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>35.06</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2339,22 +2339,22 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-30m2-aluguel-RS2700-id-2913849795/?source=ranking%2Crp</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/458-santanna-proximo-ao-parque-de-santana/850501009-266</t>
         </is>
       </c>
     </row>
@@ -2362,20 +2362,20 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 30 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa Monteiro, 93</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1526.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1178.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2400,22 +2400,22 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2704.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2430,22 +2430,22 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1526/id-45586419/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-30m2-aluguel-RS2700-id-2913849795/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2453,20 +2453,20 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 36 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 93 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Rua Otaviano Pessoa Monteiro, 93</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>1526.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1178.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2491,52 +2491,52 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>2704.0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>29.08</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-36m2-aluguel-RS2800-id-2705654338/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-RS1526/id-45586419/</t>
         </is>
       </c>
     </row>
@@ -2552,17 +2552,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 36 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2592,42 +2592,42 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-60m2-aluguel-RS2800-id-2912116616/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-36m2-aluguel-RS2800-id-2705654338/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2635,35 +2635,35 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CTI Imobiliária</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
+          <t>Apartamento · 2 quartos · 60 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2500.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>380.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2673,17 +2673,17 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2880.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2703,22 +2703,22 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-torre-recife-pe/1353</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-com-garagem-60m2-aluguel-RS2800-id-2912116616/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Âncora Imobiliária</t>
+          <t>CTI Imobiliária</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>2500.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2759,12 +2759,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>176.42</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2956.42</t>
+          <t>2880.0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>https://ancoraimobiliaria.com.br/imovel/6596/apartamento-2-quartos-torre-recife/</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-torre-recife-pe/1353</t>
         </is>
       </c>
     </row>
@@ -2817,55 +2817,55 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Âncora Imobiliária</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 42 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 45 m² · Torre</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rua Ulisses Tenório de Albuquerque</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2998.0</t>
+          <t>2400.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>380.0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>176.42</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2998.0</t>
+          <t>2956.42</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>71.38</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2885,22 +2885,22 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-42m2-aluguel-RS2998-id-2911376544/?source=ranking%2Crp</t>
+          <t>https://ancoraimobiliaria.com.br/imovel/6596/apartamento-2-quartos-torre-recife/</t>
         </is>
       </c>
     </row>
@@ -3363,25 +3363,25 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · Graças</t>
+          <t>Apartamento · 1 quarto · 34 m² · Santo Amaro</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rua da Amizade</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3431,22 +3431,22 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-gracas-bairros-recife-com-garagem-35m2-aluguel-RS3000-id-2507980929/?source=ranking%2Crp</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/185-rua-dom-pedro-henrique-prox-a-catolica/850301004-158</t>
         </is>
       </c>
     </row>
@@ -3454,25 +3454,25 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 35 m² · Graças</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Rua da Amizade</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3502,17 +3502,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3522,22 +3522,22 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3000-id-2913637829/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-gracas-bairros-recife-com-garagem-35m2-aluguel-RS3000-id-2507980929/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3553,12 +3553,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 62 m² · Casa Caiada</t>
+          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rua Otaviano Pessoa Monteiro</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>48.39</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3613,22 +3613,22 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-62m2-aluguel-RS3000-id-2911451041/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3000-id-2913637829/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3644,17 +3644,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 60 m² · Casa Caiada</t>
+          <t>Apartamento · 4 quartos · 147 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Rua Coronel João Manguinhos</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3684,17 +3684,17 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>20.41</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3704,22 +3704,22 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3000-id-2859906255/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-bairro-novo-bairros-olinda-com-garagem-147m2-aluguel-RS3000-id-2912098153/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 35 m² · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 60 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3795,22 +3795,22 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-35m2-aluguel-RS3000-id-2913485117/?source=ranking%2Crp</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3000-id-2859906255/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3917,22 +3917,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 2 quartos · 56 m² · Torreão</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rua Amélia, 623</t>
+          <t>Rua Cândido Lacerda</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Torreão</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3100.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>3200.0</t>
+          <t>3100.0</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3957,17 +3957,17 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>55.36</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3977,22 +3977,22 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-RS3200/id-45197779/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-torreao-bairros-recife-com-garagem-56m2-aluguel-RS3100-id-2889237280/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Newville</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -4008,17 +4008,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 52 m² · Torre</t>
+          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Amélia, 623</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4048,17 +4048,17 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4068,22 +4068,22 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>https://newville.com.br/imovel/apartamento_2_quartos--torre--recife--pe--locacao--cod-6391</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-RS3200/id-45197779/</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Newville</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 38 m² · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 52 m² · Torre</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4159,22 +4159,22 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-1-quarto-alugar-38m2-boa-vista-recife--pe_33378812</t>
+          <t>https://newville.com.br/imovel/apartamento_2_quartos--torre--recife--pe--locacao--cod-6391</t>
         </is>
       </c>
     </row>
@@ -4182,25 +4182,25 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 56 m² · Torre</t>
+          <t>Apartamento · 1 quarto · 38 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rua Marquês de Maricá</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4230,17 +4230,17 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4250,22 +4250,22 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-torre-bairros-recife-com-garagem-56m2-aluguel-RS3200-id-2914225341/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-1-quarto-alugar-38m2-boa-vista-recife--pe_33378812</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4273,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>REMAX Recife e Olinda, Viva Real</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -4346,17 +4346,17 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-1-quartos-santana-bairros-recife-com-garagem-40m2-aluguel-RS3200-id-2913910137/?source=ranking%2Crp</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/70-rua-samuel-de-farias/850091105-39</t>
         </is>
       </c>
     </row>
@@ -4364,25 +4364,25 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
+          <t>Apartamento · 1 quarto · 35 m² · Encruzilhada</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4412,17 +4412,17 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>91.43</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4432,22 +4432,22 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3200-id-2906163316/?source=ranking%2Crp</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/68-rua-engenheiro-sampaio/850701030-102</t>
         </is>
       </c>
     </row>
@@ -4455,55 +4455,55 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · 1 vaga · Casa Amarela</t>
+          <t>Apartamento · 2 quartos · 60 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Casa Amarela</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2000.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>237.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>3202.0</t>
+          <t>3200.0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>45.74</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4523,22 +4523,22 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-amarela-70m2-RS2000/id-43758789/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-caiada-bairros-olinda-com-garagem-60m2-aluguel-RS3200-id-2906163316/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4546,60 +4546,60 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 65 m² · Encruzilhada</t>
+          <t>Apartamento · 2 quartos · 70 m² · 1 vaga · Casa Amarela</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rua Marechal Deodoro</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Encruzilhada</t>
+          <t>Casa Amarela</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>2000.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>237.0</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>3300.0</t>
+          <t>3202.0</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>50.77</t>
+          <t>45.74</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4614,22 +4614,22 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-encruzilhada-bairros-recife-com-garagem-65m2-aluguel-RS3300-id-2914237860/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-casa-amarela-70m2-RS2000/id-43758789/</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -4645,59 +4645,59 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 65 m² · 1 vaga · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 65 m² · Encruzilhada</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rua Eduardo De Moraes, 85</t>
+          <t>Rua Marechal Deodoro</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Encruzilhada</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2700.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>421.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>3316.0</t>
+          <t>3300.0</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>50.77</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O47" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -4710,17 +4710,17 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-65m2-RS2700/id-47042111/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-encruzilhada-bairros-recife-com-garagem-65m2-aluguel-RS3300-id-2914237860/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -4728,25 +4728,25 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 65 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 65 m² · 1 vaga · Casa Caiada</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rua Eduardo de Moraes</t>
+          <t>Rua Eduardo De Moraes, 85</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>422.0</t>
+          <t>421.0</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>3317.0</t>
+          <t>3316.0</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>51.03</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4801,17 +4801,17 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-1038m2-RS2700/id-27611651/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-casa-caiada-65m2-RS2700/id-47042111/</t>
         </is>
       </c>
     </row>
@@ -4819,67 +4819,67 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 38 m² · 1 vaga · Espinheiro</t>
+          <t>Apartamento · 2 quartos · 65 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rua Barão De Itamaracá, 78</t>
+          <t>Rua Eduardo de Moraes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Espinheiro</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>3350.0</t>
+          <t>2700.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>422.0</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>3350.0</t>
+          <t>3317.0</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>88.16</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O49" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -4887,22 +4887,22 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-espinheiro-38m2-RS3350/id-46539992/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-1038m2-RS2700/id-27611651/</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4910,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -4918,22 +4918,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 59 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 38 m² · 1 vaga · Espinheiro</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rua Pereira Simões, 1529 - 2</t>
+          <t>Rua Barão De Itamaracá, 78</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Espinheiro</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3350.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3350.0</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4958,42 +4958,42 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>59.32</t>
+          <t>88.16</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-59m2-RS3500/id-45711136/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-espinheiro-38m2-RS3350/id-46539992/</t>
         </is>
       </c>
     </row>
@@ -5001,30 +5001,30 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Chaves na Mão Olinda</t>
+          <t>Rogério Corretor, Viva Real</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 57 m² · 1 vaga · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 34 m² · Graças</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rua Francisco Ambrósio De Barros Leite, 1225</t>
+          <t>Rua Ricardo Hardman</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3450.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>3500.0</t>
+          <t>3450.0</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5049,12 +5049,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-RS3500/id-42986293/</t>
+          <t>https://www.rogeriocorretor.com/imovel/apartamento-1-quarto-gracas-recife-1-vaga-34m2-code-726</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5092,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Chaves na Mão Olinda</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -5100,17 +5100,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 50 m² · 1 vaga · Torre</t>
+          <t>Apartamento · 2 quartos · 59 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rua Real Da Torre</t>
+          <t>Rua Pereira Simões, 1529 - 2</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>59.32</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5160,22 +5160,22 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-50m2-RS3500/id-46933917/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-59m2-RS3500/id-45711136/</t>
         </is>
       </c>
     </row>
@@ -5183,25 +5183,25 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife, Rogério Corretor</t>
+          <t>Chaves na Mão Olinda, Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 33 m² · 1 vaga · Graças</t>
+          <t>Apartamento · 2 quartos · 57 m² · 1 vaga · Bairro Novo</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rua Cardeal Arcoverde, 1</t>
+          <t>Rua Francisco Ambrósio de Barros Leite</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Graças</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5231,19 +5231,19 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>106.06</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O53" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS3500/id-45844382/</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-olinda-bairro-novo-RS3500/id-42986293/</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5274,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -5282,17 +5282,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · Tamarineira</t>
+          <t>Apartamento · 2 quartos · 50 m² · 1 vaga · Torre</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Real Da Torre</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tamarineira</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5317,47 +5317,47 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-70m2-tamarineira-recife--pe_33364198</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-50m2-RS3500/id-46933917/</t>
         </is>
       </c>
     </row>
@@ -5365,7 +5365,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Portal CRECI Brasil</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -5373,17 +5373,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 77 m² · Torre</t>
+          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Graças</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua Cardeal Arcoverde, 1</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Graças</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5413,17 +5413,17 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>109.38</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5433,22 +5433,22 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-77m2-torre-recife--pe_33379670</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-gracas-32m2-RS3500/id-45844382/</t>
         </is>
       </c>
     </row>
@@ -5456,25 +5456,25 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 60 m² · Bairro Novo</t>
+          <t>Apartamento · 2 quartos · 70 m² · Tamarineira</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rua Maria Ramos</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Tamarineira</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5499,12 +5499,12 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5524,22 +5524,22 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-60m2-aluguel-RS3500-id-2904577437/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-2-quarto-alugar-70m2-tamarineira-recife--pe_33364198</t>
         </is>
       </c>
     </row>
@@ -5547,25 +5547,25 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Portal CRECI Brasil</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Apartamento · 4 quartos · 160 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 77 m² · Torre</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos de Lima Cavalcante</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Torre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5595,42 +5595,42 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>21.88</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-casa-caiada-bairros-olinda-com-garagem-160m2-aluguel-RS3500-id-2909290334/?source=ranking%2Crp</t>
+          <t>https://www.portalcreci.org.br/Anuncio/Index/apartamento-3-quarto-alugar-77m2-torre-recife--pe_33379670</t>
         </is>
       </c>
     </row>
@@ -5638,25 +5638,25 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>REMAX Recife e Olinda</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Apartamento · 4 quartos · 130 m² · Casa Caiada</t>
+          <t>Apartamento · 3 quartos · 83 m² · Aflitos</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Avenida Ministro Marcos Freire</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Casa Caiada</t>
+          <t>Aflitos</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5686,17 +5686,17 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>42.09</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5706,22 +5706,22 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>83.15</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-casa-caiada-bairros-olinda-com-garagem-130m2-aluguel-RS3500-id-2911955918/?source=ranking%2Crp</t>
+          <t>https://www.remax.com.br/pt-br/imoveis/apartamento/alugar/recife/850191006-42</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CTI Imobiliária, Chaves na Mão Recife</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -5737,47 +5737,47 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Boa Vista</t>
+          <t>Apartamento · 2 quartos · 60 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Avenida Governador Carlos De Lima Cavalcanti, 60</t>
+          <t>Rua Maria Ramos</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>553.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>3527.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>80.16</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5797,22 +5797,22 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6519</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-bairro-novo-bairros-olinda-60m2-aluguel-RS3500-id-2904577437/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5820,90 +5820,90 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CTI Imobiliária</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 41 m² · Boa Vista</t>
+          <t>Apartamento · 4 quartos · 160 m² · Casa Caiada</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Avenida Governador Carlos de Lima Cavalcante</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Boa Vista</t>
+          <t>Casa Caiada</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>550.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>3542.0</t>
+          <t>3500.0</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>86.39</t>
+          <t>21.88</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6210</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-4-quartos-casa-caiada-bairros-olinda-com-garagem-160m2-aluguel-RS3500-id-2909290334/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -5911,67 +5911,67 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>CTI Imobiliária, Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Parnamirim</t>
+          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Boa Vista</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Avenida Parnamirim, 375</t>
+          <t>Avenida Governador Carlos De Lima Cavalcanti, 60</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>553.0</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>174.0</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3527.0</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>80.16</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O61" t="inlineStr">
         <is>
           <t>Não Localizado</t>
@@ -5979,22 +5979,22 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-32m2-RS3600/id-41530823/</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6519</t>
         </is>
       </c>
     </row>
@@ -6002,7 +6002,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>CTI Imobiliária</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -6010,37 +6010,37 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 34 m² · 1 vaga · Parnamirim</t>
+          <t>Apartamento · 2 quartos · 41 m² · Boa Vista</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Avenida Parnamirim, 375</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Boa Vista</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>2800.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>600.0</t>
+          <t>550.0</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>3600.0</t>
+          <t>3542.0</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6050,17 +6050,17 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>105.88</t>
+          <t>86.39</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6070,22 +6070,22 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-55m2-RS3000/id-46882194/</t>
+          <t>https://www.ctiimobiliaria.com.br/imovel/apartamento-para-alugar-boa-vista-recife-pe/6210</t>
         </is>
       </c>
     </row>
@@ -6093,25 +6093,25 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Viva Real, Zap Imóveis</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 70 m² · Casa Forte</t>
+          <t>Apartamento · 1 quarto · 32 m² · 1 vaga · Parnamirim</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rua Edson Álvares</t>
+          <t>Avenida Parnamirim, 375</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Casa Forte</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -6141,42 +6141,42 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>51.43</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Não Localizado</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-forte-bairros-recife-com-garagem-70m2-aluguel-RS3600-id-2914239412/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-32m2-RS3600/id-41530823/</t>
         </is>
       </c>
     </row>
@@ -6184,65 +6184,65 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Apartamento · 3 quartos · 90 m² · Bairro Novo</t>
+          <t>Apartamento · 1 quarto · 34 m² · 1 vaga · Parnamirim</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rua Coronel João Manguinhos</t>
+          <t>Avenida Parnamirim, 375</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bairro Novo</t>
+          <t>Parnamirim</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
+          <t>3000.0</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>600.0</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
           <t>3600.0</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>105.88</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6252,22 +6252,22 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-bairros-olinda-com-garagem-90m2-aluguel-RS3600-id-2914003157/?source=ranking%2Crp</t>
+          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-55m2-RS3000/id-46882194/</t>
         </is>
       </c>
     </row>
@@ -6275,7 +6275,7 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -6283,17 +6283,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Torre</t>
+          <t>Apartamento · 2 quartos · 70 m² · Casa Forte</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rua José De Holanda, 854</t>
+          <t>Rua Edson Álvares</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Torre</t>
+          <t>Casa Forte</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>3601.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>81.84</t>
+          <t>51.43</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6333,32 +6333,32 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-2-quartos-com-garagem-pe-recife-torre-RS3600/id-40119104/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-2-quartos-casa-forte-bairros-recife-com-garagem-70m2-aluguel-RS3600-id-2914239412/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -6366,30 +6366,30 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Chaves na Mão Recife</t>
+          <t>Viva Real Olinda, Zap Imóveis Olinda</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Apartamento · 1 quarto · 40 m² · 1 vaga · Parnamirim</t>
+          <t>Apartamento · 3 quartos · 90 m² · Bairro Novo</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rua Doutor Virgílio Mota, 73</t>
+          <t>Rua Coronel João Manguinhos</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Parnamirim</t>
+          <t>Bairro Novo</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>3650.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>3650.0</t>
+          <t>3600.0</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6414,42 +6414,42 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>91.25</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Não Localizado</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>Não Localizado</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>https://www.chavesnamao.com.br/imovel/apartamento-para-alugar-1-quarto-com-garagem-pe-recife-parnamirim-40m2-RS3650/id-45924007/</t>
+          <t>https://www.vivareal.com.br/imovel/apartamento-3-quartos-bairro-novo-bairros-olinda-com-garagem-90m2-aluguel-RS3600-id-2914003157/?source=ranking%2Crp</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>REMAX Recife e Olinda</t>
+          <t>Chaves na Mão Recife</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -6465,22 +6465,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Apartamento · 2 quartos · 51 m² · Aflitos</t>
+          <t>Apartamento · 2 quartos · 44 m² · 1 vaga · Torre</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Não Localizado</t>
+          <t>Rua José De Holanda, 854</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-